--- a/2.RD_CGE/Input_w-t/Employment.xlsx
+++ b/2.RD_CGE/Input_w-t/Employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10759959-802E-4BF9-8029-2C1324C9A185}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE52439-CFC2-423B-8D57-6AD72F426B66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="4" xr2:uid="{DE1A9DA4-B28E-43B1-BF27-4214AB335DA3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{DE1A9DA4-B28E-43B1-BF27-4214AB335DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="LDC, LS" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -827,15 +827,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
@@ -857,7 +848,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -11238,7 +11238,7 @@
       <c r="B4" s="36">
         <v>14.502000000000001</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="64">
         <f>'R17'!J3</f>
         <v>230111.22980023501</v>
       </c>
@@ -11251,7 +11251,7 @@
       <c r="F4" s="36">
         <v>57.923000000000002</v>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="64">
         <f>'R17'!J7</f>
         <v>1899.8952166196839</v>
       </c>
@@ -11339,7 +11339,7 @@
       <c r="B5" s="36">
         <v>4429.1210000000001</v>
       </c>
-      <c r="C5" s="47"/>
+      <c r="C5" s="65"/>
       <c r="D5" s="36">
         <v>10606.694</v>
       </c>
@@ -11349,7 +11349,7 @@
       <c r="F5" s="36">
         <v>90.254999999999995</v>
       </c>
-      <c r="G5" s="47"/>
+      <c r="G5" s="65"/>
       <c r="I5" t="s">
         <v>21</v>
       </c>
@@ -11434,7 +11434,7 @@
       <c r="B6" s="36">
         <v>67.915999999999997</v>
       </c>
-      <c r="C6" s="47"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="36">
         <v>278.50799999999998</v>
       </c>
@@ -11444,7 +11444,7 @@
       <c r="F6" s="36">
         <v>19.347999999999999</v>
       </c>
-      <c r="G6" s="47"/>
+      <c r="G6" s="65"/>
       <c r="I6" t="s">
         <v>22</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="B7" s="36">
         <v>135.11699999999999</v>
       </c>
-      <c r="C7" s="47"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="36">
         <v>322.791</v>
       </c>
@@ -11539,7 +11539,7 @@
       <c r="F7" s="36">
         <v>10.786</v>
       </c>
-      <c r="G7" s="47"/>
+      <c r="G7" s="65"/>
       <c r="I7" t="s">
         <v>23</v>
       </c>
@@ -11624,7 +11624,7 @@
       <c r="B8" s="36">
         <v>2019.588</v>
       </c>
-      <c r="C8" s="48"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="36">
         <v>4960.6779999999999</v>
       </c>
@@ -11634,7 +11634,7 @@
       <c r="F8" s="36">
         <v>68.847999999999999</v>
       </c>
-      <c r="G8" s="48"/>
+      <c r="G8" s="66"/>
       <c r="I8" t="s">
         <v>24</v>
       </c>
@@ -11719,7 +11719,7 @@
       <c r="B9" s="36">
         <v>3662.6019999999999</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="64">
         <f>'R17'!K3</f>
         <v>330795.37743578054</v>
       </c>
@@ -11732,7 +11732,7 @@
       <c r="F9" s="36">
         <v>160.405</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="64">
         <f>'R17'!K7</f>
         <v>6338.7901704974856</v>
       </c>
@@ -11820,7 +11820,7 @@
       <c r="B10" s="36">
         <v>1431.36</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="36">
         <v>3723.1309999999999</v>
       </c>
@@ -11830,7 +11830,7 @@
       <c r="F10" s="36">
         <v>61.122999999999998</v>
       </c>
-      <c r="G10" s="47"/>
+      <c r="G10" s="65"/>
       <c r="I10" t="s">
         <v>26</v>
       </c>
@@ -11915,7 +11915,7 @@
       <c r="B11" s="36">
         <v>2303.41</v>
       </c>
-      <c r="C11" s="47"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="36">
         <v>4183.7129999999997</v>
       </c>
@@ -11925,7 +11925,7 @@
       <c r="F11" s="36">
         <v>36.280999999999999</v>
       </c>
-      <c r="G11" s="47"/>
+      <c r="G11" s="65"/>
       <c r="I11" t="s">
         <v>27</v>
       </c>
@@ -12010,7 +12010,7 @@
       <c r="B12" s="36">
         <v>860.50400000000002</v>
       </c>
-      <c r="C12" s="47"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="36">
         <v>3273.18</v>
       </c>
@@ -12020,7 +12020,7 @@
       <c r="F12" s="36">
         <v>12.954000000000001</v>
       </c>
-      <c r="G12" s="47"/>
+      <c r="G12" s="65"/>
       <c r="I12" t="s">
         <v>28</v>
       </c>
@@ -12105,7 +12105,7 @@
       <c r="B13" s="36">
         <v>799.995</v>
       </c>
-      <c r="C13" s="47"/>
+      <c r="C13" s="65"/>
       <c r="D13" s="36">
         <v>1646.1379999999999</v>
       </c>
@@ -12115,7 +12115,7 @@
       <c r="F13" s="36">
         <v>24.257000000000001</v>
       </c>
-      <c r="G13" s="47"/>
+      <c r="G13" s="65"/>
       <c r="I13" t="s">
         <v>29</v>
       </c>
@@ -12200,7 +12200,7 @@
       <c r="B14" s="36">
         <v>555.72699999999998</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="36">
         <v>997.42200000000003</v>
       </c>
@@ -12210,7 +12210,7 @@
       <c r="F14" s="36">
         <v>1.1539999999999999</v>
       </c>
-      <c r="G14" s="47"/>
+      <c r="G14" s="65"/>
       <c r="I14" t="s">
         <v>30</v>
       </c>
@@ -12295,7 +12295,7 @@
       <c r="B15" s="36">
         <v>1156.684</v>
       </c>
-      <c r="C15" s="47"/>
+      <c r="C15" s="65"/>
       <c r="D15" s="36">
         <v>1697.019</v>
       </c>
@@ -12305,7 +12305,7 @@
       <c r="F15" s="36">
         <v>18.030999999999999</v>
       </c>
-      <c r="G15" s="47"/>
+      <c r="G15" s="65"/>
       <c r="I15" t="s">
         <v>31</v>
       </c>
@@ -12390,7 +12390,7 @@
       <c r="B16" s="36">
         <v>1311.5930000000001</v>
       </c>
-      <c r="C16" s="47"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="36">
         <v>522.83000000000004</v>
       </c>
@@ -12400,7 +12400,7 @@
       <c r="F16" s="36">
         <v>20.163</v>
       </c>
-      <c r="G16" s="47"/>
+      <c r="G16" s="65"/>
       <c r="I16" t="s">
         <v>32</v>
       </c>
@@ -12485,7 +12485,7 @@
       <c r="B17" s="36">
         <v>1076.364</v>
       </c>
-      <c r="C17" s="47"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="36">
         <v>268.52600000000001</v>
       </c>
@@ -12495,7 +12495,7 @@
       <c r="F17" s="36">
         <v>85.953000000000003</v>
       </c>
-      <c r="G17" s="47"/>
+      <c r="G17" s="65"/>
       <c r="I17" t="s">
         <v>33</v>
       </c>
@@ -12580,7 +12580,7 @@
       <c r="B18" s="36">
         <v>1883.3330000000001</v>
       </c>
-      <c r="C18" s="47"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="36">
         <v>3327.5749999999998</v>
       </c>
@@ -12590,7 +12590,7 @@
       <c r="F18" s="36">
         <v>96.108000000000004</v>
       </c>
-      <c r="G18" s="47"/>
+      <c r="G18" s="65"/>
       <c r="I18" t="s">
         <v>34</v>
       </c>
@@ -12675,7 +12675,7 @@
       <c r="B19" s="36">
         <v>2205.9699999999998</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="36">
         <v>8364.0650000000005</v>
       </c>
@@ -12685,7 +12685,7 @@
       <c r="F19" s="36">
         <v>44.37</v>
       </c>
-      <c r="G19" s="47"/>
+      <c r="G19" s="65"/>
       <c r="I19" t="s">
         <v>35</v>
       </c>
@@ -12770,7 +12770,7 @@
       <c r="B20" s="36">
         <v>494.846</v>
       </c>
-      <c r="C20" s="47"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="36">
         <v>3662.3850000000002</v>
       </c>
@@ -12780,7 +12780,7 @@
       <c r="F20" s="36">
         <v>17.998999999999999</v>
       </c>
-      <c r="G20" s="47"/>
+      <c r="G20" s="65"/>
       <c r="I20" t="s">
         <v>36</v>
       </c>
@@ -12865,7 +12865,7 @@
       <c r="B21" s="36">
         <v>1232.653</v>
       </c>
-      <c r="C21" s="47"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="36">
         <v>1848.499</v>
       </c>
@@ -12875,7 +12875,7 @@
       <c r="F21" s="36">
         <v>24.547000000000001</v>
       </c>
-      <c r="G21" s="47"/>
+      <c r="G21" s="65"/>
       <c r="I21" t="s">
         <v>37</v>
       </c>
@@ -12960,7 +12960,7 @@
       <c r="B22" s="36">
         <v>74.706999999999994</v>
       </c>
-      <c r="C22" s="47"/>
+      <c r="C22" s="65"/>
       <c r="D22" s="36">
         <v>2317.614</v>
       </c>
@@ -12970,7 +12970,7 @@
       <c r="F22" s="36">
         <v>3.2749999999999999</v>
       </c>
-      <c r="G22" s="47"/>
+      <c r="G22" s="65"/>
       <c r="I22" t="s">
         <v>38</v>
       </c>
@@ -13055,7 +13055,7 @@
       <c r="B23" s="36">
         <v>11.797000000000001</v>
       </c>
-      <c r="C23" s="47"/>
+      <c r="C23" s="65"/>
       <c r="D23" s="36">
         <v>1484.646</v>
       </c>
@@ -13065,7 +13065,7 @@
       <c r="F23" s="36">
         <v>2.0139999999999998</v>
       </c>
-      <c r="G23" s="47"/>
+      <c r="G23" s="65"/>
       <c r="I23" t="s">
         <v>39</v>
       </c>
@@ -13150,13 +13150,13 @@
       <c r="B24" s="36">
         <v>108.663</v>
       </c>
-      <c r="C24" s="48"/>
+      <c r="C24" s="66"/>
       <c r="D24" s="36"/>
       <c r="E24" s="36"/>
       <c r="F24" s="36">
         <v>16.995000000000001</v>
       </c>
-      <c r="G24" s="48"/>
+      <c r="G24" s="66"/>
       <c r="I24" t="s">
         <v>40</v>
       </c>
@@ -14720,37 +14720,37 @@
       <c r="Y2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="64" t="s">
+      <c r="AB2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="64" t="s">
+      <c r="AC2" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="AD2" s="64" t="s">
+      <c r="AD2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AE2" s="64" t="s">
+      <c r="AE2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" s="64" t="s">
+      <c r="AF2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="AG2" s="64" t="s">
+      <c r="AG2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AH2" s="64" t="s">
+      <c r="AH2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AI2" s="64" t="s">
+      <c r="AI2" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="AJ2" s="64" t="s">
+      <c r="AJ2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AK2" s="64" t="s">
+      <c r="AK2" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="AL2" s="64" t="s">
+      <c r="AL2" s="61" t="s">
         <v>17</v>
       </c>
     </row>
@@ -14758,97 +14758,97 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="58">
         <v>8.6774000000000004</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="58">
         <v>11.7065</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3" s="58">
         <v>11.3611</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="58">
         <v>1.69085</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="58">
         <v>1.5001599999999999</v>
       </c>
-      <c r="G3" s="61">
+      <c r="G3" s="58">
         <v>6.2986599999999999</v>
       </c>
-      <c r="H3" s="61">
+      <c r="H3" s="58">
         <v>8.9731400000000008</v>
       </c>
-      <c r="I3" s="61">
+      <c r="I3" s="58">
         <v>2.8198699999999999</v>
       </c>
-      <c r="J3" s="61">
+      <c r="J3" s="58">
         <v>29.2409</v>
       </c>
-      <c r="K3" s="61">
+      <c r="K3" s="58">
         <v>9.1507299999999994</v>
       </c>
-      <c r="L3" s="61">
+      <c r="L3" s="58">
         <v>1.6977199999999999</v>
       </c>
       <c r="N3" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="51"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="48"/>
       <c r="AA3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" s="63">
+      <c r="AB3" s="60">
         <f>'R17'!N23</f>
         <v>3013.7449883689551</v>
       </c>
-      <c r="AC3" s="63">
+      <c r="AC3" s="60">
         <f>'R17'!O23</f>
         <v>40613.028794254271</v>
       </c>
-      <c r="AD3" s="63">
+      <c r="AD3" s="60">
         <f>'R17'!P23</f>
         <v>10134.688716835852</v>
       </c>
-      <c r="AE3" s="63">
+      <c r="AE3" s="60">
         <f>'R17'!Q23</f>
         <v>5659.7225029440533</v>
       </c>
-      <c r="AF3" s="63">
+      <c r="AF3" s="60">
         <f>'R17'!R23</f>
         <v>14012.492902458791</v>
       </c>
-      <c r="AG3" s="63">
+      <c r="AG3" s="60">
         <f>'R17'!S23</f>
         <v>26036.1120361576</v>
       </c>
-      <c r="AH3" s="63">
+      <c r="AH3" s="60">
         <f>'R17'!T23</f>
         <v>203725.33954966738</v>
       </c>
-      <c r="AI3" s="63">
+      <c r="AI3" s="60">
         <f>'R17'!U23</f>
         <v>24335.925717258258</v>
       </c>
-      <c r="AJ3" s="63">
+      <c r="AJ3" s="60">
         <f>'R17'!V23</f>
         <v>260012.23677728849</v>
       </c>
-      <c r="AK3" s="63">
+      <c r="AK3" s="60">
         <f>'R17'!W23</f>
         <v>74893.657395713381</v>
       </c>
-      <c r="AL3" s="63">
+      <c r="AL3" s="60">
         <f>'R17'!X23</f>
         <v>487.99553781470706</v>
       </c>
@@ -14857,130 +14857,130 @@
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="58">
         <v>0.55101500000000003</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="58">
         <v>4.7880499999999999E-2</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="58">
         <v>0.154394</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="58">
         <v>0.18962100000000001</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="58">
         <v>0.20752200000000001</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="58">
         <v>5.9234300000000004E-3</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="58">
         <v>0.23750499999999999</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="58">
         <v>8.0176399999999995E-2</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="58">
         <v>0.55425500000000005</v>
       </c>
-      <c r="K4" s="61">
+      <c r="K4" s="58">
         <v>0.24721799999999999</v>
       </c>
-      <c r="L4" s="61">
+      <c r="L4" s="58">
         <v>0.340665</v>
       </c>
       <c r="N4" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4" s="49">
         <f>B4/SUM(B$4:B$29)</f>
         <v>2.8886542695609439E-3</v>
       </c>
-      <c r="P4" s="53">
+      <c r="P4" s="50">
         <f t="shared" ref="P4:Y19" si="0">C4/SUM(C$4:C$29)</f>
         <v>1.0174827742772687E-3</v>
       </c>
-      <c r="Q4" s="53">
+      <c r="Q4" s="50">
         <f t="shared" si="0"/>
         <v>1.0213874012728692E-3</v>
       </c>
-      <c r="R4" s="53">
+      <c r="R4" s="50">
         <f t="shared" si="0"/>
         <v>1.460913148185205E-2</v>
       </c>
-      <c r="S4" s="53">
+      <c r="S4" s="50">
         <f t="shared" si="0"/>
         <v>2.6244087445053525E-2</v>
       </c>
-      <c r="T4" s="53">
+      <c r="T4" s="50">
         <f t="shared" si="0"/>
         <v>1.4092155836074898E-4</v>
       </c>
-      <c r="U4" s="53">
+      <c r="U4" s="50">
         <f t="shared" si="0"/>
         <v>1.2874162652953146E-2</v>
       </c>
-      <c r="V4" s="53">
+      <c r="V4" s="50">
         <f t="shared" si="0"/>
         <v>9.8983108445741333E-3</v>
       </c>
-      <c r="W4" s="53">
+      <c r="W4" s="50">
         <f t="shared" si="0"/>
         <v>1.0817363849499382E-2</v>
       </c>
-      <c r="X4" s="53">
+      <c r="X4" s="50">
         <f t="shared" si="0"/>
         <v>7.7961432923972281E-3</v>
       </c>
-      <c r="Y4" s="54">
+      <c r="Y4" s="51">
         <f t="shared" si="0"/>
         <v>2.1851617557088653E-2</v>
       </c>
       <c r="AA4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" s="63">
+      <c r="AB4" s="60">
         <f>O4*'R17'!N$24</f>
         <v>102.54092334959473</v>
       </c>
-      <c r="AC4" s="63">
+      <c r="AC4" s="60">
         <f>P4*'R17'!O$24</f>
         <v>59.399808617589187</v>
       </c>
-      <c r="AD4" s="63">
+      <c r="AD4" s="60">
         <f>Q4*'R17'!P$24</f>
         <v>51.574502859013698</v>
       </c>
-      <c r="AE4" s="63">
+      <c r="AE4" s="60">
         <f>R4*'R17'!Q$24</f>
         <v>246.91789785039927</v>
       </c>
-      <c r="AF4" s="63">
+      <c r="AF4" s="60">
         <f>S4*'R17'!R$24</f>
         <v>366.63989166155545</v>
       </c>
-      <c r="AG4" s="63">
+      <c r="AG4" s="60">
         <f>T4*'R17'!S$24</f>
         <v>5.6035149310321959</v>
       </c>
-      <c r="AH4" s="63">
+      <c r="AH4" s="60">
         <f>U4*'R17'!T$24</f>
         <v>556.36923516670311</v>
       </c>
-      <c r="AI4" s="63">
+      <c r="AI4" s="60">
         <f>V4*'R17'!U$24</f>
         <v>180.66051618852265</v>
       </c>
-      <c r="AJ4" s="63">
+      <c r="AJ4" s="60">
         <f>W4*'R17'!V$24</f>
         <v>1717.7207377805842</v>
       </c>
-      <c r="AK4" s="63">
+      <c r="AK4" s="60">
         <f>X4*'R17'!W$24</f>
         <v>438.87430807301371</v>
       </c>
-      <c r="AL4" s="63">
+      <c r="AL4" s="60">
         <f>Y4*'R17'!X$24</f>
         <v>65.255093832988194</v>
       </c>
@@ -14989,130 +14989,130 @@
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="58">
         <v>1.43004</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="58">
         <v>0.80056099999999997</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="58">
         <v>0.225663</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="58">
         <v>4.6496900000000001E-2</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="58">
         <v>0.82893499999999998</v>
       </c>
-      <c r="G5" s="61">
+      <c r="G5" s="58">
         <v>3.8958599999999999</v>
       </c>
-      <c r="H5" s="61">
+      <c r="H5" s="58">
         <v>0.174868</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="58">
         <v>2.5073999999999999E-2</v>
       </c>
-      <c r="J5" s="61">
+      <c r="J5" s="58">
         <v>0.157942</v>
       </c>
-      <c r="K5" s="61">
+      <c r="K5" s="58">
         <v>0.36366900000000002</v>
       </c>
-      <c r="L5" s="61">
+      <c r="L5" s="58">
         <v>2.82261E-2</v>
       </c>
       <c r="N5" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="55">
+      <c r="O5" s="52">
         <f t="shared" ref="O5:O29" si="1">B5/SUM(B$4:B$29)</f>
         <v>7.4968760408390548E-3</v>
       </c>
-      <c r="P5" s="56">
+      <c r="P5" s="53">
         <f t="shared" si="0"/>
         <v>1.701229158547184E-2</v>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="53">
         <f t="shared" si="0"/>
         <v>1.4928646523403725E-3</v>
       </c>
-      <c r="R5" s="56">
+      <c r="R5" s="53">
         <f t="shared" si="0"/>
         <v>3.5823000912268504E-3</v>
       </c>
-      <c r="S5" s="56">
+      <c r="S5" s="53">
         <f t="shared" si="0"/>
         <v>0.10483053664799608</v>
       </c>
-      <c r="T5" s="56">
+      <c r="T5" s="53">
         <f t="shared" si="0"/>
         <v>9.2684586861887033E-2</v>
       </c>
-      <c r="U5" s="56">
+      <c r="U5" s="53">
         <f t="shared" si="0"/>
         <v>9.4788702334544991E-3</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="53">
         <f t="shared" si="0"/>
         <v>3.0955523834551293E-3</v>
       </c>
-      <c r="W5" s="56">
+      <c r="W5" s="53">
         <f t="shared" si="0"/>
         <v>3.082545184288155E-3</v>
       </c>
-      <c r="X5" s="56">
+      <c r="X5" s="53">
         <f t="shared" si="0"/>
         <v>1.1468483828049769E-2</v>
       </c>
-      <c r="Y5" s="57">
+      <c r="Y5" s="54">
         <f t="shared" si="0"/>
         <v>1.8105351072993704E-3</v>
       </c>
       <c r="AA5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AB5" s="63">
+      <c r="AB5" s="60">
         <f>O5*'R17'!N$24</f>
         <v>266.1227408089697</v>
       </c>
-      <c r="AC5" s="63">
+      <c r="AC5" s="60">
         <f>P5*'R17'!O$24</f>
         <v>993.16360912492166</v>
       </c>
-      <c r="AD5" s="63">
+      <c r="AD5" s="60">
         <f>Q5*'R17'!P$24</f>
         <v>75.381537097773275</v>
       </c>
-      <c r="AE5" s="63">
+      <c r="AE5" s="60">
         <f>R5*'R17'!Q$24</f>
         <v>60.54665255726016</v>
       </c>
-      <c r="AF5" s="63">
+      <c r="AF5" s="60">
         <f>S5*'R17'!R$24</f>
         <v>1464.5225016840211</v>
       </c>
-      <c r="AG5" s="63">
+      <c r="AG5" s="60">
         <f>T5*'R17'!S$24</f>
         <v>3685.4507741648149</v>
       </c>
-      <c r="AH5" s="63">
+      <c r="AH5" s="60">
         <f>U5*'R17'!T$24</f>
         <v>409.63843041254307</v>
       </c>
-      <c r="AI5" s="63">
+      <c r="AI5" s="60">
         <f>V5*'R17'!U$24</f>
         <v>56.49894211901529</v>
       </c>
-      <c r="AJ5" s="63">
+      <c r="AJ5" s="60">
         <f>W5*'R17'!V$24</f>
         <v>489.48633529068934</v>
       </c>
-      <c r="AK5" s="63">
+      <c r="AK5" s="60">
         <f>X5*'R17'!W$24</f>
         <v>645.60420658125554</v>
       </c>
-      <c r="AL5" s="63">
+      <c r="AL5" s="60">
         <f>Y5*'R17'!X$24</f>
         <v>5.4067685381219324</v>
       </c>
@@ -15121,130 +15121,130 @@
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="58">
         <v>1.15656</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="58">
         <v>0.26385700000000001</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="58">
         <v>0.25412000000000001</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="58">
         <v>4.9875900000000001E-2</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="58">
         <v>0.43570599999999998</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="58">
         <v>1.1526700000000001</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="58">
         <v>5.6999500000000002E-2</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="58">
         <v>0.14186499999999999</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="58">
         <v>0.189527</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="58">
         <v>0.391953</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="58">
         <v>0.23092799999999999</v>
       </c>
       <c r="N6" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="52">
         <f t="shared" si="1"/>
         <v>6.063177920752439E-3</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="53">
         <f t="shared" si="0"/>
         <v>5.6070833089144284E-3</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="53">
         <f t="shared" si="0"/>
         <v>1.6811208104684217E-3</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="53">
         <f t="shared" si="0"/>
         <v>3.8426312532668038E-3</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="53">
         <f t="shared" si="0"/>
         <v>5.5101176570843041E-2</v>
       </c>
-      <c r="T6" s="56">
+      <c r="T6" s="53">
         <f t="shared" si="0"/>
         <v>2.742263395966265E-2</v>
       </c>
-      <c r="U6" s="56">
+      <c r="U6" s="53">
         <f t="shared" si="0"/>
         <v>3.0897068867476599E-3</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="53">
         <f t="shared" si="0"/>
         <v>1.7514179583587058E-2</v>
       </c>
-      <c r="W6" s="56">
+      <c r="W6" s="53">
         <f t="shared" si="0"/>
         <v>3.6989878635358621E-3</v>
       </c>
-      <c r="X6" s="56">
+      <c r="X6" s="53">
         <f t="shared" si="0"/>
         <v>1.2360433916158899E-2</v>
       </c>
-      <c r="Y6" s="57">
+      <c r="Y6" s="54">
         <f t="shared" si="0"/>
         <v>1.4812646850199956E-2</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AB6" s="63">
+      <c r="AB6" s="60">
         <f>O6*'R17'!N$24</f>
         <v>215.22958596264581</v>
       </c>
-      <c r="AC6" s="63">
+      <c r="AC6" s="60">
         <f>P6*'R17'!O$24</f>
         <v>327.33691800234396</v>
       </c>
-      <c r="AD6" s="63">
+      <c r="AD6" s="60">
         <f>Q6*'R17'!P$24</f>
         <v>84.887448129671881</v>
       </c>
-      <c r="AE6" s="63">
+      <c r="AE6" s="60">
         <f>R6*'R17'!Q$24</f>
         <v>64.9466693108713</v>
       </c>
-      <c r="AF6" s="63">
+      <c r="AF6" s="60">
         <f>S6*'R17'!R$24</f>
         <v>769.78441146620435</v>
       </c>
-      <c r="AG6" s="63">
+      <c r="AG6" s="60">
         <f>T6*'R17'!S$24</f>
         <v>1090.4161196389391</v>
       </c>
-      <c r="AH6" s="63">
+      <c r="AH6" s="60">
         <f>U6*'R17'!T$24</f>
         <v>133.52463409142754</v>
       </c>
-      <c r="AI6" s="63">
+      <c r="AI6" s="60">
         <f>V6*'R17'!U$24</f>
         <v>319.66269537026812</v>
       </c>
-      <c r="AJ6" s="63">
+      <c r="AJ6" s="60">
         <f>W6*'R17'!V$24</f>
         <v>587.37306523051802</v>
       </c>
-      <c r="AK6" s="63">
+      <c r="AK6" s="60">
         <f>X6*'R17'!W$24</f>
         <v>695.81544091507067</v>
       </c>
-      <c r="AL6" s="63">
+      <c r="AL6" s="60">
         <f>Y6*'R17'!X$24</f>
         <v>44.234741780530129</v>
       </c>
@@ -15253,130 +15253,130 @@
       <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="58">
         <v>4.7415700000000003</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="58">
         <v>1.55128</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="58">
         <v>1.24613</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="58">
         <v>0.21010400000000001</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="58">
         <v>0.41816799999999998</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="58">
         <v>0.93914699999999995</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="58">
         <v>1.2804500000000001</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="58">
         <v>0.12207</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="58">
         <v>0.71360299999999999</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="58">
         <v>0.97142700000000004</v>
       </c>
-      <c r="L7" s="61">
+      <c r="L7" s="58">
         <v>1.31307</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="52">
         <f t="shared" si="1"/>
         <v>2.4857320444855557E-2</v>
       </c>
-      <c r="P7" s="56">
+      <c r="P7" s="53">
         <f t="shared" si="0"/>
         <v>3.2965417614286431E-2</v>
       </c>
-      <c r="Q7" s="56">
+      <c r="Q7" s="53">
         <f t="shared" si="0"/>
         <v>8.243723735042556E-3</v>
       </c>
-      <c r="R7" s="56">
+      <c r="R7" s="53">
         <f t="shared" si="0"/>
         <v>1.6187220618301999E-2</v>
       </c>
-      <c r="S7" s="56">
+      <c r="S7" s="53">
         <f t="shared" si="0"/>
         <v>5.2883248806021244E-2</v>
       </c>
-      <c r="T7" s="56">
+      <c r="T7" s="53">
         <f t="shared" si="0"/>
         <v>2.2342807928822036E-2</v>
       </c>
-      <c r="U7" s="56">
+      <c r="U7" s="53">
         <f t="shared" si="0"/>
         <v>6.940789275583191E-2</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="53">
         <f t="shared" si="0"/>
         <v>1.5070354927349752E-2</v>
       </c>
-      <c r="W7" s="56">
+      <c r="W7" s="53">
         <f t="shared" si="0"/>
         <v>1.3927349857185424E-2</v>
       </c>
-      <c r="X7" s="56">
+      <c r="X7" s="53">
         <f t="shared" si="0"/>
         <v>3.0634436368320923E-2</v>
       </c>
-      <c r="Y7" s="57">
+      <c r="Y7" s="54">
         <f t="shared" si="0"/>
         <v>8.4225569006755596E-2</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AB7" s="63">
+      <c r="AB7" s="60">
         <f>O7*'R17'!N$24</f>
         <v>882.38063560291084</v>
       </c>
-      <c r="AC7" s="63">
+      <c r="AC7" s="60">
         <f>P7*'R17'!O$24</f>
         <v>1924.4940030345081</v>
       </c>
-      <c r="AD7" s="63">
+      <c r="AD7" s="60">
         <f>Q7*'R17'!P$24</f>
         <v>416.26316597602715</v>
       </c>
-      <c r="AE7" s="63">
+      <c r="AE7" s="60">
         <f>R7*'R17'!Q$24</f>
         <v>273.59015093244045</v>
       </c>
-      <c r="AF7" s="63">
+      <c r="AF7" s="60">
         <f>S7*'R17'!R$24</f>
         <v>738.79911631696541</v>
       </c>
-      <c r="AG7" s="63">
+      <c r="AG7" s="60">
         <f>T7*'R17'!S$24</f>
         <v>888.4251585540967</v>
       </c>
-      <c r="AH7" s="63">
+      <c r="AH7" s="60">
         <f>U7*'R17'!T$24</f>
         <v>2999.5283769571379</v>
       </c>
-      <c r="AI7" s="63">
+      <c r="AI7" s="60">
         <f>V7*'R17'!U$24</f>
         <v>275.05886035208573</v>
       </c>
-      <c r="AJ7" s="63">
+      <c r="AJ7" s="60">
         <f>W7*'R17'!V$24</f>
         <v>2211.5644814073635</v>
       </c>
-      <c r="AK7" s="63">
+      <c r="AK7" s="60">
         <f>X7*'R17'!W$24</f>
         <v>1724.5279569790366</v>
       </c>
-      <c r="AL7" s="63">
+      <c r="AL7" s="60">
         <f>Y7*'R17'!X$24</f>
         <v>251.52130702972659</v>
       </c>
@@ -15385,130 +15385,130 @@
       <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="58">
         <v>14.32</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="58">
         <v>7.6149500000000003</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="58">
         <v>13.383599999999999</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="58">
         <v>1.33125</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="58">
         <v>0.62094300000000002</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="58">
         <v>4.6331899999999999</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="58">
         <v>7.1182600000000003</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="58">
         <v>0.30335000000000001</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="58">
         <v>4.3158899999999996</v>
       </c>
-      <c r="K8" s="61">
+      <c r="K8" s="58">
         <v>3.8833799999999998</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="58">
         <v>2.0186199999999999</v>
       </c>
       <c r="N8" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="52">
         <f t="shared" si="1"/>
         <v>7.5071511919117845E-2</v>
       </c>
-      <c r="P8" s="56">
+      <c r="P8" s="53">
         <f t="shared" si="0"/>
         <v>0.16182121013737719</v>
       </c>
-      <c r="Q8" s="56">
+      <c r="Q8" s="53">
         <f t="shared" si="0"/>
         <v>8.8538676526779353E-2</v>
       </c>
-      <c r="R8" s="56">
+      <c r="R8" s="53">
         <f t="shared" si="0"/>
         <v>0.1025646225113017</v>
       </c>
-      <c r="S8" s="56">
+      <c r="S8" s="53">
         <f t="shared" si="0"/>
         <v>7.8527011065785163E-2</v>
       </c>
-      <c r="T8" s="56">
+      <c r="T8" s="53">
         <f t="shared" si="0"/>
         <v>0.11022606074207655</v>
       </c>
-      <c r="U8" s="56">
+      <c r="U8" s="53">
         <f t="shared" si="0"/>
         <v>0.38585140121685974</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="53">
         <f t="shared" si="0"/>
         <v>3.7450578907279E-2</v>
       </c>
-      <c r="W8" s="56">
+      <c r="W8" s="53">
         <f t="shared" si="0"/>
         <v>8.4232983851144111E-2</v>
       </c>
-      <c r="X8" s="56">
+      <c r="X8" s="53">
         <f t="shared" si="0"/>
         <v>0.12246433082878086</v>
       </c>
-      <c r="Y8" s="57">
+      <c r="Y8" s="54">
         <f t="shared" si="0"/>
         <v>0.12948237192869913</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="AB8" s="63">
+      <c r="AB8" s="60">
         <f>O8*'R17'!N$24</f>
         <v>2664.8748625104522</v>
       </c>
-      <c r="AC8" s="63">
+      <c r="AC8" s="60">
         <f>P8*'R17'!O$24</f>
         <v>9446.9893303643621</v>
       </c>
-      <c r="AD8" s="63">
+      <c r="AD8" s="60">
         <f>Q8*'R17'!P$24</f>
         <v>4470.7211191101705</v>
       </c>
-      <c r="AE8" s="63">
+      <c r="AE8" s="60">
         <f>R8*'R17'!Q$24</f>
         <v>1733.5076363553826</v>
       </c>
-      <c r="AF8" s="63">
+      <c r="AF8" s="60">
         <f>S8*'R17'!R$24</f>
         <v>1097.0522366207015</v>
       </c>
-      <c r="AG8" s="63">
+      <c r="AG8" s="60">
         <f>T8*'R17'!S$24</f>
         <v>4382.9587491215489</v>
       </c>
-      <c r="AH8" s="63">
+      <c r="AH8" s="60">
         <f>U8*'R17'!T$24</f>
         <v>16674.936830457198</v>
       </c>
-      <c r="AI8" s="63">
+      <c r="AI8" s="60">
         <f>V8*'R17'!U$24</f>
         <v>683.53490036704522</v>
       </c>
-      <c r="AJ8" s="63">
+      <c r="AJ8" s="60">
         <f>W8*'R17'!V$24</f>
         <v>13375.601041000702</v>
       </c>
-      <c r="AK8" s="63">
+      <c r="AK8" s="60">
         <f>X8*'R17'!W$24</f>
         <v>6893.979040703266</v>
       </c>
-      <c r="AL8" s="63">
+      <c r="AL8" s="60">
         <f>Y8*'R17'!X$24</f>
         <v>386.67088639322094</v>
       </c>
@@ -15517,130 +15517,130 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="61">
+      <c r="B9" s="58">
         <v>2.6378300000000001</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="58">
         <v>3.0233300000000001</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="58">
         <v>4.9371600000000004</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="58">
         <v>0.81547599999999998</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="58">
         <v>0.16580600000000001</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="58">
         <v>2.2733599999999998</v>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="58">
         <v>0.92512799999999995</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="58">
         <v>2.3819400000000002</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="58">
         <v>5.7646100000000002</v>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="58">
         <v>1.2334400000000001</v>
       </c>
-      <c r="L9" s="61">
+      <c r="L9" s="58">
         <v>0.13033700000000001</v>
       </c>
       <c r="N9" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="52">
         <f t="shared" si="1"/>
         <v>1.3828623343966942E-2</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="53">
         <f t="shared" si="0"/>
         <v>6.424716107717536E-2</v>
       </c>
-      <c r="Q9" s="56">
+      <c r="Q9" s="53">
         <f t="shared" si="0"/>
         <v>3.2661586733087805E-2</v>
       </c>
-      <c r="R9" s="56">
+      <c r="R9" s="53">
         <f t="shared" si="0"/>
         <v>6.2827408906686394E-2</v>
       </c>
-      <c r="S9" s="56">
+      <c r="S9" s="53">
         <f t="shared" si="0"/>
         <v>2.0968510147909833E-2</v>
       </c>
-      <c r="T9" s="56">
+      <c r="T9" s="53">
         <f t="shared" si="0"/>
         <v>5.4084446666035096E-2</v>
       </c>
-      <c r="U9" s="56">
+      <c r="U9" s="53">
         <f t="shared" si="0"/>
         <v>5.0147358357934518E-2</v>
       </c>
-      <c r="V9" s="56">
+      <c r="V9" s="53">
         <f t="shared" si="0"/>
         <v>0.2940663653285121</v>
       </c>
-      <c r="W9" s="56">
+      <c r="W9" s="53">
         <f t="shared" si="0"/>
         <v>0.11250757110077966</v>
       </c>
-      <c r="X9" s="56">
+      <c r="X9" s="53">
         <f t="shared" si="0"/>
         <v>3.8897147386413762E-2</v>
       </c>
-      <c r="Y9" s="57">
+      <c r="Y9" s="54">
         <f t="shared" si="0"/>
         <v>8.3603372155585803E-3</v>
       </c>
       <c r="AA9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AB9" s="63">
+      <c r="AB9" s="60">
         <f>O9*'R17'!N$24</f>
         <v>490.88595381116932</v>
       </c>
-      <c r="AC9" s="63">
+      <c r="AC9" s="60">
         <f>P9*'R17'!O$24</f>
         <v>3750.6964920545092</v>
       </c>
-      <c r="AD9" s="63">
+      <c r="AD9" s="60">
         <f>Q9*'R17'!P$24</f>
         <v>1649.2323052411884</v>
       </c>
-      <c r="AE9" s="63">
+      <c r="AE9" s="60">
         <f>R9*'R17'!Q$24</f>
         <v>1061.8845996353366</v>
       </c>
-      <c r="AF9" s="63">
+      <c r="AF9" s="60">
         <f>S9*'R17'!R$24</f>
         <v>292.93806862325852</v>
       </c>
-      <c r="AG9" s="63">
+      <c r="AG9" s="60">
         <f>T9*'R17'!S$24</f>
         <v>2150.5794284074177</v>
       </c>
-      <c r="AH9" s="63">
+      <c r="AH9" s="60">
         <f>U9*'R17'!T$24</f>
         <v>2167.1659872057503</v>
       </c>
-      <c r="AI9" s="63">
+      <c r="AI9" s="60">
         <f>V9*'R17'!U$24</f>
         <v>5367.1967053907356</v>
       </c>
-      <c r="AJ9" s="63">
+      <c r="AJ9" s="60">
         <f>W9*'R17'!V$24</f>
         <v>17865.405169492984</v>
       </c>
-      <c r="AK9" s="63">
+      <c r="AK9" s="60">
         <f>X9*'R17'!W$24</f>
         <v>2189.667121931162</v>
       </c>
-      <c r="AL9" s="63">
+      <c r="AL9" s="60">
         <f>Y9*'R17'!X$24</f>
         <v>24.96632517256009</v>
       </c>
@@ -15649,130 +15649,130 @@
       <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="61">
+      <c r="B10" s="58">
         <v>2.1160600000000001</v>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="58">
         <v>0.809639</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="58">
         <v>1.9005099999999999</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="58">
         <v>0.24787100000000001</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="58">
         <v>6.3712400000000002E-2</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="58">
         <v>0.46068900000000002</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="58">
         <v>0.34102300000000002</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="58">
         <v>0.155088</v>
       </c>
-      <c r="J10" s="61">
+      <c r="J10" s="58">
         <v>0.15845000000000001</v>
       </c>
-      <c r="K10" s="61">
+      <c r="K10" s="58">
         <v>0.46244299999999999</v>
       </c>
-      <c r="L10" s="61">
+      <c r="L10" s="58">
         <v>0.35319699999999998</v>
       </c>
       <c r="N10" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="55">
+      <c r="O10" s="52">
         <f t="shared" si="1"/>
         <v>1.1093283764774337E-2</v>
       </c>
-      <c r="P10" s="56">
+      <c r="P10" s="53">
         <f t="shared" si="0"/>
         <v>1.7205203284908755E-2</v>
       </c>
-      <c r="Q10" s="56">
+      <c r="Q10" s="53">
         <f t="shared" si="0"/>
         <v>1.2572748746668267E-2</v>
       </c>
-      <c r="R10" s="56">
+      <c r="R10" s="53">
         <f t="shared" si="0"/>
         <v>1.9096935621783186E-2</v>
       </c>
-      <c r="S10" s="56">
+      <c r="S10" s="53">
         <f t="shared" si="0"/>
         <v>8.0573327017580219E-3</v>
       </c>
-      <c r="T10" s="56">
+      <c r="T10" s="53">
         <f t="shared" si="0"/>
         <v>1.0960036971763841E-2</v>
       </c>
-      <c r="U10" s="56">
+      <c r="U10" s="53">
         <f t="shared" si="0"/>
         <v>1.8485444813364102E-2</v>
       </c>
-      <c r="V10" s="56">
+      <c r="V10" s="53">
         <f t="shared" si="0"/>
         <v>1.9146647046553767E-2</v>
       </c>
-      <c r="W10" s="56">
+      <c r="W10" s="53">
         <f t="shared" si="0"/>
         <v>3.0924597918885297E-3</v>
       </c>
-      <c r="X10" s="56">
+      <c r="X10" s="53">
         <f t="shared" si="0"/>
         <v>1.4583371326384209E-2</v>
       </c>
-      <c r="Y10" s="57">
+      <c r="Y10" s="54">
         <f t="shared" si="0"/>
         <v>2.2655470231197922E-2</v>
       </c>
       <c r="AA10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AB10" s="63">
+      <c r="AB10" s="60">
         <f>O10*'R17'!N$24</f>
         <v>393.78736742764431</v>
       </c>
-      <c r="AC10" s="63">
+      <c r="AC10" s="60">
         <f>P10*'R17'!O$24</f>
         <v>1004.4256356833429</v>
       </c>
-      <c r="AD10" s="63">
+      <c r="AD10" s="60">
         <f>Q10*'R17'!P$24</f>
         <v>634.85535984937314</v>
       </c>
-      <c r="AE10" s="63">
+      <c r="AE10" s="60">
         <f>R10*'R17'!Q$24</f>
         <v>322.76903010782729</v>
       </c>
-      <c r="AF10" s="63">
+      <c r="AF10" s="60">
         <f>S10*'R17'!R$24</f>
         <v>112.5640049416336</v>
       </c>
-      <c r="AG10" s="63">
+      <c r="AG10" s="60">
         <f>T10*'R17'!S$24</f>
         <v>435.80791704507203</v>
       </c>
-      <c r="AH10" s="63">
+      <c r="AH10" s="60">
         <f>U10*'R17'!T$24</f>
         <v>798.86615306732324</v>
       </c>
-      <c r="AI10" s="63">
+      <c r="AI10" s="60">
         <f>V10*'R17'!U$24</f>
         <v>349.45792196513696</v>
       </c>
-      <c r="AJ10" s="63">
+      <c r="AJ10" s="60">
         <f>W10*'R17'!V$24</f>
         <v>491.06070473217846</v>
       </c>
-      <c r="AK10" s="63">
+      <c r="AK10" s="60">
         <f>X10*'R17'!W$24</f>
         <v>820.95297125698244</v>
       </c>
-      <c r="AL10" s="63">
+      <c r="AL10" s="60">
         <f>Y10*'R17'!X$24</f>
         <v>67.655624665081334</v>
       </c>
@@ -15781,130 +15781,130 @@
       <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="61">
+      <c r="B11" s="58">
         <v>6.30131</v>
       </c>
-      <c r="C11" s="61">
+      <c r="C11" s="58">
         <v>1.57498</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="58">
         <v>5.7594000000000003</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="58">
         <v>0.42775999999999997</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="58">
         <v>5.4081400000000002E-2</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="58">
         <v>0.56195300000000004</v>
       </c>
-      <c r="H11" s="61">
+      <c r="H11" s="58">
         <v>0.33743800000000002</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="58">
         <v>0.13817299999999999</v>
       </c>
-      <c r="J11" s="61">
+      <c r="J11" s="58">
         <v>0.79379999999999995</v>
       </c>
-      <c r="K11" s="61">
+      <c r="K11" s="58">
         <v>0.871888</v>
       </c>
-      <c r="L11" s="61">
+      <c r="L11" s="58">
         <v>0.28423500000000002</v>
       </c>
       <c r="N11" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="55">
+      <c r="O11" s="52">
         <f t="shared" si="1"/>
         <v>3.3034138880660362E-2</v>
       </c>
-      <c r="P11" s="56">
+      <c r="P11" s="53">
         <f t="shared" si="0"/>
         <v>3.346905357778663E-2</v>
       </c>
-      <c r="Q11" s="56">
+      <c r="Q11" s="53">
         <f t="shared" si="0"/>
         <v>3.810108293645454E-2</v>
       </c>
-      <c r="R11" s="56">
+      <c r="R11" s="53">
         <f t="shared" si="0"/>
         <v>3.2956276375913175E-2</v>
       </c>
-      <c r="S11" s="56">
+      <c r="S11" s="53">
         <f t="shared" si="0"/>
         <v>6.839356746518044E-3</v>
       </c>
-      <c r="T11" s="56">
+      <c r="T11" s="53">
         <f t="shared" si="0"/>
         <v>1.3369161530649975E-2</v>
       </c>
-      <c r="U11" s="56">
+      <c r="U11" s="53">
         <f t="shared" si="0"/>
         <v>1.8291116807171236E-2</v>
       </c>
-      <c r="V11" s="56">
+      <c r="V11" s="53">
         <f t="shared" si="0"/>
         <v>1.7058377581524512E-2</v>
       </c>
-      <c r="W11" s="56">
+      <c r="W11" s="53">
         <f t="shared" si="0"/>
         <v>1.5492550222790247E-2</v>
       </c>
-      <c r="X11" s="56">
+      <c r="X11" s="53">
         <f t="shared" si="0"/>
         <v>2.7495424212321248E-2</v>
       </c>
-      <c r="Y11" s="57">
+      <c r="Y11" s="54">
         <f t="shared" si="0"/>
         <v>1.8231971339407023E-2</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB11" s="63">
+      <c r="AB11" s="60">
         <f>O11*'R17'!N$24</f>
         <v>1172.6398477573837</v>
       </c>
-      <c r="AC11" s="63">
+      <c r="AC11" s="60">
         <f>P11*'R17'!O$24</f>
         <v>1953.8958569048073</v>
       </c>
-      <c r="AD11" s="63">
+      <c r="AD11" s="60">
         <f>Q11*'R17'!P$24</f>
         <v>1923.8972483788455</v>
       </c>
-      <c r="AE11" s="63">
+      <c r="AE11" s="60">
         <f>R11*'R17'!Q$24</f>
         <v>557.0142546684533</v>
       </c>
-      <c r="AF11" s="63">
+      <c r="AF11" s="60">
         <f>S11*'R17'!R$24</f>
         <v>95.548417213140013</v>
       </c>
-      <c r="AG11" s="63">
+      <c r="AG11" s="60">
         <f>T11*'R17'!S$24</f>
         <v>531.60280885202246</v>
       </c>
-      <c r="AH11" s="63">
+      <c r="AH11" s="60">
         <f>U11*'R17'!T$24</f>
         <v>790.4680826769204</v>
       </c>
-      <c r="AI11" s="63">
+      <c r="AI11" s="60">
         <f>V11*'R17'!U$24</f>
         <v>311.34355624992821</v>
       </c>
-      <c r="AJ11" s="63">
+      <c r="AJ11" s="60">
         <f>W11*'R17'!V$24</f>
         <v>2460.1072099489002</v>
       </c>
-      <c r="AK11" s="63">
+      <c r="AK11" s="60">
         <f>X11*'R17'!W$24</f>
         <v>1547.8211243403141</v>
       </c>
-      <c r="AL11" s="63">
+      <c r="AL11" s="60">
         <f>Y11*'R17'!X$24</f>
         <v>54.445809213213572</v>
       </c>
@@ -15913,130 +15913,130 @@
       <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="58">
         <v>0.48960199999999998</v>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="58">
         <v>0.245588</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="58">
         <v>0.26254499999999997</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="58">
         <v>3.7302500000000002E-2</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="58">
         <v>0.12008199999999999</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="58">
         <v>0.94808800000000004</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="58">
         <v>5.9282500000000002E-2</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="58">
         <v>8.4193799999999999E-2</v>
       </c>
-      <c r="J12" s="61">
+      <c r="J12" s="58">
         <v>0.15659300000000001</v>
       </c>
-      <c r="K12" s="61">
+      <c r="K12" s="58">
         <v>0.19750799999999999</v>
       </c>
-      <c r="L12" s="61">
+      <c r="L12" s="58">
         <v>3.0493300000000001E-2</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
       </c>
-      <c r="O12" s="55">
+      <c r="O12" s="52">
         <f t="shared" si="1"/>
         <v>2.566701283423459E-3</v>
       </c>
-      <c r="P12" s="56">
+      <c r="P12" s="53">
         <f t="shared" si="0"/>
         <v>5.2188586077673771E-3</v>
       </c>
-      <c r="Q12" s="56">
+      <c r="Q12" s="53">
         <f t="shared" si="0"/>
         <v>1.736856064789988E-3</v>
       </c>
-      <c r="R12" s="56">
+      <c r="R12" s="53">
         <f t="shared" si="0"/>
         <v>2.8739281361335827E-3</v>
       </c>
-      <c r="S12" s="56">
+      <c r="S12" s="53">
         <f t="shared" si="0"/>
         <v>1.5186064651347409E-2</v>
       </c>
-      <c r="T12" s="56">
+      <c r="T12" s="53">
         <f t="shared" si="0"/>
         <v>2.2555519086597763E-2</v>
       </c>
-      <c r="U12" s="56">
+      <c r="U12" s="53">
         <f t="shared" si="0"/>
         <v>3.2134588639131595E-3</v>
       </c>
-      <c r="V12" s="56">
+      <c r="V12" s="53">
         <f t="shared" si="0"/>
         <v>1.0394285644976648E-2</v>
       </c>
-      <c r="W12" s="56">
+      <c r="W12" s="53">
         <f t="shared" si="0"/>
         <v>3.0562168267036956E-3</v>
       </c>
-      <c r="X12" s="56">
+      <c r="X12" s="53">
         <f t="shared" si="0"/>
         <v>6.2285135766602419E-3</v>
       </c>
-      <c r="Y12" s="57">
+      <c r="Y12" s="54">
         <f t="shared" si="0"/>
         <v>1.9559623960593879E-3</v>
       </c>
       <c r="AA12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AB12" s="63">
+      <c r="AB12" s="60">
         <f>O12*'R17'!N$24</f>
         <v>91.112294862768309</v>
       </c>
-      <c r="AC12" s="63">
+      <c r="AC12" s="60">
         <f>P12*'R17'!O$24</f>
         <v>304.67267883118382</v>
       </c>
-      <c r="AD12" s="63">
+      <c r="AD12" s="60">
         <f>Q12*'R17'!P$24</f>
         <v>87.701775024416435</v>
       </c>
-      <c r="AE12" s="63">
+      <c r="AE12" s="60">
         <f>R12*'R17'!Q$24</f>
         <v>48.574023365368383</v>
       </c>
-      <c r="AF12" s="63">
+      <c r="AF12" s="60">
         <f>S12*'R17'!R$24</f>
         <v>212.15510389502268</v>
       </c>
-      <c r="AG12" s="63">
+      <c r="AG12" s="60">
         <f>T12*'R17'!S$24</f>
         <v>896.88326931059407</v>
       </c>
-      <c r="AH12" s="63">
+      <c r="AH12" s="60">
         <f>U12*'R17'!T$24</f>
         <v>138.87269398021127</v>
       </c>
-      <c r="AI12" s="63">
+      <c r="AI12" s="60">
         <f>V12*'R17'!U$24</f>
         <v>189.71287520858058</v>
       </c>
-      <c r="AJ12" s="63">
+      <c r="AJ12" s="60">
         <f>W12*'R17'!V$24</f>
         <v>485.30557864390045</v>
       </c>
-      <c r="AK12" s="63">
+      <c r="AK12" s="60">
         <f>X12*'R17'!W$24</f>
         <v>350.62651926188545</v>
       </c>
-      <c r="AL12" s="63">
+      <c r="AL12" s="60">
         <f>Y12*'R17'!X$24</f>
         <v>5.841055443845006</v>
       </c>
@@ -16045,130 +16045,130 @@
       <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="58">
         <v>12.728300000000001</v>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="58">
         <v>4.1257799999999998</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="58">
         <v>16.1462</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="58">
         <v>1.2255</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="58">
         <v>0.23389499999999999</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="58">
         <v>2.3648899999999999</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="58">
         <v>0.78330500000000003</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="58">
         <v>0.60567199999999999</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="58">
         <v>2.8592399999999998</v>
       </c>
-      <c r="K13" s="61">
+      <c r="K13" s="58">
         <v>2.8584700000000001</v>
       </c>
-      <c r="L13" s="61">
+      <c r="L13" s="58">
         <v>0.75378100000000003</v>
       </c>
       <c r="N13" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="55">
+      <c r="O13" s="52">
         <f t="shared" si="1"/>
         <v>6.6727145611739355E-2</v>
       </c>
-      <c r="P13" s="56">
+      <c r="P13" s="53">
         <f t="shared" si="0"/>
         <v>8.7674733564972587E-2</v>
       </c>
-      <c r="Q13" s="56">
+      <c r="Q13" s="53">
         <f t="shared" si="0"/>
         <v>0.10681454757589025</v>
       </c>
-      <c r="R13" s="56">
+      <c r="R13" s="53">
         <f t="shared" si="0"/>
         <v>9.4417235596319427E-2</v>
       </c>
-      <c r="S13" s="56">
+      <c r="S13" s="53">
         <f t="shared" si="0"/>
         <v>2.9579325724312572E-2</v>
       </c>
-      <c r="T13" s="56">
+      <c r="T13" s="53">
         <f t="shared" si="0"/>
         <v>5.6261994174279364E-2</v>
       </c>
-      <c r="U13" s="56">
+      <c r="U13" s="53">
         <f t="shared" si="0"/>
         <v>4.2459720750600893E-2</v>
       </c>
-      <c r="V13" s="56">
+      <c r="V13" s="53">
         <f t="shared" si="0"/>
         <v>7.4774244364362891E-2</v>
       </c>
-      <c r="W13" s="56">
+      <c r="W13" s="53">
         <f t="shared" si="0"/>
         <v>5.5803627234833439E-2</v>
       </c>
-      <c r="X13" s="56">
+      <c r="X13" s="53">
         <f t="shared" si="0"/>
         <v>9.0143281302408021E-2</v>
       </c>
-      <c r="Y13" s="57">
+      <c r="Y13" s="54">
         <f t="shared" si="0"/>
         <v>4.835053244037351E-2</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AB13" s="63">
+      <c r="AB13" s="60">
         <f>O13*'R17'!N$24</f>
         <v>2368.6680665147892</v>
       </c>
-      <c r="AC13" s="63">
+      <c r="AC13" s="60">
         <f>P13*'R17'!O$24</f>
         <v>5118.3789308440209</v>
       </c>
-      <c r="AD13" s="63">
+      <c r="AD13" s="60">
         <f>Q13*'R17'!P$24</f>
         <v>5393.5531047981585</v>
       </c>
-      <c r="AE13" s="63">
+      <c r="AE13" s="60">
         <f>R13*'R17'!Q$24</f>
         <v>1595.8036494674338</v>
       </c>
-      <c r="AF13" s="63">
+      <c r="AF13" s="60">
         <f>S13*'R17'!R$24</f>
         <v>413.2344400120445</v>
       </c>
-      <c r="AG13" s="63">
+      <c r="AG13" s="60">
         <f>T13*'R17'!S$24</f>
         <v>2237.1660381314082</v>
       </c>
-      <c r="AH13" s="63">
+      <c r="AH13" s="60">
         <f>U13*'R17'!T$24</f>
         <v>1834.9373855382178</v>
       </c>
-      <c r="AI13" s="63">
+      <c r="AI13" s="60">
         <f>V13*'R17'!U$24</f>
         <v>1364.7534207190008</v>
       </c>
-      <c r="AJ13" s="63">
+      <c r="AJ13" s="60">
         <f>W13*'R17'!V$24</f>
         <v>8861.2206336284871</v>
       </c>
-      <c r="AK13" s="63">
+      <c r="AK13" s="60">
         <f>X13*'R17'!W$24</f>
         <v>5074.5052682145624</v>
       </c>
-      <c r="AL13" s="63">
+      <c r="AL13" s="60">
         <f>Y13*'R17'!X$24</f>
         <v>144.38832837104979</v>
       </c>
@@ -16177,130 +16177,130 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="58">
         <v>2.72235</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="58">
         <v>1.1433</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="58">
         <v>3.8859300000000001</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="58">
         <v>0.38735799999999998</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="58">
         <v>0.131434</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="58">
         <v>1.5803199999999999</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="58">
         <v>0.258633</v>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="58">
         <v>0.27607599999999999</v>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="58">
         <v>0.75412299999999999</v>
       </c>
-      <c r="K14" s="61">
+      <c r="K14" s="58">
         <v>0.70174999999999998</v>
       </c>
-      <c r="L14" s="61">
+      <c r="L14" s="58">
         <v>0.30401800000000001</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="55">
+      <c r="O14" s="52">
         <f t="shared" si="1"/>
         <v>1.4271713021858271E-2</v>
       </c>
-      <c r="P14" s="56">
+      <c r="P14" s="53">
         <f t="shared" si="0"/>
         <v>2.429565388480073E-2</v>
       </c>
-      <c r="Q14" s="56">
+      <c r="Q14" s="53">
         <f t="shared" si="0"/>
         <v>2.5707216240451573E-2</v>
       </c>
-      <c r="R14" s="56">
+      <c r="R14" s="53">
         <f t="shared" si="0"/>
         <v>2.9843550833226519E-2</v>
       </c>
-      <c r="S14" s="56">
+      <c r="S14" s="53">
         <f t="shared" si="0"/>
         <v>1.6621685359880709E-2</v>
       </c>
-      <c r="T14" s="56">
+      <c r="T14" s="53">
         <f t="shared" si="0"/>
         <v>3.7596655503426023E-2</v>
       </c>
-      <c r="U14" s="56">
+      <c r="U14" s="53">
         <f t="shared" si="0"/>
         <v>1.4019424051793567E-2</v>
       </c>
-      <c r="V14" s="56">
+      <c r="V14" s="53">
         <f t="shared" si="0"/>
         <v>3.4083421863873267E-2</v>
       </c>
-      <c r="W14" s="56">
+      <c r="W14" s="53">
         <f t="shared" si="0"/>
         <v>1.4718176431923973E-2</v>
       </c>
-      <c r="X14" s="56">
+      <c r="X14" s="53">
         <f t="shared" si="0"/>
         <v>2.2130037276572721E-2</v>
       </c>
-      <c r="Y14" s="57">
+      <c r="Y14" s="54">
         <f t="shared" si="0"/>
         <v>1.950093219576704E-2</v>
       </c>
       <c r="AA14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AB14" s="63">
+      <c r="AB14" s="60">
         <f>O14*'R17'!N$24</f>
         <v>506.61467052760668</v>
       </c>
-      <c r="AC14" s="63">
+      <c r="AC14" s="60">
         <f>P14*'R17'!O$24</f>
         <v>1418.3603177178543</v>
       </c>
-      <c r="AD14" s="63">
+      <c r="AD14" s="60">
         <f>Q14*'R17'!P$24</f>
         <v>1298.0744581714775</v>
       </c>
-      <c r="AE14" s="63">
+      <c r="AE14" s="60">
         <f>R14*'R17'!Q$24</f>
         <v>504.40416976777334</v>
       </c>
-      <c r="AF14" s="63">
+      <c r="AF14" s="60">
         <f>S14*'R17'!R$24</f>
         <v>232.2112716755085</v>
       </c>
-      <c r="AG14" s="63">
+      <c r="AG14" s="60">
         <f>T14*'R17'!S$24</f>
         <v>1494.9694207256266</v>
       </c>
-      <c r="AH14" s="63">
+      <c r="AH14" s="60">
         <f>U14*'R17'!T$24</f>
         <v>605.86280035733955</v>
       </c>
-      <c r="AI14" s="63">
+      <c r="AI14" s="60">
         <f>V14*'R17'!U$24</f>
         <v>622.07872475270256</v>
       </c>
-      <c r="AJ14" s="63">
+      <c r="AJ14" s="60">
         <f>W14*'R17'!V$24</f>
         <v>2337.1421384332257</v>
       </c>
-      <c r="AK14" s="63">
+      <c r="AK14" s="60">
         <f>X14*'R17'!W$24</f>
         <v>1245.7832588656061</v>
       </c>
-      <c r="AL14" s="63">
+      <c r="AL14" s="60">
         <f>Y14*'R17'!X$24</f>
         <v>58.235284273163984</v>
       </c>
@@ -16309,130 +16309,130 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="58">
         <v>1.7567900000000001</v>
       </c>
-      <c r="C15" s="61">
+      <c r="C15" s="58">
         <v>0.52473099999999995</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="58">
         <v>2.94767</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="58">
         <v>0.29798799999999998</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="58">
         <v>0.21824499999999999</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G15" s="58">
         <v>0.48184100000000002</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="58">
         <v>0.122627</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="58">
         <v>0.20461599999999999</v>
       </c>
-      <c r="J15" s="61">
+      <c r="J15" s="58">
         <v>0.28245100000000001</v>
       </c>
-      <c r="K15" s="61">
+      <c r="K15" s="58">
         <v>0.52198599999999995</v>
       </c>
-      <c r="L15" s="61">
+      <c r="L15" s="58">
         <v>0.25454100000000002</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
       </c>
-      <c r="O15" s="55">
+      <c r="O15" s="52">
         <f t="shared" si="1"/>
         <v>9.2098380882951834E-3</v>
       </c>
-      <c r="P15" s="56">
+      <c r="P15" s="53">
         <f t="shared" si="0"/>
         <v>1.1150776487908135E-2</v>
       </c>
-      <c r="Q15" s="56">
+      <c r="Q15" s="53">
         <f t="shared" si="0"/>
         <v>1.9500194315258353E-2</v>
       </c>
-      <c r="R15" s="56">
+      <c r="R15" s="53">
         <f t="shared" si="0"/>
         <v>2.2958142146777667E-2</v>
       </c>
-      <c r="S15" s="56">
+      <c r="S15" s="53">
         <f t="shared" si="0"/>
         <v>2.7600162221093214E-2</v>
       </c>
-      <c r="T15" s="56">
+      <c r="T15" s="53">
         <f t="shared" si="0"/>
         <v>1.1463254331038208E-2</v>
       </c>
-      <c r="U15" s="56">
+      <c r="U15" s="53">
         <f t="shared" si="0"/>
         <v>6.6471019289854345E-3</v>
       </c>
-      <c r="V15" s="56">
+      <c r="V15" s="53">
         <f t="shared" si="0"/>
         <v>2.52612086820234E-2</v>
       </c>
-      <c r="W15" s="56">
+      <c r="W15" s="53">
         <f t="shared" si="0"/>
         <v>5.5125803766406254E-3</v>
       </c>
-      <c r="X15" s="56">
+      <c r="X15" s="53">
         <f t="shared" si="0"/>
         <v>1.6461089615745047E-2</v>
       </c>
-      <c r="Y15" s="57">
+      <c r="Y15" s="54">
         <f t="shared" si="0"/>
         <v>1.6327279246764134E-2</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AB15" s="63">
+      <c r="AB15" s="60">
         <f>O15*'R17'!N$24</f>
         <v>326.92915570598717</v>
       </c>
-      <c r="AC15" s="63">
+      <c r="AC15" s="60">
         <f>P15*'R17'!O$24</f>
         <v>650.97317228759493</v>
       </c>
-      <c r="AD15" s="63">
+      <c r="AD15" s="60">
         <f>Q15*'R17'!P$24</f>
         <v>984.65364484648956</v>
       </c>
-      <c r="AE15" s="63">
+      <c r="AE15" s="60">
         <f>R15*'R17'!Q$24</f>
         <v>388.02965148714941</v>
       </c>
-      <c r="AF15" s="63">
+      <c r="AF15" s="60">
         <f>S15*'R17'!R$24</f>
         <v>385.584772485212</v>
       </c>
-      <c r="AG15" s="63">
+      <c r="AG15" s="60">
         <f>T15*'R17'!S$24</f>
         <v>455.81753103919254</v>
       </c>
-      <c r="AH15" s="63">
+      <c r="AH15" s="60">
         <f>U15*'R17'!T$24</f>
         <v>287.26085851155682</v>
       </c>
-      <c r="AI15" s="63">
+      <c r="AI15" s="60">
         <f>V15*'R17'!U$24</f>
         <v>461.05876767266619</v>
       </c>
-      <c r="AJ15" s="63">
+      <c r="AJ15" s="60">
         <f>W15*'R17'!V$24</f>
         <v>875.3587069252668</v>
       </c>
-      <c r="AK15" s="63">
+      <c r="AK15" s="60">
         <f>X15*'R17'!W$24</f>
         <v>926.65681533626241</v>
       </c>
-      <c r="AL15" s="63">
+      <c r="AL15" s="60">
         <f>Y15*'R17'!X$24</f>
         <v>48.757861357470389</v>
       </c>
@@ -16441,130 +16441,130 @@
       <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="61">
+      <c r="B16" s="58">
         <v>1.9782500000000001</v>
       </c>
-      <c r="C16" s="61">
+      <c r="C16" s="58">
         <v>0.93108500000000005</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="58">
         <v>2.5796800000000002</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="58">
         <v>0.174515</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="58">
         <v>0.33087800000000001</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="58">
         <v>1.1966300000000001</v>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="58">
         <v>0.65188599999999997</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="58">
         <v>9.6741499999999994E-2</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J16" s="58">
         <v>0.28279300000000002</v>
       </c>
-      <c r="K16" s="61">
+      <c r="K16" s="58">
         <v>0.49331599999999998</v>
       </c>
-      <c r="L16" s="61">
+      <c r="L16" s="58">
         <v>0.29571500000000001</v>
       </c>
       <c r="N16" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="55">
+      <c r="O16" s="52">
         <f t="shared" si="1"/>
         <v>1.0370825311033161E-2</v>
       </c>
-      <c r="P16" s="56">
+      <c r="P16" s="53">
         <f t="shared" si="0"/>
         <v>1.9785986965214459E-2</v>
       </c>
-      <c r="Q16" s="56">
+      <c r="Q16" s="53">
         <f t="shared" si="0"/>
         <v>1.7065771022938683E-2</v>
       </c>
-      <c r="R16" s="56">
+      <c r="R16" s="53">
         <f t="shared" si="0"/>
         <v>1.344530711553789E-2</v>
       </c>
-      <c r="S16" s="56">
+      <c r="S16" s="53">
         <f t="shared" si="0"/>
         <v>4.184419563055685E-2</v>
       </c>
-      <c r="T16" s="56">
+      <c r="T16" s="53">
         <f t="shared" si="0"/>
         <v>2.8468465801271065E-2</v>
       </c>
-      <c r="U16" s="56">
+      <c r="U16" s="53">
         <f t="shared" si="0"/>
         <v>3.5336040905172582E-2</v>
       </c>
-      <c r="V16" s="56">
+      <c r="V16" s="53">
         <f t="shared" si="0"/>
         <v>1.1943382823004882E-2</v>
       </c>
-      <c r="W16" s="56">
+      <c r="W16" s="53">
         <f t="shared" si="0"/>
         <v>5.5192551715211929E-3</v>
       </c>
-      <c r="X16" s="56">
+      <c r="X16" s="53">
         <f t="shared" si="0"/>
         <v>1.5556966824552544E-2</v>
       </c>
-      <c r="Y16" s="57">
+      <c r="Y16" s="54">
         <f t="shared" si="0"/>
         <v>1.8968344519966745E-2</v>
       </c>
       <c r="AA16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AB16" s="63">
+      <c r="AB16" s="60">
         <f>O16*'R17'!N$24</f>
         <v>368.14166876824731</v>
       </c>
-      <c r="AC16" s="63">
+      <c r="AC16" s="60">
         <f>P16*'R17'!O$24</f>
         <v>1155.0896671235271</v>
       </c>
-      <c r="AD16" s="63">
+      <c r="AD16" s="60">
         <f>Q16*'R17'!P$24</f>
         <v>861.72852271034139</v>
       </c>
-      <c r="AE16" s="63">
+      <c r="AE16" s="60">
         <f>R16*'R17'!Q$24</f>
         <v>227.24738791253301</v>
       </c>
-      <c r="AF16" s="63">
+      <c r="AF16" s="60">
         <f>S16*'R17'!R$24</f>
         <v>584.57934133822982</v>
       </c>
-      <c r="AG16" s="63">
+      <c r="AG16" s="60">
         <f>T16*'R17'!S$24</f>
         <v>1132.0019096910162</v>
       </c>
-      <c r="AH16" s="63">
+      <c r="AH16" s="60">
         <f>U16*'R17'!T$24</f>
         <v>1527.0807571877704</v>
       </c>
-      <c r="AI16" s="63">
+      <c r="AI16" s="60">
         <f>V16*'R17'!U$24</f>
         <v>217.98645644917914</v>
       </c>
-      <c r="AJ16" s="63">
+      <c r="AJ16" s="60">
         <f>W16*'R17'!V$24</f>
         <v>876.4186170610725</v>
       </c>
-      <c r="AK16" s="63">
+      <c r="AK16" s="60">
         <f>X16*'R17'!W$24</f>
         <v>875.76033363811223</v>
       </c>
-      <c r="AL16" s="63">
+      <c r="AL16" s="60">
         <f>Y16*'R17'!X$24</f>
         <v>56.644827243251008</v>
       </c>
@@ -16573,130 +16573,130 @@
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="61">
+      <c r="B17" s="58">
         <v>36.223599999999998</v>
       </c>
-      <c r="C17" s="61">
+      <c r="C17" s="58">
         <v>5.2904099999999996</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="58">
         <v>38.423099999999998</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="58">
         <v>3.2237100000000001</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="58">
         <v>0.479852</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="58">
         <v>4.4307100000000004</v>
       </c>
-      <c r="H17" s="61">
+      <c r="H17" s="58">
         <v>0.92022700000000002</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="58">
         <v>1.2396499999999999</v>
       </c>
-      <c r="J17" s="61">
+      <c r="J17" s="58">
         <v>4.1748700000000003</v>
       </c>
-      <c r="K17" s="61">
+      <c r="K17" s="58">
         <v>6.6887600000000003</v>
       </c>
-      <c r="L17" s="61">
+      <c r="L17" s="58">
         <v>1.2577799999999999</v>
       </c>
       <c r="N17" t="s">
         <v>32</v>
       </c>
-      <c r="O17" s="55">
+      <c r="O17" s="52">
         <f t="shared" si="1"/>
         <v>0.18989947061126791</v>
       </c>
-      <c r="P17" s="56">
+      <c r="P17" s="53">
         <f t="shared" si="0"/>
         <v>0.11242365981692348</v>
       </c>
-      <c r="Q17" s="56">
+      <c r="Q17" s="53">
         <f t="shared" si="0"/>
         <v>0.25418649855465608</v>
       </c>
-      <c r="R17" s="56">
+      <c r="R17" s="53">
         <f t="shared" si="0"/>
         <v>0.2483670229002129</v>
       </c>
-      <c r="S17" s="56">
+      <c r="S17" s="53">
         <f t="shared" si="0"/>
         <v>6.0684061683502578E-2</v>
       </c>
-      <c r="T17" s="56">
+      <c r="T17" s="53">
         <f t="shared" si="0"/>
         <v>0.10540895356990024</v>
       </c>
-      <c r="U17" s="56">
+      <c r="U17" s="53">
         <f t="shared" si="0"/>
         <v>4.9881695440681738E-2</v>
       </c>
-      <c r="V17" s="56">
+      <c r="V17" s="53">
         <f t="shared" si="0"/>
         <v>0.15304305304898105</v>
       </c>
-      <c r="W17" s="56">
+      <c r="W17" s="53">
         <f t="shared" si="0"/>
         <v>8.1480704394835388E-2</v>
       </c>
-      <c r="X17" s="56">
+      <c r="X17" s="53">
         <f t="shared" si="0"/>
         <v>0.21093339242472184</v>
       </c>
-      <c r="Y17" s="57">
+      <c r="Y17" s="54">
         <f t="shared" si="0"/>
         <v>8.0679046955087735E-2</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AB17" s="63">
+      <c r="AB17" s="60">
         <f>O17*'R17'!N$24</f>
         <v>6741.0168344716194</v>
       </c>
-      <c r="AC17" s="63">
+      <c r="AC17" s="60">
         <f>P17*'R17'!O$24</f>
         <v>6563.2009170451438</v>
       </c>
-      <c r="AD17" s="63">
+      <c r="AD17" s="60">
         <f>Q17*'R17'!P$24</f>
         <v>12835.034268185091</v>
       </c>
-      <c r="AE17" s="63">
+      <c r="AE17" s="60">
         <f>R17*'R17'!Q$24</f>
         <v>4197.8034947569658</v>
       </c>
-      <c r="AF17" s="63">
+      <c r="AF17" s="60">
         <f>S17*'R17'!R$24</f>
         <v>847.77944166681448</v>
       </c>
-      <c r="AG17" s="63">
+      <c r="AG17" s="60">
         <f>T17*'R17'!S$24</f>
         <v>4191.414373103702</v>
       </c>
-      <c r="AH17" s="63">
+      <c r="AH17" s="60">
         <f>U17*'R17'!T$24</f>
         <v>2155.6851105018832</v>
       </c>
-      <c r="AI17" s="63">
+      <c r="AI17" s="60">
         <f>V17*'R17'!U$24</f>
         <v>2793.2884102192429</v>
       </c>
-      <c r="AJ17" s="63">
+      <c r="AJ17" s="60">
         <f>W17*'R17'!V$24</f>
         <v>12938.558563365288</v>
       </c>
-      <c r="AK17" s="63">
+      <c r="AK17" s="60">
         <f>X17*'R17'!W$24</f>
         <v>11874.236167538169</v>
       </c>
-      <c r="AL17" s="63">
+      <c r="AL17" s="60">
         <f>Y17*'R17'!X$24</f>
         <v>240.93039179621002</v>
       </c>
@@ -16705,130 +16705,130 @@
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="61">
+      <c r="B18" s="58">
         <v>11.5685</v>
       </c>
-      <c r="C18" s="61">
+      <c r="C18" s="58">
         <v>2.7755399999999999</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="58">
         <v>10.9419</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="58">
         <v>0.90874900000000003</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="58">
         <v>0.257739</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="58">
         <v>1.9313400000000001</v>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="58">
         <v>0.68861700000000003</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="58">
         <v>0.17138500000000001</v>
       </c>
-      <c r="J18" s="61">
+      <c r="J18" s="58">
         <v>2.48509</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="58">
         <v>1.21591</v>
       </c>
-      <c r="L18" s="61">
+      <c r="L18" s="58">
         <v>0.50403200000000004</v>
       </c>
       <c r="N18" t="s">
         <v>33</v>
       </c>
-      <c r="O18" s="55">
+      <c r="O18" s="52">
         <f t="shared" si="1"/>
         <v>6.0646982237172818E-2</v>
       </c>
-      <c r="P18" s="56">
+      <c r="P18" s="53">
         <f t="shared" si="0"/>
         <v>5.8981508950773913E-2</v>
       </c>
-      <c r="Q18" s="56">
+      <c r="Q18" s="53">
         <f t="shared" si="0"/>
         <v>7.2385706737228175E-2</v>
       </c>
-      <c r="R18" s="56">
+      <c r="R18" s="53">
         <f t="shared" si="0"/>
         <v>7.0013519731472615E-2</v>
       </c>
-      <c r="S18" s="56">
+      <c r="S18" s="53">
         <f t="shared" si="0"/>
         <v>3.2594736240016235E-2</v>
       </c>
-      <c r="T18" s="56">
+      <c r="T18" s="53">
         <f t="shared" si="0"/>
         <v>4.5947608484349256E-2</v>
       </c>
-      <c r="U18" s="56">
+      <c r="U18" s="53">
         <f t="shared" si="0"/>
         <v>3.7327076329292594E-2</v>
       </c>
-      <c r="V18" s="56">
+      <c r="V18" s="53">
         <f t="shared" si="0"/>
         <v>2.1158620293469627E-2</v>
       </c>
-      <c r="W18" s="56">
+      <c r="W18" s="53">
         <f t="shared" si="0"/>
         <v>4.850136260160471E-2</v>
       </c>
-      <c r="X18" s="56">
+      <c r="X18" s="53">
         <f t="shared" si="0"/>
         <v>3.8344330067627413E-2</v>
       </c>
-      <c r="Y18" s="57">
+      <c r="Y18" s="54">
         <f t="shared" si="0"/>
         <v>3.2330631266888316E-2</v>
       </c>
       <c r="AA18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AB18" s="63">
+      <c r="AB18" s="60">
         <f>O18*'R17'!N$24</f>
         <v>2152.8355340050393</v>
       </c>
-      <c r="AC18" s="63">
+      <c r="AC18" s="60">
         <f>P18*'R17'!O$24</f>
         <v>3443.2920460409455</v>
       </c>
-      <c r="AD18" s="63">
+      <c r="AD18" s="60">
         <f>Q18*'R17'!P$24</f>
         <v>3655.0840889739366</v>
       </c>
-      <c r="AE18" s="63">
+      <c r="AE18" s="60">
         <f>R18*'R17'!Q$24</f>
         <v>1183.3414693185484</v>
       </c>
-      <c r="AF18" s="63">
+      <c r="AF18" s="60">
         <f>S18*'R17'!R$24</f>
         <v>455.36087276027422</v>
       </c>
-      <c r="AG18" s="63">
+      <c r="AG18" s="60">
         <f>T18*'R17'!S$24</f>
         <v>1827.0313866965118</v>
       </c>
-      <c r="AH18" s="63">
+      <c r="AH18" s="60">
         <f>U18*'R17'!T$24</f>
         <v>1613.1252546800683</v>
       </c>
-      <c r="AI18" s="63">
+      <c r="AI18" s="60">
         <f>V18*'R17'!U$24</f>
         <v>386.17975572574926</v>
       </c>
-      <c r="AJ18" s="63">
+      <c r="AJ18" s="60">
         <f>W18*'R17'!V$24</f>
         <v>7701.6727467522205</v>
       </c>
-      <c r="AK18" s="63">
+      <c r="AK18" s="60">
         <f>X18*'R17'!W$24</f>
         <v>2158.5469501778111</v>
       </c>
-      <c r="AL18" s="63">
+      <c r="AL18" s="60">
         <f>Y18*'R17'!X$24</f>
         <v>96.548384644236151</v>
       </c>
@@ -16837,130 +16837,130 @@
       <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="61">
+      <c r="B19" s="58">
         <v>27.7043</v>
       </c>
-      <c r="C19" s="61">
+      <c r="C19" s="58">
         <v>2.3663500000000002</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="58">
         <v>7.9406800000000004</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="58">
         <v>0.64837599999999995</v>
       </c>
-      <c r="F19" s="61">
+      <c r="F19" s="58">
         <v>0.20835300000000001</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="58">
         <v>1.2022299999999999</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="58">
         <v>0.40882800000000002</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="58">
         <v>0.59612699999999996</v>
       </c>
-      <c r="J19" s="61">
+      <c r="J19" s="58">
         <v>0.51290100000000005</v>
       </c>
-      <c r="K19" s="61">
+      <c r="K19" s="58">
         <v>0.81080300000000005</v>
       </c>
-      <c r="L19" s="61">
+      <c r="L19" s="58">
         <v>0.26342599999999999</v>
       </c>
       <c r="N19" t="s">
         <v>34</v>
       </c>
-      <c r="O19" s="55">
+      <c r="O19" s="52">
         <f t="shared" si="1"/>
         <v>0.14523768768581119</v>
       </c>
-      <c r="P19" s="56">
+      <c r="P19" s="53">
         <f t="shared" si="0"/>
         <v>5.0286032161548339E-2</v>
       </c>
-      <c r="Q19" s="56">
+      <c r="Q19" s="53">
         <f t="shared" si="0"/>
         <v>5.2531254514679632E-2</v>
       </c>
-      <c r="R19" s="56">
+      <c r="R19" s="53">
         <f t="shared" si="0"/>
         <v>4.9953381923295959E-2</v>
       </c>
-      <c r="S19" s="56">
+      <c r="S19" s="53">
         <f t="shared" si="0"/>
         <v>2.6349179130112647E-2</v>
       </c>
-      <c r="T19" s="56">
+      <c r="T19" s="53">
         <f t="shared" si="0"/>
         <v>2.8601692787463214E-2</v>
       </c>
-      <c r="U19" s="56">
+      <c r="U19" s="53">
         <f t="shared" si="0"/>
         <v>2.2160873114593502E-2</v>
       </c>
-      <c r="V19" s="56">
+      <c r="V19" s="53">
         <f t="shared" si="0"/>
         <v>7.3595850510168134E-2</v>
       </c>
-      <c r="W19" s="56">
+      <c r="W19" s="53">
         <f t="shared" si="0"/>
         <v>1.0010260143385415E-2</v>
       </c>
-      <c r="X19" s="56">
+      <c r="X19" s="53">
         <f t="shared" si="0"/>
         <v>2.5569078181627351E-2</v>
       </c>
-      <c r="Y19" s="57">
+      <c r="Y19" s="54">
         <f t="shared" si="0"/>
         <v>1.6897198733634614E-2</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AB19" s="63">
+      <c r="AB19" s="60">
         <f>O19*'R17'!N$24</f>
         <v>5155.6209953525349</v>
       </c>
-      <c r="AC19" s="63">
+      <c r="AC19" s="60">
         <f>P19*'R17'!O$24</f>
         <v>2935.6572534169904</v>
       </c>
-      <c r="AD19" s="63">
+      <c r="AD19" s="60">
         <f>Q19*'R17'!P$24</f>
         <v>2652.5423485531364</v>
       </c>
-      <c r="AE19" s="63">
+      <c r="AE19" s="60">
         <f>R19*'R17'!Q$24</f>
         <v>844.29276787196795</v>
       </c>
-      <c r="AF19" s="63">
+      <c r="AF19" s="60">
         <f>S19*'R17'!R$24</f>
         <v>368.10806250595147</v>
       </c>
-      <c r="AG19" s="63">
+      <c r="AG19" s="60">
         <f>T19*'R17'!S$24</f>
         <v>1137.2994625638921</v>
       </c>
-      <c r="AH19" s="63">
+      <c r="AH19" s="60">
         <f>U19*'R17'!T$24</f>
         <v>957.70329750840165</v>
       </c>
-      <c r="AI19" s="63">
+      <c r="AI19" s="60">
         <f>V19*'R17'!U$24</f>
         <v>1343.2457872131381</v>
       </c>
-      <c r="AJ19" s="63">
+      <c r="AJ19" s="60">
         <f>W19*'R17'!V$24</f>
         <v>1589.5583876165294</v>
       </c>
-      <c r="AK19" s="63">
+      <c r="AK19" s="60">
         <f>X19*'R17'!W$24</f>
         <v>1439.3798413081724</v>
       </c>
-      <c r="AL19" s="63">
+      <c r="AL19" s="60">
         <f>Y19*'R17'!X$24</f>
         <v>50.459801705630895</v>
       </c>
@@ -16969,130 +16969,130 @@
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="61">
+      <c r="B20" s="58">
         <v>2.7208899999999998</v>
       </c>
-      <c r="C20" s="61">
+      <c r="C20" s="58">
         <v>0.97823199999999999</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="58">
         <v>2.2060900000000001</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="58">
         <v>0.35295799999999999</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="58">
         <v>0.54177600000000004</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="58">
         <v>0.89046400000000003</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="58">
         <v>0.28070699999999998</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="58">
         <v>0.36798399999999998</v>
       </c>
-      <c r="J20" s="61">
+      <c r="J20" s="58">
         <v>3.45343</v>
       </c>
-      <c r="K20" s="61">
+      <c r="K20" s="58">
         <v>0.59402500000000003</v>
       </c>
-      <c r="L20" s="61">
+      <c r="L20" s="58">
         <v>0.361431</v>
       </c>
       <c r="N20" t="s">
         <v>35</v>
       </c>
-      <c r="O20" s="55">
+      <c r="O20" s="52">
         <f t="shared" si="1"/>
         <v>1.4264059082793891E-2</v>
       </c>
-      <c r="P20" s="56">
+      <c r="P20" s="53">
         <f t="shared" ref="P20:P29" si="2">C20/SUM(C$4:C$29)</f>
         <v>2.0787882525178332E-2</v>
       </c>
-      <c r="Q20" s="56">
+      <c r="Q20" s="53">
         <f t="shared" ref="Q20:Q29" si="3">D20/SUM(D$4:D$29)</f>
         <v>1.4594301152078862E-2</v>
       </c>
-      <c r="R20" s="56">
+      <c r="R20" s="53">
         <f t="shared" ref="R20:R29" si="4">E20/SUM(E$4:E$29)</f>
         <v>2.7193242465610536E-2</v>
       </c>
-      <c r="S20" s="56">
+      <c r="S20" s="53">
         <f t="shared" ref="S20:S29" si="5">F20/SUM(F$4:F$29)</f>
         <v>6.8515225950170663E-2</v>
       </c>
-      <c r="T20" s="56">
+      <c r="T20" s="53">
         <f t="shared" ref="T20:T29" si="6">G20/SUM(G$4:G$29)</f>
         <v>2.1184613398680489E-2</v>
       </c>
-      <c r="U20" s="56">
+      <c r="U20" s="53">
         <f t="shared" ref="U20:U29" si="7">H20/SUM(H$4:H$29)</f>
         <v>1.5215964193690739E-2</v>
       </c>
-      <c r="V20" s="56">
+      <c r="V20" s="53">
         <f t="shared" ref="V20:V29" si="8">I20/SUM(I$4:I$29)</f>
         <v>4.5430076903300323E-2</v>
       </c>
-      <c r="W20" s="56">
+      <c r="W20" s="53">
         <f t="shared" ref="W20:W29" si="9">J20/SUM(J$4:J$29)</f>
         <v>6.7400400246775669E-2</v>
       </c>
-      <c r="X20" s="56">
+      <c r="X20" s="53">
         <f t="shared" ref="X20:X29" si="10">K20/SUM(K$4:K$29)</f>
         <v>1.8732875515804933E-2</v>
       </c>
-      <c r="Y20" s="57">
+      <c r="Y20" s="54">
         <f t="shared" ref="Y20:Y29" si="11">L20/SUM(L$4:L$29)</f>
         <v>2.3183631970634225E-2</v>
       </c>
       <c r="AA20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AB20" s="63">
+      <c r="AB20" s="60">
         <f>O20*'R17'!N$24</f>
         <v>506.34297239218313</v>
       </c>
-      <c r="AC20" s="63">
+      <c r="AC20" s="60">
         <f>P20*'R17'!O$24</f>
         <v>1213.5795069725987</v>
       </c>
-      <c r="AD20" s="63">
+      <c r="AD20" s="60">
         <f>Q20*'R17'!P$24</f>
         <v>736.93275005661826</v>
       </c>
-      <c r="AE20" s="63">
+      <c r="AE20" s="60">
         <f>R20*'R17'!Q$24</f>
         <v>459.60968136166991</v>
       </c>
-      <c r="AF20" s="63">
+      <c r="AF20" s="60">
         <f>S20*'R17'!R$24</f>
         <v>957.18378747713905</v>
       </c>
-      <c r="AG20" s="63">
+      <c r="AG20" s="60">
         <f>T20*'R17'!S$24</f>
         <v>842.37145024869926</v>
       </c>
-      <c r="AH20" s="63">
+      <c r="AH20" s="60">
         <f>U20*'R17'!T$24</f>
         <v>657.57242540552716</v>
       </c>
-      <c r="AI20" s="63">
+      <c r="AI20" s="60">
         <f>V20*'R17'!U$24</f>
         <v>829.17391388385272</v>
       </c>
-      <c r="AJ20" s="63">
+      <c r="AJ20" s="60">
         <f>W20*'R17'!V$24</f>
         <v>10702.706024255267</v>
       </c>
-      <c r="AK20" s="63">
+      <c r="AK20" s="60">
         <f>X20*'R17'!W$24</f>
         <v>1054.5442113967106</v>
       </c>
-      <c r="AL20" s="63">
+      <c r="AL20" s="60">
         <f>Y20*'R17'!X$24</f>
         <v>69.232864600562891</v>
       </c>
@@ -17101,130 +17101,130 @@
       <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="61">
+      <c r="B21" s="58">
         <v>1.4113899999999999</v>
       </c>
-      <c r="C21" s="61">
+      <c r="C21" s="58">
         <v>4.6764800000000002E-2</v>
       </c>
-      <c r="D21" s="61">
+      <c r="D21" s="58">
         <v>0.49106699999999998</v>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="58">
         <v>3.7866499999999997E-2</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="58">
         <v>0.30793599999999999</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="58">
         <v>1.99872E-2</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="58">
         <v>0.145124</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="58">
         <v>1.0989799999999999E-5</v>
       </c>
-      <c r="J21" s="61">
+      <c r="J21" s="58">
         <v>0.108276</v>
       </c>
-      <c r="K21" s="61">
+      <c r="K21" s="58">
         <v>9.3363700000000001E-3</v>
       </c>
-      <c r="L21" s="61">
+      <c r="L21" s="58">
         <v>5.3118599999999997E-6</v>
       </c>
       <c r="N21" t="s">
         <v>36</v>
       </c>
-      <c r="O21" s="55">
+      <c r="O21" s="52">
         <f t="shared" si="1"/>
         <v>7.3991048329276341E-3</v>
       </c>
-      <c r="P21" s="56">
+      <c r="P21" s="53">
         <f t="shared" si="2"/>
         <v>9.9377363316008847E-4</v>
       </c>
-      <c r="Q21" s="56">
+      <c r="Q21" s="53">
         <f t="shared" si="3"/>
         <v>3.248634318567198E-3</v>
       </c>
-      <c r="R21" s="56">
+      <c r="R21" s="53">
         <f t="shared" si="4"/>
         <v>2.9173808663468213E-3</v>
       </c>
-      <c r="S21" s="56">
+      <c r="S21" s="53">
         <f t="shared" si="5"/>
         <v>3.8942855752546725E-2</v>
       </c>
-      <c r="T21" s="56">
+      <c r="T21" s="53">
         <f t="shared" si="6"/>
         <v>4.7550614614639864E-4</v>
       </c>
-      <c r="U21" s="56">
+      <c r="U21" s="53">
         <f t="shared" si="7"/>
         <v>7.8665711494375797E-3</v>
       </c>
-      <c r="V21" s="56">
+      <c r="V21" s="53">
         <f t="shared" si="8"/>
         <v>1.3567640417841261E-6</v>
       </c>
-      <c r="W21" s="56">
+      <c r="W21" s="53">
         <f t="shared" si="9"/>
         <v>2.1132166388546699E-3</v>
       </c>
-      <c r="X21" s="56">
+      <c r="X21" s="53">
         <f t="shared" si="10"/>
         <v>2.944270981515857E-4</v>
       </c>
-      <c r="Y21" s="57">
+      <c r="Y21" s="54">
         <f t="shared" si="11"/>
         <v>3.4072397586132103E-7</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AB21" s="63">
+      <c r="AB21" s="60">
         <f>O21*'R17'!N$24</f>
         <v>262.6520762708538</v>
       </c>
-      <c r="AC21" s="63">
+      <c r="AC21" s="60">
         <f>P21*'R17'!O$24</f>
         <v>58.015688433492443</v>
       </c>
-      <c r="AD21" s="63">
+      <c r="AD21" s="60">
         <f>Q21*'R17'!P$24</f>
         <v>164.0383460203588</v>
       </c>
-      <c r="AE21" s="63">
+      <c r="AE21" s="60">
         <f>R21*'R17'!Q$24</f>
         <v>49.308444628770772</v>
       </c>
-      <c r="AF21" s="63">
+      <c r="AF21" s="60">
         <f>S21*'R17'!R$24</f>
         <v>544.04651882062012</v>
       </c>
-      <c r="AG21" s="63">
+      <c r="AG21" s="60">
         <f>T21*'R17'!S$24</f>
         <v>18.907722996562246</v>
       </c>
-      <c r="AH21" s="63">
+      <c r="AH21" s="60">
         <f>U21*'R17'!T$24</f>
         <v>339.96138558907234</v>
       </c>
-      <c r="AI21" s="63">
+      <c r="AI21" s="60">
         <f>V21*'R17'!U$24</f>
         <v>2.4763183939521184E-2</v>
       </c>
-      <c r="AJ21" s="63">
+      <c r="AJ21" s="60">
         <f>W21*'R17'!V$24</f>
         <v>335.56383001313571</v>
       </c>
-      <c r="AK21" s="63">
+      <c r="AK21" s="60">
         <f>X21*'R17'!W$24</f>
         <v>16.574411748592915</v>
       </c>
-      <c r="AL21" s="63">
+      <c r="AL21" s="60">
         <f>Y21*'R17'!X$24</f>
         <v>1.0174979018322888E-3</v>
       </c>
@@ -17233,130 +17233,130 @@
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="61">
+      <c r="B22" s="58">
         <v>1.6475599999999999</v>
       </c>
-      <c r="C22" s="61">
+      <c r="C22" s="58">
         <v>3.1288000000000003E-2</v>
       </c>
-      <c r="D22" s="61">
+      <c r="D22" s="58">
         <v>0.17535100000000001</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="58">
         <v>0.173067</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F22" s="58">
         <v>0.32256800000000002</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="58">
         <v>7.5924599999999995E-2</v>
       </c>
-      <c r="H22" s="61">
+      <c r="H22" s="58">
         <v>0.30330200000000002</v>
       </c>
-      <c r="I22" s="61">
+      <c r="I22" s="58">
         <v>9.6032900000000004E-2</v>
       </c>
-      <c r="J22" s="61">
+      <c r="J22" s="58">
         <v>3.7916699999999999</v>
       </c>
-      <c r="K22" s="61">
+      <c r="K22" s="58">
         <v>0.230238</v>
       </c>
-      <c r="L22" s="61">
+      <c r="L22" s="58">
         <v>3.9814700000000001E-2</v>
       </c>
       <c r="N22" t="s">
         <v>37</v>
       </c>
-      <c r="O22" s="55">
+      <c r="O22" s="52">
         <f t="shared" si="1"/>
         <v>8.6372081129512408E-3</v>
       </c>
-      <c r="P22" s="56">
+      <c r="P22" s="53">
         <f t="shared" si="2"/>
         <v>6.6488447367064223E-4</v>
       </c>
-      <c r="Q22" s="56">
+      <c r="Q22" s="53">
         <f t="shared" si="3"/>
         <v>1.1600276059989306E-3</v>
       </c>
-      <c r="R22" s="56">
+      <c r="R22" s="53">
         <f t="shared" si="4"/>
         <v>1.3333747623784753E-2</v>
       </c>
-      <c r="S22" s="56">
+      <c r="S22" s="53">
         <f t="shared" si="5"/>
         <v>4.0793278779965615E-2</v>
       </c>
-      <c r="T22" s="56">
+      <c r="T22" s="53">
         <f t="shared" si="6"/>
         <v>1.8062867206865821E-3</v>
       </c>
-      <c r="U22" s="56">
+      <c r="U22" s="53">
         <f t="shared" si="7"/>
         <v>1.6440745588370751E-2</v>
       </c>
-      <c r="V22" s="56">
+      <c r="V22" s="53">
         <f t="shared" si="8"/>
         <v>1.1855901431168067E-2</v>
       </c>
-      <c r="W22" s="56">
+      <c r="W22" s="53">
         <f t="shared" si="9"/>
         <v>7.4001811417544847E-2</v>
       </c>
-      <c r="X22" s="56">
+      <c r="X22" s="53">
         <f t="shared" si="10"/>
         <v>7.2606704987296759E-3</v>
       </c>
-      <c r="Y22" s="57">
+      <c r="Y22" s="54">
         <f t="shared" si="11"/>
         <v>2.5538743268319832E-3</v>
       </c>
       <c r="AA22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AB22" s="63">
+      <c r="AB22" s="60">
         <f>O22*'R17'!N$24</f>
         <v>306.60204109481282</v>
       </c>
-      <c r="AC22" s="63">
+      <c r="AC22" s="60">
         <f>P22*'R17'!O$24</f>
         <v>38.815409447000988</v>
       </c>
-      <c r="AD22" s="63">
+      <c r="AD22" s="60">
         <f>Q22*'R17'!P$24</f>
         <v>58.575078376302912</v>
       </c>
-      <c r="AE22" s="63">
+      <c r="AE22" s="60">
         <f>R22*'R17'!Q$24</f>
         <v>225.36185247032262</v>
       </c>
-      <c r="AF22" s="63">
+      <c r="AF22" s="60">
         <f>S22*'R17'!R$24</f>
         <v>569.89763289426958</v>
       </c>
-      <c r="AG22" s="63">
+      <c r="AG22" s="60">
         <f>T22*'R17'!S$24</f>
         <v>71.82403265213685</v>
       </c>
-      <c r="AH22" s="63">
+      <c r="AH22" s="60">
         <f>U22*'R17'!T$24</f>
         <v>710.50252316596027</v>
       </c>
-      <c r="AI22" s="63">
+      <c r="AI22" s="60">
         <f>V22*'R17'!U$24</f>
         <v>216.38977660609331</v>
       </c>
-      <c r="AJ22" s="63">
+      <c r="AJ22" s="60">
         <f>W22*'R17'!V$24</f>
         <v>11750.96334687194</v>
       </c>
-      <c r="AK22" s="63">
+      <c r="AK22" s="60">
         <f>X22*'R17'!W$24</f>
         <v>408.7305250512282</v>
       </c>
-      <c r="AL22" s="63">
+      <c r="AL22" s="60">
         <f>Y22*'R17'!X$24</f>
         <v>7.6265891254818516</v>
       </c>
@@ -17365,130 +17365,130 @@
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="61">
+      <c r="B23" s="58">
         <v>0.29578599999999999</v>
       </c>
-      <c r="C23" s="61">
+      <c r="C23" s="58">
         <v>0.176291</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="58">
         <v>0.10953499999999999</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="58">
         <v>1.9266599999999998E-2</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="58">
         <v>0.260382</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="58">
         <v>0.33162900000000001</v>
       </c>
-      <c r="H23" s="61">
+      <c r="H23" s="58">
         <v>4.0598700000000001E-2</v>
       </c>
-      <c r="I23" s="61">
+      <c r="I23" s="58">
         <v>1.44253E-2</v>
       </c>
-      <c r="J23" s="61">
+      <c r="J23" s="58">
         <v>8.75412E-2</v>
       </c>
-      <c r="K23" s="61">
+      <c r="K23" s="58">
         <v>0.114403</v>
       </c>
-      <c r="L23" s="61">
+      <c r="L23" s="58">
         <v>1.0158199999999999E-2</v>
       </c>
       <c r="N23" t="s">
         <v>38</v>
       </c>
-      <c r="O23" s="55">
+      <c r="O23" s="52">
         <f t="shared" si="1"/>
         <v>1.5506356302030858E-3</v>
       </c>
-      <c r="P23" s="56">
+      <c r="P23" s="53">
         <f t="shared" si="2"/>
         <v>3.7462653013254662E-3</v>
       </c>
-      <c r="Q23" s="56">
+      <c r="Q23" s="53">
         <f t="shared" si="3"/>
         <v>7.2462446078489905E-4</v>
       </c>
-      <c r="R23" s="56">
+      <c r="R23" s="53">
         <f t="shared" si="4"/>
         <v>1.48437299986948E-3</v>
       </c>
-      <c r="S23" s="56">
+      <c r="S23" s="53">
         <f t="shared" si="5"/>
         <v>3.2928980913435331E-2</v>
       </c>
-      <c r="T23" s="56">
+      <c r="T23" s="53">
         <f t="shared" si="6"/>
         <v>7.8896307506996499E-3</v>
       </c>
-      <c r="U23" s="56">
+      <c r="U23" s="53">
         <f t="shared" si="7"/>
         <v>2.2006874267844843E-3</v>
       </c>
-      <c r="V23" s="56">
+      <c r="V23" s="53">
         <f t="shared" si="8"/>
         <v>1.7808994096297074E-3</v>
       </c>
-      <c r="W23" s="56">
+      <c r="W23" s="53">
         <f t="shared" si="9"/>
         <v>1.7085367064289816E-3</v>
       </c>
-      <c r="X23" s="56">
+      <c r="X23" s="53">
         <f t="shared" si="10"/>
         <v>3.6077558312101873E-3</v>
       </c>
-      <c r="Y23" s="57">
+      <c r="Y23" s="54">
         <f t="shared" si="11"/>
         <v>6.5158763438691368E-4</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AB23" s="63">
+      <c r="AB23" s="60">
         <f>O23*'R17'!N$24</f>
         <v>55.044181290678523</v>
       </c>
-      <c r="AC23" s="63">
+      <c r="AC23" s="60">
         <f>P23*'R17'!O$24</f>
         <v>218.70389116662142</v>
       </c>
-      <c r="AD23" s="63">
+      <c r="AD23" s="60">
         <f>Q23*'R17'!P$24</f>
         <v>36.589590079031986</v>
       </c>
-      <c r="AE23" s="63">
+      <c r="AE23" s="60">
         <f>R23*'R17'!Q$24</f>
         <v>25.088299137355577</v>
       </c>
-      <c r="AF23" s="63">
+      <c r="AF23" s="60">
         <f>S23*'R17'!R$24</f>
         <v>460.03039808125948</v>
       </c>
-      <c r="AG23" s="63">
+      <c r="AG23" s="60">
         <f>T23*'R17'!S$24</f>
         <v>313.7182431569675</v>
       </c>
-      <c r="AH23" s="63">
+      <c r="AH23" s="60">
         <f>U23*'R17'!T$24</f>
         <v>95.104809026178103</v>
       </c>
-      <c r="AI23" s="63">
+      <c r="AI23" s="60">
         <f>V23*'R17'!U$24</f>
         <v>32.504354700065065</v>
       </c>
-      <c r="AJ23" s="63">
+      <c r="AJ23" s="60">
         <f>W23*'R17'!V$24</f>
         <v>271.30352391985218</v>
       </c>
-      <c r="AK23" s="63">
+      <c r="AK23" s="60">
         <f>X23*'R17'!W$24</f>
         <v>203.09418192233974</v>
       </c>
-      <c r="AL23" s="63">
+      <c r="AL23" s="60">
         <f>Y23*'R17'!X$24</f>
         <v>1.9458244732340002</v>
       </c>
@@ -17497,130 +17497,130 @@
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="61">
+      <c r="B24" s="58">
         <v>1.9940800000000002E-2</v>
       </c>
-      <c r="C24" s="61">
+      <c r="C24" s="58">
         <v>0.109695</v>
       </c>
-      <c r="D24" s="61">
+      <c r="D24" s="58">
         <v>2.3758700000000001E-2</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="58">
         <v>5.7771200000000002E-3</v>
       </c>
-      <c r="F24" s="61">
+      <c r="F24" s="58">
         <v>1.5509E-2</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="58">
         <v>0.17518900000000001</v>
       </c>
-      <c r="H24" s="61">
+      <c r="H24" s="58">
         <v>2.46766E-2</v>
       </c>
-      <c r="I24" s="61">
+      <c r="I24" s="58">
         <v>9.6983499999999995E-4</v>
       </c>
-      <c r="J24" s="61">
+      <c r="J24" s="58">
         <v>4.2373000000000001E-2</v>
       </c>
-      <c r="K24" s="61">
+      <c r="K24" s="58">
         <v>1.7006899999999998E-2</v>
       </c>
-      <c r="L24" s="61">
+      <c r="L24" s="58">
         <v>3.2604399999999999E-3</v>
       </c>
       <c r="N24" t="s">
         <v>39</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="52">
         <f t="shared" si="1"/>
         <v>1.0453812883217493E-4</v>
       </c>
-      <c r="P24" s="56">
+      <c r="P24" s="53">
         <f t="shared" si="2"/>
         <v>2.3310694943525024E-3</v>
       </c>
-      <c r="Q24" s="56">
+      <c r="Q24" s="53">
         <f t="shared" si="3"/>
         <v>1.5717474027890797E-4</v>
       </c>
-      <c r="R24" s="56">
+      <c r="R24" s="53">
         <f t="shared" si="4"/>
         <v>4.45091554555862E-4</v>
       </c>
-      <c r="S24" s="56">
+      <c r="S24" s="53">
         <f t="shared" si="5"/>
         <v>1.9613320620721422E-3</v>
       </c>
-      <c r="T24" s="56">
+      <c r="T24" s="53">
         <f t="shared" si="6"/>
         <v>4.1678397292888164E-3</v>
       </c>
-      <c r="U24" s="56">
+      <c r="U24" s="53">
         <f t="shared" si="7"/>
         <v>1.3376163117486521E-3</v>
       </c>
-      <c r="V24" s="56">
+      <c r="V24" s="53">
         <f t="shared" si="8"/>
         <v>1.1973259335599448E-4</v>
       </c>
-      <c r="W24" s="56">
+      <c r="W24" s="53">
         <f t="shared" si="9"/>
         <v>8.2699147214700325E-4</v>
       </c>
-      <c r="X24" s="56">
+      <c r="X24" s="53">
         <f t="shared" si="10"/>
         <v>5.3632109862336238E-4</v>
       </c>
-      <c r="Y24" s="57">
+      <c r="Y24" s="54">
         <f t="shared" si="11"/>
         <v>2.0913768055959411E-4</v>
       </c>
       <c r="AA24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="AB24" s="63">
+      <c r="AB24" s="60">
         <f>O24*'R17'!N$24</f>
         <v>3.7108754649684648</v>
       </c>
-      <c r="AC24" s="63">
+      <c r="AC24" s="60">
         <f>P24*'R17'!O$24</f>
         <v>136.08592237563195</v>
       </c>
-      <c r="AD24" s="63">
+      <c r="AD24" s="60">
         <f>Q24*'R17'!P$24</f>
         <v>7.9364686521266936</v>
       </c>
-      <c r="AE24" s="63">
+      <c r="AE24" s="60">
         <f>R24*'R17'!Q$24</f>
         <v>7.5227655482752356</v>
       </c>
-      <c r="AF24" s="63">
+      <c r="AF24" s="60">
         <f>S24*'R17'!R$24</f>
         <v>27.400555506303252</v>
       </c>
-      <c r="AG24" s="63">
+      <c r="AG24" s="60">
         <f>T24*'R17'!S$24</f>
         <v>165.72731968683672</v>
       </c>
-      <c r="AH24" s="63">
+      <c r="AH24" s="60">
         <f>U24*'R17'!T$24</f>
         <v>57.806366470241329</v>
       </c>
-      <c r="AI24" s="63">
+      <c r="AI24" s="60">
         <f>V24*'R17'!U$24</f>
         <v>2.1853175213366511</v>
       </c>
-      <c r="AJ24" s="63">
+      <c r="AJ24" s="60">
         <f>W24*'R17'!V$24</f>
         <v>131.32038650436476</v>
       </c>
-      <c r="AK24" s="63">
+      <c r="AK24" s="60">
         <f>X24*'R17'!W$24</f>
         <v>30.191537307020266</v>
       </c>
-      <c r="AL24" s="63">
+      <c r="AL24" s="60">
         <f>Y24*'R17'!X$24</f>
         <v>0.62454410678181804</v>
       </c>
@@ -17629,130 +17629,130 @@
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="61">
+      <c r="B25" s="58">
         <v>0.22412699999999999</v>
       </c>
-      <c r="C25" s="61">
+      <c r="C25" s="58">
         <v>3.7982399999999999E-2</v>
       </c>
-      <c r="D25" s="61">
+      <c r="D25" s="58">
         <v>0.26159500000000002</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="58">
         <v>9.2142400000000003E-3</v>
       </c>
-      <c r="F25" s="61">
+      <c r="F25" s="58">
         <v>3.4841199999999998E-3</v>
       </c>
-      <c r="G25" s="61">
+      <c r="G25" s="58">
         <v>8.3844000000000002E-3</v>
       </c>
-      <c r="H25" s="61">
+      <c r="H25" s="58">
         <v>1.7263000000000001E-2</v>
       </c>
-      <c r="I25" s="61">
+      <c r="I25" s="58">
         <v>5.4374800000000004E-4</v>
       </c>
-      <c r="J25" s="61">
+      <c r="J25" s="58">
         <v>1.8286500000000001E-2</v>
       </c>
-      <c r="K25" s="61">
+      <c r="K25" s="58">
         <v>3.41384E-3</v>
       </c>
-      <c r="L25" s="61">
+      <c r="L25" s="58">
         <v>4.0014899999999999E-3</v>
       </c>
       <c r="N25" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="55">
+      <c r="O25" s="52">
         <f t="shared" si="1"/>
         <v>1.1749687675905113E-3</v>
       </c>
-      <c r="P25" s="56">
+      <c r="P25" s="53">
         <f t="shared" si="2"/>
         <v>8.0714357046624268E-4</v>
       </c>
-      <c r="Q25" s="56">
+      <c r="Q25" s="53">
         <f t="shared" si="3"/>
         <v>1.7305713773590697E-3</v>
       </c>
-      <c r="R25" s="56">
+      <c r="R25" s="53">
         <f t="shared" si="4"/>
         <v>7.0990050503552053E-4</v>
       </c>
-      <c r="S25" s="56">
+      <c r="S25" s="53">
         <f t="shared" si="5"/>
         <v>4.4061617538892198E-4</v>
       </c>
-      <c r="T25" s="56">
+      <c r="T25" s="53">
         <f t="shared" si="6"/>
         <v>1.9946934696955375E-4</v>
       </c>
-      <c r="U25" s="56">
+      <c r="U25" s="53">
         <f t="shared" si="7"/>
         <v>9.3575575199650611E-4</v>
       </c>
-      <c r="V25" s="56">
+      <c r="V25" s="53">
         <f t="shared" si="8"/>
         <v>6.7129313926735261E-5</v>
       </c>
-      <c r="W25" s="56">
+      <c r="W25" s="53">
         <f t="shared" si="9"/>
         <v>3.5689659819734679E-4</v>
       </c>
-      <c r="X25" s="56">
+      <c r="X25" s="53">
         <f t="shared" si="10"/>
         <v>1.0765715205736376E-4</v>
       </c>
-      <c r="Y25" s="57">
+      <c r="Y25" s="54">
         <f t="shared" si="11"/>
         <v>2.5667159566880859E-4</v>
       </c>
       <c r="AA25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB25" s="63">
+      <c r="AB25" s="60">
         <f>O25*'R17'!N$24</f>
         <v>41.708827395941334</v>
       </c>
-      <c r="AC25" s="63">
+      <c r="AC25" s="60">
         <f>P25*'R17'!O$24</f>
         <v>47.12037866849176</v>
       </c>
-      <c r="AD25" s="63">
+      <c r="AD25" s="60">
         <f>Q25*'R17'!P$24</f>
         <v>87.384432525899243</v>
       </c>
-      <c r="AE25" s="63">
+      <c r="AE25" s="60">
         <f>R25*'R17'!Q$24</f>
         <v>11.998464152646926</v>
       </c>
-      <c r="AF25" s="63">
+      <c r="AF25" s="60">
         <f>S25*'R17'!R$24</f>
         <v>6.1555756947979408</v>
       </c>
-      <c r="AG25" s="63">
+      <c r="AG25" s="60">
         <f>T25*'R17'!S$24</f>
         <v>7.9315718405968063</v>
       </c>
-      <c r="AH25" s="63">
+      <c r="AH25" s="60">
         <f>U25*'R17'!T$24</f>
         <v>40.439578563326229</v>
       </c>
-      <c r="AI25" s="63">
+      <c r="AI25" s="60">
         <f>V25*'R17'!U$24</f>
         <v>1.2252208175532555</v>
       </c>
-      <c r="AJ25" s="63">
+      <c r="AJ25" s="60">
         <f>W25*'R17'!V$24</f>
         <v>56.672651164941506</v>
       </c>
-      <c r="AK25" s="63">
+      <c r="AK25" s="60">
         <f>X25*'R17'!W$24</f>
         <v>6.0604271043046101</v>
       </c>
-      <c r="AL25" s="63">
+      <c r="AL25" s="60">
         <f>Y25*'R17'!X$24</f>
         <v>0.7664937854542262</v>
       </c>
@@ -17761,130 +17761,130 @@
       <c r="A26" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="61">
+      <c r="B26" s="58">
         <v>2.7385300000000001E-2</v>
       </c>
-      <c r="C26" s="61">
+      <c r="C26" s="58">
         <v>5.1764200000000002E-3</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="58">
         <v>7.6372099999999998E-2</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="58">
         <v>2.10684E-3</v>
       </c>
-      <c r="F26" s="61">
+      <c r="F26" s="58">
         <v>1.8565400000000001E-3</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="58">
         <v>4.9126999999999999E-3</v>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="58">
         <v>2.30438E-2</v>
       </c>
-      <c r="I26" s="61">
+      <c r="I26" s="58">
         <v>1.0511499999999999E-5</v>
       </c>
-      <c r="J26" s="61">
+      <c r="J26" s="58">
         <v>7.58277E-3</v>
       </c>
-      <c r="K26" s="61">
+      <c r="K26" s="58">
         <v>8.5207200000000007E-3</v>
       </c>
-      <c r="L26" s="61">
+      <c r="L26" s="58">
         <v>1.6057300000000001E-3</v>
       </c>
       <c r="N26" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="55">
+      <c r="O26" s="52">
         <f t="shared" si="1"/>
         <v>1.4356535442448448E-4</v>
       </c>
-      <c r="P26" s="56">
+      <c r="P26" s="53">
         <f t="shared" si="2"/>
         <v>1.100013195857257E-4</v>
       </c>
-      <c r="Q26" s="56">
+      <c r="Q26" s="53">
         <f t="shared" si="3"/>
         <v>5.0523660730826124E-4</v>
       </c>
-      <c r="R26" s="56">
+      <c r="R26" s="53">
         <f t="shared" si="4"/>
         <v>1.6231906050081569E-4</v>
       </c>
-      <c r="S26" s="56">
+      <c r="S26" s="53">
         <f t="shared" si="5"/>
         <v>2.3478570033654103E-4</v>
       </c>
-      <c r="T26" s="56">
+      <c r="T26" s="53">
         <f t="shared" si="6"/>
         <v>1.1687575269039247E-4</v>
       </c>
-      <c r="U26" s="56">
+      <c r="U26" s="53">
         <f t="shared" si="7"/>
         <v>1.2491089844092619E-3</v>
       </c>
-      <c r="V26" s="56">
+      <c r="V26" s="53">
         <f t="shared" si="8"/>
         <v>1.2977147195775939E-6</v>
       </c>
-      <c r="W26" s="56">
+      <c r="W26" s="53">
         <f t="shared" si="9"/>
         <v>1.4799249817695542E-4</v>
       </c>
-      <c r="X26" s="56">
+      <c r="X26" s="53">
         <f t="shared" si="10"/>
         <v>2.6870516740041145E-4</v>
       </c>
-      <c r="Y26" s="57">
+      <c r="Y26" s="54">
         <f t="shared" si="11"/>
         <v>1.0299795359060651E-4</v>
       </c>
       <c r="AA26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB26" s="63">
+      <c r="AB26" s="60">
         <f>O26*'R17'!N$24</f>
         <v>5.0962568137086226</v>
       </c>
-      <c r="AC26" s="63">
+      <c r="AC26" s="60">
         <f>P26*'R17'!O$24</f>
         <v>6.4217866840208648</v>
       </c>
-      <c r="AD26" s="63">
+      <c r="AD26" s="60">
         <f>Q26*'R17'!P$24</f>
         <v>25.511697927373344</v>
       </c>
-      <c r="AE26" s="63">
+      <c r="AE26" s="60">
         <f>R26*'R17'!Q$24</f>
         <v>2.7434540684161308</v>
       </c>
-      <c r="AF26" s="63">
+      <c r="AF26" s="60">
         <f>S26*'R17'!R$24</f>
         <v>3.2800456070457309</v>
       </c>
-      <c r="AG26" s="63">
+      <c r="AG26" s="60">
         <f>T26*'R17'!S$24</f>
         <v>4.6473728568889756</v>
       </c>
-      <c r="AH26" s="63">
+      <c r="AH26" s="60">
         <f>U26*'R17'!T$24</f>
         <v>53.981437785875976</v>
       </c>
-      <c r="AI26" s="63">
+      <c r="AI26" s="60">
         <f>V26*'R17'!U$24</f>
         <v>2.3685436311878007E-2</v>
       </c>
-      <c r="AJ26" s="63">
+      <c r="AJ26" s="60">
         <f>W26*'R17'!V$24</f>
         <v>23.500160176850873</v>
       </c>
-      <c r="AK26" s="63">
+      <c r="AK26" s="60">
         <f>X26*'R17'!W$24</f>
         <v>15.126427259681293</v>
       </c>
-      <c r="AL26" s="63">
+      <c r="AL26" s="60">
         <f>Y26*'R17'!X$24</f>
         <v>0.30758094262822466</v>
       </c>
@@ -17893,130 +17893,130 @@
       <c r="A27" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="61">
+      <c r="B27" s="58">
         <v>0.44273699999999999</v>
       </c>
-      <c r="C27" s="61">
+      <c r="C27" s="58">
         <v>0.31370399999999998</v>
       </c>
-      <c r="D27" s="61">
+      <c r="D27" s="58">
         <v>0.157334</v>
       </c>
-      <c r="E27" s="61">
+      <c r="E27" s="58">
         <v>3.04782E-2</v>
       </c>
-      <c r="F27" s="61">
+      <c r="F27" s="58">
         <v>7.6224600000000003E-2</v>
       </c>
-      <c r="G27" s="61">
+      <c r="G27" s="58">
         <v>3.2395199999999999E-2</v>
       </c>
-      <c r="H27" s="61">
+      <c r="H27" s="58">
         <v>0.111247</v>
       </c>
-      <c r="I27" s="61">
+      <c r="I27" s="58">
         <v>0.122797</v>
       </c>
-      <c r="J27" s="61">
+      <c r="J27" s="58">
         <v>0.232042</v>
       </c>
-      <c r="K27" s="61">
+      <c r="K27" s="58">
         <v>2.77174E-2</v>
       </c>
-      <c r="L27" s="61">
+      <c r="L27" s="58">
         <v>9.7178400000000002E-3</v>
       </c>
       <c r="N27" t="s">
         <v>42</v>
       </c>
-      <c r="O27" s="55">
+      <c r="O27" s="52">
         <f t="shared" si="1"/>
         <v>2.3210150818808988E-3</v>
       </c>
-      <c r="P27" s="56">
+      <c r="P27" s="53">
         <f t="shared" si="2"/>
         <v>6.6663551178846566E-3</v>
       </c>
-      <c r="Q27" s="56">
+      <c r="Q27" s="53">
         <f t="shared" si="3"/>
         <v>1.0408368550064483E-3</v>
       </c>
-      <c r="R27" s="56">
+      <c r="R27" s="53">
         <f t="shared" si="4"/>
         <v>2.3481578049381825E-3</v>
       </c>
-      <c r="S27" s="56">
+      <c r="S27" s="53">
         <f t="shared" si="5"/>
         <v>9.6396770841849378E-3</v>
       </c>
-      <c r="T27" s="56">
+      <c r="T27" s="53">
         <f t="shared" si="6"/>
         <v>7.7069908269501535E-4</v>
       </c>
-      <c r="U27" s="56">
+      <c r="U27" s="53">
         <f t="shared" si="7"/>
         <v>6.030239248239316E-3</v>
       </c>
-      <c r="V27" s="56">
+      <c r="V27" s="53">
         <f t="shared" si="8"/>
         <v>1.5160107921797063E-2</v>
       </c>
-      <c r="W27" s="56">
+      <c r="W27" s="53">
         <f t="shared" si="9"/>
         <v>4.5287507417443871E-3</v>
       </c>
-      <c r="X27" s="56">
+      <c r="X27" s="53">
         <f t="shared" si="10"/>
         <v>8.7408207368674983E-4</v>
       </c>
-      <c r="Y27" s="57">
+      <c r="Y27" s="54">
         <f t="shared" si="11"/>
         <v>6.2334118022391025E-4</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AB27" s="63">
+      <c r="AB27" s="60">
         <f>O27*'R17'!N$24</f>
         <v>82.390970810285594</v>
       </c>
-      <c r="AC27" s="63">
+      <c r="AC27" s="60">
         <f>P27*'R17'!O$24</f>
         <v>389.17633614043712</v>
       </c>
-      <c r="AD27" s="63">
+      <c r="AD27" s="60">
         <f>Q27*'R17'!P$24</f>
         <v>52.556594380740577</v>
       </c>
-      <c r="AE27" s="63">
+      <c r="AE27" s="60">
         <f>R27*'R17'!Q$24</f>
         <v>39.68765629473549</v>
       </c>
-      <c r="AF27" s="63">
+      <c r="AF27" s="60">
         <f>S27*'R17'!R$24</f>
         <v>134.66995829813416</v>
       </c>
-      <c r="AG27" s="63">
+      <c r="AG27" s="60">
         <f>T27*'R17'!S$24</f>
         <v>30.645586576320504</v>
       </c>
-      <c r="AH27" s="63">
+      <c r="AH27" s="60">
         <f>U27*'R17'!T$24</f>
         <v>260.60254859725154</v>
       </c>
-      <c r="AI27" s="63">
+      <c r="AI27" s="60">
         <f>V27*'R17'!U$24</f>
         <v>276.69700069349608</v>
       </c>
-      <c r="AJ27" s="63">
+      <c r="AJ27" s="60">
         <f>W27*'R17'!V$24</f>
         <v>719.13353138191314</v>
       </c>
-      <c r="AK27" s="63">
+      <c r="AK27" s="60">
         <f>X27*'R17'!W$24</f>
         <v>49.205376415078796</v>
       </c>
-      <c r="AL27" s="63">
+      <c r="AL27" s="60">
         <f>Y27*'R17'!X$24</f>
         <v>1.861472593468557</v>
       </c>
@@ -18025,130 +18025,130 @@
       <c r="A28" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="61">
+      <c r="B28" s="58">
         <v>9.9560200000000001E-2</v>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="58">
         <v>8.4804000000000004E-2</v>
       </c>
-      <c r="D28" s="61">
+      <c r="D28" s="58">
         <v>0.38017299999999998</v>
       </c>
-      <c r="E28" s="61">
+      <c r="E28" s="58">
         <v>2.0003900000000002E-2</v>
       </c>
-      <c r="F28" s="61">
+      <c r="F28" s="58">
         <v>8.8353000000000001E-2</v>
       </c>
-      <c r="G28" s="61">
+      <c r="G28" s="58">
         <v>3.49856E-3</v>
       </c>
-      <c r="H28" s="61">
+      <c r="H28" s="58">
         <v>3.0431E-2</v>
       </c>
-      <c r="I28" s="61">
+      <c r="I28" s="58">
         <v>3.9031599999999998E-4</v>
       </c>
-      <c r="J28" s="61">
+      <c r="J28" s="58">
         <v>8.5900899999999999E-3</v>
       </c>
-      <c r="K28" s="61">
+      <c r="K28" s="58">
         <v>7.8072299999999997E-2</v>
       </c>
-      <c r="L28" s="61">
+      <c r="L28" s="58">
         <v>3.99228E-3</v>
       </c>
       <c r="N28" t="s">
         <v>43</v>
       </c>
-      <c r="O28" s="55">
+      <c r="O28" s="52">
         <f t="shared" si="1"/>
         <v>5.2193678358727349E-4</v>
       </c>
-      <c r="P28" s="56">
+      <c r="P28" s="53">
         <f t="shared" si="2"/>
         <v>1.8021242299017242E-3</v>
       </c>
-      <c r="Q28" s="56">
+      <c r="Q28" s="53">
         <f t="shared" si="3"/>
         <v>2.5150194470258589E-3</v>
       </c>
-      <c r="R28" s="56">
+      <c r="R28" s="53">
         <f t="shared" si="4"/>
         <v>1.5411774289230634E-3</v>
       </c>
-      <c r="S28" s="56">
+      <c r="S28" s="53">
         <f t="shared" si="5"/>
         <v>1.1173484536737376E-2</v>
       </c>
-      <c r="T28" s="56">
+      <c r="T28" s="53">
         <f t="shared" si="6"/>
         <v>8.3232608002218632E-5</v>
       </c>
-      <c r="U28" s="56">
+      <c r="U28" s="53">
         <f t="shared" si="7"/>
         <v>1.6495385094714521E-3</v>
       </c>
-      <c r="V28" s="56">
+      <c r="V28" s="53">
         <f t="shared" si="8"/>
         <v>4.8187111115126118E-5</v>
       </c>
-      <c r="W28" s="56">
+      <c r="W28" s="53">
         <f t="shared" si="9"/>
         <v>1.6765230630295827E-4</v>
       </c>
-      <c r="X28" s="56">
+      <c r="X28" s="53">
         <f t="shared" si="10"/>
         <v>2.4620490335130292E-3</v>
       </c>
-      <c r="Y28" s="57">
+      <c r="Y28" s="54">
         <f t="shared" si="11"/>
         <v>2.5608082938022363E-4</v>
       </c>
       <c r="AA28" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AB28" s="63">
+      <c r="AB28" s="60">
         <f>O28*'R17'!N$24</f>
         <v>18.52761691944924</v>
       </c>
-      <c r="AC28" s="63">
+      <c r="AC28" s="60">
         <f>P28*'R17'!O$24</f>
         <v>105.20653230450881</v>
       </c>
-      <c r="AD28" s="63">
+      <c r="AD28" s="60">
         <f>Q28*'R17'!P$24</f>
         <v>126.9947891460796</v>
       </c>
-      <c r="AE28" s="63">
+      <c r="AE28" s="60">
         <f>R28*'R17'!Q$24</f>
         <v>26.048385657757322</v>
       </c>
-      <c r="AF28" s="63">
+      <c r="AF28" s="60">
         <f>S28*'R17'!R$24</f>
         <v>156.09783226825783</v>
       </c>
-      <c r="AG28" s="63">
+      <c r="AG28" s="60">
         <f>T28*'R17'!S$24</f>
         <v>3.3096083176659463</v>
       </c>
-      <c r="AH28" s="63">
+      <c r="AH28" s="60">
         <f>U28*'R17'!T$24</f>
         <v>71.286382161882671</v>
       </c>
-      <c r="AI28" s="63">
+      <c r="AI28" s="60">
         <f>V28*'R17'!U$24</f>
         <v>0.87949434043732833</v>
       </c>
-      <c r="AJ28" s="63">
+      <c r="AJ28" s="60">
         <f>W28*'R17'!V$24</f>
         <v>26.621998416616208</v>
       </c>
-      <c r="AK28" s="63">
+      <c r="AK28" s="60">
         <f>X28*'R17'!W$24</f>
         <v>138.59802539527359</v>
       </c>
-      <c r="AL28" s="63">
+      <c r="AL28" s="60">
         <f>Y28*'R17'!X$24</f>
         <v>0.76472959067577273</v>
       </c>
@@ -18157,130 +18157,130 @@
       <c r="A29" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="61">
+      <c r="B29" s="58">
         <v>55.436</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="58">
         <v>12.1846</v>
       </c>
-      <c r="D29" s="61">
+      <c r="D29" s="58">
         <v>36.2911</v>
       </c>
-      <c r="E29" s="61">
+      <c r="E29" s="58">
         <v>2.1069300000000002</v>
       </c>
-      <c r="F29" s="61">
+      <c r="F29" s="58">
         <v>1.5139400000000001</v>
       </c>
-      <c r="G29" s="61">
+      <c r="G29" s="58">
         <v>12.4323</v>
       </c>
-      <c r="H29" s="61">
+      <c r="H29" s="58">
         <v>3.1067200000000001</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="58">
         <v>0.87464600000000003</v>
       </c>
-      <c r="J29" s="61">
+      <c r="J29" s="58">
         <v>19.331600000000002</v>
       </c>
-      <c r="K29" s="61">
+      <c r="K29" s="58">
         <v>8.7136399999999998</v>
       </c>
-      <c r="L29" s="61">
+      <c r="L29" s="58">
         <v>6.7928699999999997</v>
       </c>
       <c r="N29" t="s">
         <v>44</v>
       </c>
-      <c r="O29" s="55">
+      <c r="O29" s="52">
         <f t="shared" si="1"/>
         <v>0.29061901778967991</v>
       </c>
-      <c r="P29" s="56">
+      <c r="P29" s="53">
         <f t="shared" si="2"/>
         <v>0.258928386534368</v>
       </c>
-      <c r="Q29" s="56">
+      <c r="Q29" s="53">
         <f t="shared" si="3"/>
         <v>0.24008233686758437</v>
       </c>
-      <c r="R29" s="56">
+      <c r="R29" s="53">
         <f t="shared" si="4"/>
         <v>0.16232599444712634</v>
       </c>
-      <c r="S29" s="56">
+      <c r="S29" s="53">
         <f t="shared" si="5"/>
         <v>0.19145909227245464</v>
       </c>
-      <c r="T29" s="56">
+      <c r="T29" s="53">
         <f t="shared" si="6"/>
         <v>0.29577104650655778</v>
       </c>
-      <c r="U29" s="56">
+      <c r="U29" s="53">
         <f t="shared" si="7"/>
         <v>0.16840242772650094</v>
       </c>
-      <c r="V29" s="56">
+      <c r="V29" s="53">
         <f t="shared" si="8"/>
         <v>0.10798087700325019</v>
       </c>
-      <c r="W29" s="56">
+      <c r="W29" s="53">
         <f t="shared" si="9"/>
         <v>0.37729375647126728</v>
       </c>
-      <c r="X29" s="56">
+      <c r="X29" s="53">
         <f t="shared" si="10"/>
         <v>0.27478899610208068</v>
       </c>
-      <c r="Y29" s="57">
+      <c r="Y29" s="54">
         <f t="shared" si="11"/>
         <v>0.43572188911399995</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AB29" s="63">
+      <c r="AB29" s="60">
         <f>O29*'R17'!N$24</f>
         <v>10316.340983109594</v>
       </c>
-      <c r="AC29" s="63">
+      <c r="AC29" s="60">
         <f>P29*'R17'!O$24</f>
         <v>15116.026526077989</v>
       </c>
-      <c r="AD29" s="63">
+      <c r="AD29" s="60">
         <f>Q29*'R17'!P$24</f>
         <v>12122.850892565462</v>
       </c>
-      <c r="AE29" s="63">
+      <c r="AE29" s="60">
         <f>R29*'R17'!Q$24</f>
         <v>2743.5712632985892</v>
       </c>
-      <c r="AF29" s="63">
+      <c r="AF29" s="60">
         <f>S29*'R17'!R$24</f>
         <v>2674.7563997171155</v>
       </c>
-      <c r="AG29" s="63">
+      <c r="AG29" s="60">
         <f>T29*'R17'!S$24</f>
         <v>11760.851175260206</v>
       </c>
-      <c r="AH29" s="63">
+      <c r="AH29" s="60">
         <f>U29*'R17'!T$24</f>
         <v>7277.6717554455699</v>
       </c>
-      <c r="AI29" s="63">
+      <c r="AI29" s="60">
         <f>V29*'R17'!U$24</f>
         <v>1970.8292944336067</v>
       </c>
-      <c r="AJ29" s="63">
+      <c r="AJ29" s="60">
         <f>W29*'R17'!V$24</f>
         <v>59911.575384036485</v>
       </c>
-      <c r="AK29" s="63">
+      <c r="AK29" s="60">
         <f>X29*'R17'!W$24</f>
         <v>15468.908921669681</v>
       </c>
-      <c r="AL29" s="63">
+      <c r="AL29" s="60">
         <f>Y29*'R17'!X$24</f>
         <v>1301.1884673955074</v>
       </c>
@@ -18289,130 +18289,130 @@
       <c r="A30" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="61">
+      <c r="B30" s="58">
         <v>19.385200000000001</v>
       </c>
-      <c r="C30" s="61">
+      <c r="C30" s="58">
         <v>7.3518299999999996</v>
       </c>
-      <c r="D30" s="61">
+      <c r="D30" s="58">
         <v>16.027699999999999</v>
       </c>
-      <c r="E30" s="61">
+      <c r="E30" s="58">
         <v>1.5607500000000001</v>
       </c>
-      <c r="F30" s="61">
+      <c r="F30" s="58">
         <v>0.59164600000000001</v>
       </c>
-      <c r="G30" s="61">
+      <c r="G30" s="58">
         <v>2.9831099999999999</v>
       </c>
-      <c r="H30" s="61">
+      <c r="H30" s="58">
         <v>2.3904100000000001</v>
       </c>
-      <c r="I30" s="61">
+      <c r="I30" s="58">
         <v>0.25218299999999999</v>
       </c>
-      <c r="J30" s="61">
+      <c r="J30" s="58">
         <v>9.5821799999999993</v>
       </c>
-      <c r="K30" s="61">
+      <c r="K30" s="58">
         <v>2.9182299999999999</v>
       </c>
-      <c r="L30" s="61">
+      <c r="L30" s="58">
         <v>2.15089</v>
       </c>
       <c r="N30" t="s">
         <v>45</v>
       </c>
-      <c r="O30" s="52">
+      <c r="O30" s="49">
         <f>B30/SUM(B$30:B$33)</f>
         <v>2.4470954530171132E-2</v>
       </c>
-      <c r="P30" s="53">
+      <c r="P30" s="50">
         <f t="shared" ref="P30:Y33" si="12">C30/SUM(C$30:C$33)</f>
         <v>5.2186247227372924E-2</v>
       </c>
-      <c r="Q30" s="53">
+      <c r="Q30" s="50">
         <f t="shared" si="12"/>
         <v>3.6040543447060973E-2</v>
       </c>
-      <c r="R30" s="53">
+      <c r="R30" s="50">
         <f t="shared" si="12"/>
         <v>6.02391314625342E-2</v>
       </c>
-      <c r="S30" s="53">
+      <c r="S30" s="50">
         <f t="shared" si="12"/>
         <v>4.7977458510651709E-2</v>
       </c>
-      <c r="T30" s="53">
+      <c r="T30" s="50">
         <f t="shared" si="12"/>
         <v>4.248877503766698E-2</v>
       </c>
-      <c r="U30" s="53">
+      <c r="U30" s="50">
         <f t="shared" si="12"/>
         <v>4.8976315489746056E-2</v>
       </c>
-      <c r="V30" s="53">
+      <c r="V30" s="50">
         <f t="shared" si="12"/>
         <v>3.8039079085122308E-2</v>
       </c>
-      <c r="W30" s="53">
+      <c r="W30" s="50">
         <f t="shared" si="12"/>
         <v>0.10412802712293981</v>
       </c>
-      <c r="X30" s="53">
+      <c r="X30" s="50">
         <f t="shared" si="12"/>
         <v>4.088411386625624E-2</v>
       </c>
-      <c r="Y30" s="54">
+      <c r="Y30" s="51">
         <f t="shared" si="12"/>
         <v>3.5603701564012713E-2</v>
       </c>
       <c r="AA30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AB30" s="63">
+      <c r="AB30" s="60">
         <f>O30*'R17'!N$25</f>
         <v>3503.8434487738887</v>
       </c>
-      <c r="AC30" s="63">
+      <c r="AC30" s="60">
         <f>P30*'R17'!O$25</f>
         <v>9722.3484401190181</v>
       </c>
-      <c r="AD30" s="63">
+      <c r="AD30" s="60">
         <f>Q30*'R17'!P$25</f>
         <v>5945.5716199329108</v>
       </c>
-      <c r="AE30" s="63">
+      <c r="AE30" s="60">
         <f>R30*'R17'!Q$25</f>
         <v>1893.9582655899351</v>
       </c>
-      <c r="AF30" s="63">
+      <c r="AF30" s="60">
         <f>S30*'R17'!R$25</f>
         <v>1629.9755548809092</v>
       </c>
-      <c r="AG30" s="63">
+      <c r="AG30" s="60">
         <f>T30*'R17'!S$25</f>
         <v>3610.3300190430668</v>
       </c>
-      <c r="AH30" s="63">
+      <c r="AH30" s="60">
         <f>U30*'R17'!T$25</f>
         <v>6960.6572258488786</v>
       </c>
-      <c r="AI30" s="63">
+      <c r="AI30" s="60">
         <f>V30*'R17'!U$25</f>
         <v>906.60150365185336</v>
       </c>
-      <c r="AJ30" s="63">
+      <c r="AJ30" s="60">
         <f>W30*'R17'!V$25</f>
         <v>23661.278142146552</v>
       </c>
-      <c r="AK30" s="63">
+      <c r="AK30" s="60">
         <f>X30*'R17'!W$25</f>
         <v>5402.6774827575637</v>
       </c>
-      <c r="AL30" s="63">
+      <c r="AL30" s="60">
         <f>Y30*'R17'!X$25</f>
         <v>431.87128955562127</v>
       </c>
@@ -18421,130 +18421,130 @@
       <c r="A31" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="61">
+      <c r="B31" s="58">
         <v>0.68539600000000001</v>
       </c>
-      <c r="C31" s="61">
+      <c r="C31" s="58">
         <v>0.379388</v>
       </c>
-      <c r="D31" s="61">
+      <c r="D31" s="58">
         <v>1.93127</v>
       </c>
-      <c r="E31" s="61">
+      <c r="E31" s="58">
         <v>6.7693100000000006E-2</v>
       </c>
-      <c r="F31" s="61">
+      <c r="F31" s="58">
         <v>6.2010799999999998E-2</v>
       </c>
-      <c r="G31" s="61">
+      <c r="G31" s="58">
         <v>0.31239899999999998</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H31" s="58">
         <v>0.15324299999999999</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="58">
         <v>8.0850900000000003E-2</v>
       </c>
-      <c r="J31" s="61">
+      <c r="J31" s="58">
         <v>0.35387000000000002</v>
       </c>
-      <c r="K31" s="61">
+      <c r="K31" s="58">
         <v>1.04043</v>
       </c>
-      <c r="L31" s="61">
+      <c r="L31" s="58">
         <v>0.151444</v>
       </c>
       <c r="N31" t="s">
         <v>46</v>
       </c>
-      <c r="O31" s="55">
+      <c r="O31" s="52">
         <f t="shared" ref="O31:O33" si="13">B31/SUM(B$30:B$33)</f>
         <v>8.6521131332981723E-4</v>
       </c>
-      <c r="P31" s="56">
+      <c r="P31" s="53">
         <f t="shared" si="12"/>
         <v>2.6930486644955827E-3</v>
       </c>
-      <c r="Q31" s="56">
+      <c r="Q31" s="53">
         <f t="shared" si="12"/>
         <v>4.3427329150786112E-3</v>
       </c>
-      <c r="R31" s="56">
+      <c r="R31" s="53">
         <f t="shared" si="12"/>
         <v>2.6127012974572956E-3</v>
       </c>
-      <c r="S31" s="56">
+      <c r="S31" s="53">
         <f t="shared" si="12"/>
         <v>5.0285484634601113E-3</v>
       </c>
-      <c r="T31" s="56">
+      <c r="T31" s="53">
         <f t="shared" si="12"/>
         <v>4.4495344901770723E-3</v>
       </c>
-      <c r="U31" s="56">
+      <c r="U31" s="53">
         <f t="shared" si="12"/>
         <v>3.1397448615907535E-3</v>
       </c>
-      <c r="V31" s="56">
+      <c r="V31" s="53">
         <f t="shared" si="12"/>
         <v>1.2195484149222254E-2</v>
       </c>
-      <c r="W31" s="56">
+      <c r="W31" s="53">
         <f t="shared" si="12"/>
         <v>3.8454490479196504E-3</v>
       </c>
-      <c r="X31" s="56">
+      <c r="X31" s="53">
         <f t="shared" si="12"/>
         <v>1.4576321465363931E-2</v>
       </c>
-      <c r="Y31" s="57">
+      <c r="Y31" s="54">
         <f t="shared" si="12"/>
         <v>2.5068538975309483E-3</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AB31" s="63">
+      <c r="AB31" s="60">
         <f>O31*'R17'!N$25</f>
         <v>123.88421498957082</v>
       </c>
-      <c r="AC31" s="63">
+      <c r="AC31" s="60">
         <f>P31*'R17'!O$25</f>
         <v>501.71757644013445</v>
       </c>
-      <c r="AD31" s="63">
+      <c r="AD31" s="60">
         <f>Q31*'R17'!P$25</f>
         <v>716.41621083672851</v>
       </c>
-      <c r="AE31" s="63">
+      <c r="AE31" s="60">
         <f>R31*'R17'!Q$25</f>
         <v>82.145062481759439</v>
       </c>
-      <c r="AF31" s="63">
+      <c r="AF31" s="60">
         <f>S31*'R17'!R$25</f>
         <v>170.83879234983266</v>
       </c>
-      <c r="AG31" s="63">
+      <c r="AG31" s="60">
         <f>T31*'R17'!S$25</f>
         <v>378.08310374710788</v>
       </c>
-      <c r="AH31" s="63">
+      <c r="AH31" s="60">
         <f>U31*'R17'!T$25</f>
         <v>446.22972429865985</v>
       </c>
-      <c r="AI31" s="63">
+      <c r="AI31" s="60">
         <f>V31*'R17'!U$25</f>
         <v>290.66014565456686</v>
       </c>
-      <c r="AJ31" s="63">
+      <c r="AJ31" s="60">
         <f>W31*'R17'!V$25</f>
         <v>873.81123044666253</v>
       </c>
-      <c r="AK31" s="63">
+      <c r="AK31" s="60">
         <f>X31*'R17'!W$25</f>
         <v>1926.204491553254</v>
       </c>
-      <c r="AL31" s="63">
+      <c r="AL31" s="60">
         <f>Y31*'R17'!X$25</f>
         <v>30.40802438779366</v>
       </c>
@@ -18553,130 +18553,130 @@
       <c r="A32" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="61">
+      <c r="B32" s="58">
         <v>4.4791999999999996</v>
       </c>
-      <c r="C32" s="61">
+      <c r="C32" s="58">
         <v>0.54055299999999995</v>
       </c>
-      <c r="D32" s="61">
+      <c r="D32" s="58">
         <v>1.8870800000000001</v>
       </c>
-      <c r="E32" s="61">
+      <c r="E32" s="58">
         <v>0.13969500000000001</v>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="58">
         <v>7.2492699999999993E-2</v>
       </c>
-      <c r="G32" s="61">
+      <c r="G32" s="58">
         <v>0.46085799999999999</v>
       </c>
-      <c r="H32" s="61">
+      <c r="H32" s="58">
         <v>0.31601600000000002</v>
       </c>
-      <c r="I32" s="61">
+      <c r="I32" s="58">
         <v>0.130243</v>
       </c>
-      <c r="J32" s="61">
+      <c r="J32" s="58">
         <v>0.33181300000000002</v>
       </c>
-      <c r="K32" s="61">
+      <c r="K32" s="58">
         <v>0.87183100000000002</v>
       </c>
-      <c r="L32" s="61">
+      <c r="L32" s="58">
         <v>0.47914299999999999</v>
       </c>
       <c r="N32" t="s">
         <v>47</v>
       </c>
-      <c r="O32" s="55">
+      <c r="O32" s="52">
         <f t="shared" si="13"/>
         <v>5.6543290516240493E-3</v>
       </c>
-      <c r="P32" s="56">
+      <c r="P32" s="53">
         <f t="shared" si="12"/>
         <v>3.8370626765714269E-3</v>
       </c>
-      <c r="Q32" s="56">
+      <c r="Q32" s="53">
         <f t="shared" si="12"/>
         <v>4.243365469036719E-3</v>
       </c>
-      <c r="R32" s="56">
+      <c r="R32" s="53">
         <f t="shared" si="12"/>
         <v>5.3917062115385016E-3</v>
       </c>
-      <c r="S32" s="56">
+      <c r="S32" s="53">
         <f t="shared" si="12"/>
         <v>5.8785414024182039E-3</v>
       </c>
-      <c r="T32" s="56">
+      <c r="T32" s="53">
         <f t="shared" si="12"/>
         <v>6.5640529133384725E-3</v>
       </c>
-      <c r="U32" s="56">
+      <c r="U32" s="53">
         <f t="shared" si="12"/>
         <v>6.4747467237032926E-3</v>
       </c>
-      <c r="V32" s="56">
+      <c r="V32" s="53">
         <f t="shared" si="12"/>
         <v>1.9645748433810308E-2</v>
       </c>
-      <c r="W32" s="56">
+      <c r="W32" s="53">
         <f t="shared" si="12"/>
         <v>3.6057591345334812E-3</v>
       </c>
-      <c r="X32" s="56">
+      <c r="X32" s="53">
         <f t="shared" si="12"/>
         <v>1.221426613945167E-2</v>
       </c>
-      <c r="Y32" s="57">
+      <c r="Y32" s="54">
         <f t="shared" si="12"/>
         <v>7.931258399307143E-3</v>
       </c>
       <c r="AA32" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AB32" s="63">
+      <c r="AB32" s="60">
         <f>O32*'R17'!N$25</f>
         <v>809.60813278934449</v>
       </c>
-      <c r="AC32" s="63">
+      <c r="AC32" s="60">
         <f>P32*'R17'!O$25</f>
         <v>714.84849572849953</v>
       </c>
-      <c r="AD32" s="63">
+      <c r="AD32" s="60">
         <f>Q32*'R17'!P$25</f>
         <v>700.02366481422769</v>
       </c>
-      <c r="AE32" s="63">
+      <c r="AE32" s="60">
         <f>R32*'R17'!Q$25</f>
         <v>169.51882102296076</v>
       </c>
-      <c r="AF32" s="63">
+      <c r="AF32" s="60">
         <f>S32*'R17'!R$25</f>
         <v>199.71626429877878</v>
       </c>
-      <c r="AG32" s="63">
+      <c r="AG32" s="60">
         <f>T32*'R17'!S$25</f>
         <v>557.75666063810922</v>
       </c>
-      <c r="AH32" s="63">
+      <c r="AH32" s="60">
         <f>U32*'R17'!T$25</f>
         <v>920.20994468892741</v>
       </c>
-      <c r="AI32" s="63">
+      <c r="AI32" s="60">
         <f>V32*'R17'!U$25</f>
         <v>468.22545389708404</v>
       </c>
-      <c r="AJ32" s="63">
+      <c r="AJ32" s="60">
         <f>W32*'R17'!V$25</f>
         <v>819.34587788792055</v>
       </c>
-      <c r="AK32" s="63">
+      <c r="AK32" s="60">
         <f>X32*'R17'!W$25</f>
         <v>1614.0680181034427</v>
       </c>
-      <c r="AL32" s="63">
+      <c r="AL32" s="60">
         <f>Y32*'R17'!X$25</f>
         <v>96.205805639316281</v>
       </c>
@@ -18685,220 +18685,220 @@
       <c r="A33" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="61">
+      <c r="B33" s="58">
         <v>767.62199999999996</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="58">
         <v>132.60499999999999</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="58">
         <v>424.86700000000002</v>
       </c>
-      <c r="E33" s="61">
+      <c r="E33" s="58">
         <v>24.141100000000002</v>
       </c>
-      <c r="F33" s="61">
+      <c r="F33" s="58">
         <v>11.605600000000001</v>
       </c>
-      <c r="G33" s="61">
+      <c r="G33" s="58">
         <v>66.453000000000003</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="58">
         <v>45.947800000000001</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="58">
         <v>6.1662999999999997</v>
       </c>
-      <c r="J33" s="61">
+      <c r="J33" s="58">
         <v>81.755200000000002</v>
       </c>
-      <c r="K33" s="61">
+      <c r="K33" s="58">
         <v>66.547600000000003</v>
       </c>
-      <c r="L33" s="61">
+      <c r="L33" s="58">
         <v>57.630499999999998</v>
       </c>
       <c r="N33" t="s">
         <v>48</v>
       </c>
-      <c r="O33" s="58">
+      <c r="O33" s="55">
         <f t="shared" si="13"/>
         <v>0.96900950510487494</v>
       </c>
-      <c r="P33" s="59">
+      <c r="P33" s="56">
         <f t="shared" si="12"/>
         <v>0.94128364143156007</v>
       </c>
-      <c r="Q33" s="59">
+      <c r="Q33" s="56">
         <f t="shared" si="12"/>
         <v>0.95537335816882374</v>
       </c>
-      <c r="R33" s="59">
+      <c r="R33" s="56">
         <f t="shared" si="12"/>
         <v>0.93175646102846998</v>
       </c>
-      <c r="S33" s="59">
+      <c r="S33" s="56">
         <f t="shared" si="12"/>
         <v>0.94111545162346999</v>
       </c>
-      <c r="T33" s="59">
+      <c r="T33" s="56">
         <f t="shared" si="12"/>
         <v>0.94649763755881755</v>
       </c>
-      <c r="U33" s="59">
+      <c r="U33" s="56">
         <f t="shared" si="12"/>
         <v>0.94140919292495995</v>
       </c>
-      <c r="V33" s="59">
+      <c r="V33" s="56">
         <f t="shared" si="12"/>
         <v>0.93011968833184511</v>
       </c>
-      <c r="W33" s="59">
+      <c r="W33" s="56">
         <f t="shared" si="12"/>
         <v>0.88842076469460696</v>
       </c>
-      <c r="X33" s="59">
+      <c r="X33" s="56">
         <f t="shared" si="12"/>
         <v>0.9323252985289282</v>
       </c>
-      <c r="Y33" s="60">
+      <c r="Y33" s="57">
         <f t="shared" si="12"/>
         <v>0.95395818613914918</v>
       </c>
       <c r="AA33" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AB33" s="63">
+      <c r="AB33" s="60">
         <f>O33*'R17'!N$25</f>
         <v>138746.43108323409</v>
       </c>
-      <c r="AC33" s="63">
+      <c r="AC33" s="60">
         <f>P33*'R17'!O$25</f>
         <v>175362.05474038195</v>
       </c>
-      <c r="AD33" s="63">
+      <c r="AD33" s="60">
         <f>Q33*'R17'!P$25</f>
         <v>157606.96652957294</v>
       </c>
-      <c r="AE33" s="63">
+      <c r="AE33" s="60">
         <f>R33*'R17'!Q$25</f>
         <v>29295.041413059866</v>
       </c>
-      <c r="AF33" s="63">
+      <c r="AF33" s="60">
         <f>S33*'R17'!R$25</f>
         <v>31973.248022847922</v>
       </c>
-      <c r="AG33" s="63">
+      <c r="AG33" s="60">
         <f>T33*'R17'!S$25</f>
         <v>80425.214207812969</v>
       </c>
-      <c r="AH33" s="63">
+      <c r="AH33" s="60">
         <f>U33*'R17'!T$25</f>
         <v>133795.82836494956</v>
       </c>
-      <c r="AI33" s="63">
+      <c r="AI33" s="60">
         <f>V33*'R17'!U$25</f>
         <v>22167.936982145598</v>
       </c>
-      <c r="AJ33" s="63">
+      <c r="AJ33" s="60">
         <f>W33*'R17'!V$25</f>
         <v>201878.12447343086</v>
       </c>
-      <c r="AK33" s="63">
+      <c r="AK33" s="60">
         <f>X33*'R17'!W$25</f>
         <v>123203.18139816164</v>
       </c>
-      <c r="AL33" s="63">
+      <c r="AL33" s="60">
         <f>Y33*'R17'!X$25</f>
         <v>11571.469648719938</v>
       </c>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="B34" s="61">
+      <c r="B34" s="58">
         <f t="shared" ref="B34:L34" si="14">SUM(B3:B33)</f>
         <v>991.60064929999999</v>
       </c>
-      <c r="C34" s="61">
+      <c r="C34" s="58">
         <f t="shared" si="14"/>
         <v>199.64107011999999</v>
       </c>
-      <c r="D34" s="61">
+      <c r="D34" s="58">
         <f t="shared" si="14"/>
         <v>607.23520780000013</v>
       </c>
-      <c r="E34" s="61">
+      <c r="E34" s="58">
         <f t="shared" si="14"/>
         <v>40.579709800000003</v>
       </c>
-      <c r="F34" s="61">
+      <c r="F34" s="58">
         <f t="shared" si="14"/>
         <v>21.739290560000001</v>
       </c>
-      <c r="G34" s="61">
+      <c r="G34" s="58">
         <f t="shared" si="14"/>
         <v>118.54155309000001</v>
       </c>
-      <c r="H34" s="61">
+      <c r="H34" s="58">
         <f t="shared" si="14"/>
         <v>76.228799100000003</v>
       </c>
-      <c r="I34" s="61">
+      <c r="I34" s="58">
         <f t="shared" si="14"/>
         <v>17.549455200300002</v>
       </c>
-      <c r="J34" s="61">
+      <c r="J34" s="58">
         <f t="shared" si="14"/>
         <v>172.50149255999997</v>
       </c>
-      <c r="K34" s="61">
+      <c r="K34" s="58">
         <f t="shared" si="14"/>
         <v>112.23911552999999</v>
       </c>
-      <c r="L34" s="61">
+      <c r="L34" s="58">
         <f t="shared" si="14"/>
         <v>77.69961839186</v>
       </c>
-      <c r="AB34" s="62">
+      <c r="AB34" s="59">
         <f>SUM(AB3:AB33)</f>
         <v>181695.32980715769</v>
       </c>
-      <c r="AC34" s="62">
+      <c r="AC34" s="59">
         <f t="shared" ref="AC34:AL34" si="15">SUM(AC3:AC33)</f>
         <v>285293.17666228832</v>
       </c>
-      <c r="AD34" s="62">
+      <c r="AD34" s="59">
         <f t="shared" si="15"/>
         <v>225598.22227962775</v>
       </c>
-      <c r="AE34" s="62">
+      <c r="AE34" s="59">
         <f t="shared" si="15"/>
         <v>54001.999837082825</v>
       </c>
-      <c r="AF34" s="62">
+      <c r="AF34" s="59">
         <f t="shared" si="15"/>
         <v>61956.65219606772</v>
       </c>
-      <c r="AG34" s="62">
+      <c r="AG34" s="59">
         <f t="shared" si="15"/>
         <v>150770.8579729686</v>
       </c>
-      <c r="AH34" s="62">
+      <c r="AH34" s="59">
         <f t="shared" si="15"/>
         <v>389064.21990996471</v>
       </c>
-      <c r="AI34" s="62">
+      <c r="AI34" s="59">
         <f t="shared" si="15"/>
         <v>66421.000920187042</v>
       </c>
-      <c r="AJ34" s="62">
+      <c r="AJ34" s="59">
         <f t="shared" si="15"/>
         <v>646037.71145525156</v>
       </c>
-      <c r="AK34" s="62">
+      <c r="AK34" s="59">
         <f t="shared" si="15"/>
         <v>263333.56015667989</v>
       </c>
-      <c r="AL34" s="62">
+      <c r="AL34" s="59">
         <f t="shared" si="15"/>
         <v>15604.232381689373</v>
       </c>
@@ -19880,127 +19880,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="65" t="s">
+      <c r="L1" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="65" t="s">
+      <c r="N1" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="65" t="s">
+      <c r="O1" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="R1" s="65" t="s">
-        <v>89</v>
+      <c r="Q1" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="62" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="66">
+      <c r="B2" s="63">
         <f>Employment_NEA!Z2</f>
         <v>1394.9179999999999</v>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="63">
         <f>Employment_NEA!AA2</f>
         <v>182943.04044704448</v>
       </c>
-      <c r="D2" s="66">
+      <c r="D2" s="63">
         <f>Employment_NEA!AB2</f>
         <v>2180.4499999999998</v>
       </c>
-      <c r="E2" s="66">
+      <c r="E2" s="63">
         <f>Employment_NEA!AC2</f>
         <v>4131.2960000000003</v>
       </c>
-      <c r="F2" s="66">
+      <c r="F2" s="63">
         <f>Employment_NEA!AD2</f>
         <v>330.05099999999999</v>
       </c>
-      <c r="G2" s="66">
+      <c r="G2" s="63">
         <f>Employment_NEA!AE2</f>
         <v>6849.611337138288</v>
       </c>
-      <c r="H2" s="66">
+      <c r="H2" s="63">
         <f>Employment_R11!AB3</f>
         <v>3013.7449883689551</v>
       </c>
-      <c r="I2" s="66">
+      <c r="I2" s="63">
         <f>Employment_R11!AC3</f>
         <v>40613.028794254271</v>
       </c>
-      <c r="J2" s="66">
+      <c r="J2" s="63">
         <f>Employment_R11!AD3</f>
         <v>10134.688716835852</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="63">
         <f>Employment_R11!AE3</f>
         <v>5659.7225029440533</v>
       </c>
-      <c r="L2" s="66">
+      <c r="L2" s="63">
         <f>Employment_R11!AF3</f>
         <v>14012.492902458791</v>
       </c>
-      <c r="M2" s="66">
+      <c r="M2" s="63">
         <f>Employment_R11!AG3</f>
         <v>26036.1120361576</v>
       </c>
-      <c r="N2" s="66">
+      <c r="N2" s="63">
         <f>Employment_R11!AH3</f>
         <v>203725.33954966738</v>
       </c>
-      <c r="O2" s="66">
+      <c r="O2" s="63">
         <f>Employment_R11!AI3</f>
         <v>24335.925717258258</v>
       </c>
-      <c r="P2" s="66">
+      <c r="P2" s="63">
         <f>Employment_R11!AJ3</f>
         <v>260012.23677728849</v>
       </c>
-      <c r="Q2" s="66">
+      <c r="Q2" s="63">
         <f>Employment_R11!AK3</f>
         <v>74893.657395713381</v>
       </c>
-      <c r="R2" s="66">
+      <c r="R2" s="63">
         <f>Employment_R11!AL3</f>
         <v>487.99553781470706</v>
       </c>
@@ -20009,71 +20009,71 @@
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="66">
+      <c r="B3" s="63">
         <f>Employment_NEA!Z3</f>
         <v>0.3029869442533869</v>
       </c>
-      <c r="C3" s="66">
+      <c r="C3" s="63">
         <f>Employment_NEA!AA3</f>
         <v>3842.3183315920678</v>
       </c>
-      <c r="D3" s="66">
+      <c r="D3" s="63">
         <f>Employment_NEA!AB3</f>
         <v>0.11028650332494723</v>
       </c>
-      <c r="E3" s="66">
+      <c r="E3" s="63">
         <f>Employment_NEA!AC3</f>
         <v>166.58809437003262</v>
       </c>
-      <c r="F3" s="66">
+      <c r="F3" s="63">
         <f>Employment_NEA!AD3</f>
         <v>27.191600817785535</v>
       </c>
-      <c r="G3" s="66">
+      <c r="G3" s="63">
         <f>Employment_NEA!AE3</f>
         <v>13.399308477760645</v>
       </c>
-      <c r="H3" s="66">
+      <c r="H3" s="63">
         <f>Employment_R11!AB4</f>
         <v>102.54092334959473</v>
       </c>
-      <c r="I3" s="66">
+      <c r="I3" s="63">
         <f>Employment_R11!AC4</f>
         <v>59.399808617589187</v>
       </c>
-      <c r="J3" s="66">
+      <c r="J3" s="63">
         <f>Employment_R11!AD4</f>
         <v>51.574502859013698</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="63">
         <f>Employment_R11!AE4</f>
         <v>246.91789785039927</v>
       </c>
-      <c r="L3" s="66">
+      <c r="L3" s="63">
         <f>Employment_R11!AF4</f>
         <v>366.63989166155545</v>
       </c>
-      <c r="M3" s="66">
+      <c r="M3" s="63">
         <f>Employment_R11!AG4</f>
         <v>5.6035149310321959</v>
       </c>
-      <c r="N3" s="66">
+      <c r="N3" s="63">
         <f>Employment_R11!AH4</f>
         <v>556.36923516670311</v>
       </c>
-      <c r="O3" s="66">
+      <c r="O3" s="63">
         <f>Employment_R11!AI4</f>
         <v>180.66051618852265</v>
       </c>
-      <c r="P3" s="66">
+      <c r="P3" s="63">
         <f>Employment_R11!AJ4</f>
         <v>1717.7207377805842</v>
       </c>
-      <c r="Q3" s="66">
+      <c r="Q3" s="63">
         <f>Employment_R11!AK4</f>
         <v>438.87430807301371</v>
       </c>
-      <c r="R3" s="66">
+      <c r="R3" s="63">
         <f>Employment_R11!AL4</f>
         <v>65.255093832988194</v>
       </c>
@@ -20082,71 +20082,71 @@
       <c r="A4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="66">
+      <c r="B4" s="63">
         <f>Employment_NEA!Z4</f>
         <v>0.12803021164921635</v>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="63">
         <f>Employment_NEA!AA4</f>
         <v>631.62524982208163</v>
       </c>
-      <c r="D4" s="66">
+      <c r="D4" s="63">
         <f>Employment_NEA!AB4</f>
         <v>0.17236411978258104</v>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="63">
         <f>Employment_NEA!AC4</f>
         <v>343.77866577292599</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="63">
         <f>Employment_NEA!AD4</f>
         <v>0.84783845785409806</v>
       </c>
-      <c r="G4" s="66">
+      <c r="G4" s="63">
         <f>Employment_NEA!AE4</f>
         <v>0.10277343979361128</v>
       </c>
-      <c r="H4" s="66">
+      <c r="H4" s="63">
         <f>Employment_R11!AB5</f>
         <v>266.1227408089697</v>
       </c>
-      <c r="I4" s="66">
+      <c r="I4" s="63">
         <f>Employment_R11!AC5</f>
         <v>993.16360912492166</v>
       </c>
-      <c r="J4" s="66">
+      <c r="J4" s="63">
         <f>Employment_R11!AD5</f>
         <v>75.381537097773275</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="63">
         <f>Employment_R11!AE5</f>
         <v>60.54665255726016</v>
       </c>
-      <c r="L4" s="66">
+      <c r="L4" s="63">
         <f>Employment_R11!AF5</f>
         <v>1464.5225016840211</v>
       </c>
-      <c r="M4" s="66">
+      <c r="M4" s="63">
         <f>Employment_R11!AG5</f>
         <v>3685.4507741648149</v>
       </c>
-      <c r="N4" s="66">
+      <c r="N4" s="63">
         <f>Employment_R11!AH5</f>
         <v>409.63843041254307</v>
       </c>
-      <c r="O4" s="66">
+      <c r="O4" s="63">
         <f>Employment_R11!AI5</f>
         <v>56.49894211901529</v>
       </c>
-      <c r="P4" s="66">
+      <c r="P4" s="63">
         <f>Employment_R11!AJ5</f>
         <v>489.48633529068934</v>
       </c>
-      <c r="Q4" s="66">
+      <c r="Q4" s="63">
         <f>Employment_R11!AK5</f>
         <v>645.60420658125554</v>
       </c>
-      <c r="R4" s="66">
+      <c r="R4" s="63">
         <f>Employment_R11!AL5</f>
         <v>5.4067685381219324</v>
       </c>
@@ -20155,71 +20155,71 @@
       <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="66">
+      <c r="B5" s="63">
         <f>Employment_NEA!Z5</f>
         <v>7.099402473890018E-2</v>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="63">
         <f>Employment_NEA!AA5</f>
         <v>24.856893868046186</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="63">
         <f>Employment_NEA!AB5</f>
         <v>1.39623688229558</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="63">
         <f>Employment_NEA!AC5</f>
         <v>561.51598110337534</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="63">
         <f>Employment_NEA!AD5</f>
         <v>6.5498463947811933E-2</v>
       </c>
-      <c r="G5" s="66">
+      <c r="G5" s="63">
         <f>Employment_NEA!AE5</f>
         <v>0.17442000581366568</v>
       </c>
-      <c r="H5" s="66">
+      <c r="H5" s="63">
         <f>Employment_R11!AB6</f>
         <v>215.22958596264581</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="63">
         <f>Employment_R11!AC6</f>
         <v>327.33691800234396</v>
       </c>
-      <c r="J5" s="66">
+      <c r="J5" s="63">
         <f>Employment_R11!AD6</f>
         <v>84.887448129671881</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="63">
         <f>Employment_R11!AE6</f>
         <v>64.9466693108713</v>
       </c>
-      <c r="L5" s="66">
+      <c r="L5" s="63">
         <f>Employment_R11!AF6</f>
         <v>769.78441146620435</v>
       </c>
-      <c r="M5" s="66">
+      <c r="M5" s="63">
         <f>Employment_R11!AG6</f>
         <v>1090.4161196389391</v>
       </c>
-      <c r="N5" s="66">
+      <c r="N5" s="63">
         <f>Employment_R11!AH6</f>
         <v>133.52463409142754</v>
       </c>
-      <c r="O5" s="66">
+      <c r="O5" s="63">
         <f>Employment_R11!AI6</f>
         <v>319.66269537026812</v>
       </c>
-      <c r="P5" s="66">
+      <c r="P5" s="63">
         <f>Employment_R11!AJ6</f>
         <v>587.37306523051802</v>
       </c>
-      <c r="Q5" s="66">
+      <c r="Q5" s="63">
         <f>Employment_R11!AK6</f>
         <v>695.81544091507067</v>
       </c>
-      <c r="R5" s="66">
+      <c r="R5" s="63">
         <f>Employment_R11!AL6</f>
         <v>44.234741780530129</v>
       </c>
@@ -20228,71 +20228,71 @@
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="66">
+      <c r="B6" s="63">
         <f>Employment_NEA!Z6</f>
         <v>13.999988819358496</v>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="63">
         <f>Employment_NEA!AA6</f>
         <v>4919.3437714450956</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="63">
         <f>Employment_NEA!AB6</f>
         <v>21.183112494596891</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="63">
         <f>Employment_NEA!AC6</f>
         <v>528.45125875366602</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="63">
         <f>Employment_NEA!AD6</f>
         <v>29.81806226041255</v>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="63">
         <f>Employment_NEA!AE6</f>
         <v>117.71333684931153</v>
       </c>
-      <c r="H6" s="66">
+      <c r="H6" s="63">
         <f>Employment_R11!AB7</f>
         <v>882.38063560291084</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="63">
         <f>Employment_R11!AC7</f>
         <v>1924.4940030345081</v>
       </c>
-      <c r="J6" s="66">
+      <c r="J6" s="63">
         <f>Employment_R11!AD7</f>
         <v>416.26316597602715</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="63">
         <f>Employment_R11!AE7</f>
         <v>273.59015093244045</v>
       </c>
-      <c r="L6" s="66">
+      <c r="L6" s="63">
         <f>Employment_R11!AF7</f>
         <v>738.79911631696541</v>
       </c>
-      <c r="M6" s="66">
+      <c r="M6" s="63">
         <f>Employment_R11!AG7</f>
         <v>888.4251585540967</v>
       </c>
-      <c r="N6" s="66">
+      <c r="N6" s="63">
         <f>Employment_R11!AH7</f>
         <v>2999.5283769571379</v>
       </c>
-      <c r="O6" s="66">
+      <c r="O6" s="63">
         <f>Employment_R11!AI7</f>
         <v>275.05886035208573</v>
       </c>
-      <c r="P6" s="66">
+      <c r="P6" s="63">
         <f>Employment_R11!AJ7</f>
         <v>2211.5644814073635</v>
       </c>
-      <c r="Q6" s="66">
+      <c r="Q6" s="63">
         <f>Employment_R11!AK7</f>
         <v>1724.5279569790366</v>
       </c>
-      <c r="R6" s="66">
+      <c r="R6" s="63">
         <f>Employment_R11!AL7</f>
         <v>251.52130702972659</v>
       </c>
@@ -20301,71 +20301,71 @@
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="63">
         <f>Employment_NEA!Z7</f>
         <v>247.44940499001945</v>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="63">
         <f>Employment_NEA!AA7</f>
         <v>18249.047147816731</v>
       </c>
-      <c r="D7" s="66">
+      <c r="D7" s="63">
         <f>Employment_NEA!AB7</f>
         <v>988.93617348272539</v>
       </c>
-      <c r="E7" s="66">
+      <c r="E7" s="63">
         <f>Employment_NEA!AC7</f>
         <v>1905.3582866061406</v>
       </c>
-      <c r="F7" s="66">
+      <c r="F7" s="63">
         <f>Employment_NEA!AD7</f>
         <v>18.00683872215771</v>
       </c>
-      <c r="G7" s="66">
+      <c r="G7" s="63">
         <f>Employment_NEA!AE7</f>
         <v>281.2762674796893</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="63">
         <f>Employment_R11!AB8</f>
         <v>2664.8748625104522</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="63">
         <f>Employment_R11!AC8</f>
         <v>9446.9893303643621</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="63">
         <f>Employment_R11!AD8</f>
         <v>4470.7211191101705</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="63">
         <f>Employment_R11!AE8</f>
         <v>1733.5076363553826</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="63">
         <f>Employment_R11!AF8</f>
         <v>1097.0522366207015</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="63">
         <f>Employment_R11!AG8</f>
         <v>4382.9587491215489</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="63">
         <f>Employment_R11!AH8</f>
         <v>16674.936830457198</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="63">
         <f>Employment_R11!AI8</f>
         <v>683.53490036704522</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="63">
         <f>Employment_R11!AJ8</f>
         <v>13375.601041000702</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="63">
         <f>Employment_R11!AK8</f>
         <v>6893.979040703266</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="63">
         <f>Employment_R11!AL8</f>
         <v>386.67088639322094</v>
       </c>
@@ -20374,71 +20374,71 @@
       <c r="A8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="66">
+      <c r="B8" s="63">
         <f>Employment_NEA!Z8</f>
         <v>139.00760303930852</v>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="63">
         <f>Employment_NEA!AA8</f>
         <v>16625.492281122595</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="63">
         <f>Employment_NEA!AB8</f>
         <v>253.94219382576895</v>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="63">
         <f>Employment_NEA!AC8</f>
         <v>289.82478303043928</v>
       </c>
-      <c r="F8" s="66">
+      <c r="F8" s="63">
         <f>Employment_NEA!AD8</f>
         <v>13.012450042523403</v>
       </c>
-      <c r="G8" s="66">
+      <c r="G8" s="63">
         <f>Employment_NEA!AE8</f>
         <v>294.5681426304194</v>
       </c>
-      <c r="H8" s="66">
+      <c r="H8" s="63">
         <f>Employment_R11!AB9</f>
         <v>490.88595381116932</v>
       </c>
-      <c r="I8" s="66">
+      <c r="I8" s="63">
         <f>Employment_R11!AC9</f>
         <v>3750.6964920545092</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="63">
         <f>Employment_R11!AD9</f>
         <v>1649.2323052411884</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="63">
         <f>Employment_R11!AE9</f>
         <v>1061.8845996353366</v>
       </c>
-      <c r="L8" s="66">
+      <c r="L8" s="63">
         <f>Employment_R11!AF9</f>
         <v>292.93806862325852</v>
       </c>
-      <c r="M8" s="66">
+      <c r="M8" s="63">
         <f>Employment_R11!AG9</f>
         <v>2150.5794284074177</v>
       </c>
-      <c r="N8" s="66">
+      <c r="N8" s="63">
         <f>Employment_R11!AH9</f>
         <v>2167.1659872057503</v>
       </c>
-      <c r="O8" s="66">
+      <c r="O8" s="63">
         <f>Employment_R11!AI9</f>
         <v>5367.1967053907356</v>
       </c>
-      <c r="P8" s="66">
+      <c r="P8" s="63">
         <f>Employment_R11!AJ9</f>
         <v>17865.405169492984</v>
       </c>
-      <c r="Q8" s="66">
+      <c r="Q8" s="63">
         <f>Employment_R11!AK9</f>
         <v>2189.667121931162</v>
       </c>
-      <c r="R8" s="66">
+      <c r="R8" s="63">
         <f>Employment_R11!AL9</f>
         <v>24.96632517256009</v>
       </c>
@@ -20447,71 +20447,71 @@
       <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="66">
+      <c r="B9" s="63">
         <f>Employment_NEA!Z9</f>
         <v>27.467590605835525</v>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="63">
         <f>Employment_NEA!AA9</f>
         <v>2559.6648499981829</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="63">
         <f>Employment_NEA!AB9</f>
         <v>95.862754510110634</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="63">
         <f>Employment_NEA!AC9</f>
         <v>289.15560296034369</v>
       </c>
-      <c r="F9" s="66">
+      <c r="F9" s="63">
         <f>Employment_NEA!AD9</f>
         <v>2.3729579470023348</v>
       </c>
-      <c r="G9" s="66">
+      <c r="G9" s="63">
         <f>Employment_NEA!AE9</f>
         <v>22.287128110738792</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="63">
         <f>Employment_R11!AB10</f>
         <v>393.78736742764431</v>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="63">
         <f>Employment_R11!AC10</f>
         <v>1004.4256356833429</v>
       </c>
-      <c r="J9" s="66">
+      <c r="J9" s="63">
         <f>Employment_R11!AD10</f>
         <v>634.85535984937314</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="63">
         <f>Employment_R11!AE10</f>
         <v>322.76903010782729</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="63">
         <f>Employment_R11!AF10</f>
         <v>112.5640049416336</v>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="63">
         <f>Employment_R11!AG10</f>
         <v>435.80791704507203</v>
       </c>
-      <c r="N9" s="66">
+      <c r="N9" s="63">
         <f>Employment_R11!AH10</f>
         <v>798.86615306732324</v>
       </c>
-      <c r="O9" s="66">
+      <c r="O9" s="63">
         <f>Employment_R11!AI10</f>
         <v>349.45792196513696</v>
       </c>
-      <c r="P9" s="66">
+      <c r="P9" s="63">
         <f>Employment_R11!AJ10</f>
         <v>491.06070473217846</v>
       </c>
-      <c r="Q9" s="66">
+      <c r="Q9" s="63">
         <f>Employment_R11!AK10</f>
         <v>820.95297125698244</v>
       </c>
-      <c r="R9" s="66">
+      <c r="R9" s="63">
         <f>Employment_R11!AL10</f>
         <v>67.655624665081334</v>
       </c>
@@ -20520,71 +20520,71 @@
       <c r="A10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="66">
+      <c r="B10" s="63">
         <f>Employment_NEA!Z10</f>
         <v>118.96618518262325</v>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="63">
         <f>Employment_NEA!AA10</f>
         <v>5808.3936245626001</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="63">
         <f>Employment_NEA!AB10</f>
         <v>535.93521620877971</v>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="63">
         <f>Employment_NEA!AC10</f>
         <v>289.09770951916494</v>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="63">
         <f>Employment_NEA!AD10</f>
         <v>3.0786144695781574E-5</v>
       </c>
-      <c r="G10" s="66">
+      <c r="G10" s="63">
         <f>Employment_NEA!AE10</f>
         <v>55.210599904067415</v>
       </c>
-      <c r="H10" s="66">
+      <c r="H10" s="63">
         <f>Employment_R11!AB11</f>
         <v>1172.6398477573837</v>
       </c>
-      <c r="I10" s="66">
+      <c r="I10" s="63">
         <f>Employment_R11!AC11</f>
         <v>1953.8958569048073</v>
       </c>
-      <c r="J10" s="66">
+      <c r="J10" s="63">
         <f>Employment_R11!AD11</f>
         <v>1923.8972483788455</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="63">
         <f>Employment_R11!AE11</f>
         <v>557.0142546684533</v>
       </c>
-      <c r="L10" s="66">
+      <c r="L10" s="63">
         <f>Employment_R11!AF11</f>
         <v>95.548417213140013</v>
       </c>
-      <c r="M10" s="66">
+      <c r="M10" s="63">
         <f>Employment_R11!AG11</f>
         <v>531.60280885202246</v>
       </c>
-      <c r="N10" s="66">
+      <c r="N10" s="63">
         <f>Employment_R11!AH11</f>
         <v>790.4680826769204</v>
       </c>
-      <c r="O10" s="66">
+      <c r="O10" s="63">
         <f>Employment_R11!AI11</f>
         <v>311.34355624992821</v>
       </c>
-      <c r="P10" s="66">
+      <c r="P10" s="63">
         <f>Employment_R11!AJ11</f>
         <v>2460.1072099489002</v>
       </c>
-      <c r="Q10" s="66">
+      <c r="Q10" s="63">
         <f>Employment_R11!AK11</f>
         <v>1547.8211243403141</v>
       </c>
-      <c r="R10" s="66">
+      <c r="R10" s="63">
         <f>Employment_R11!AL11</f>
         <v>54.445809213213572</v>
       </c>
@@ -20593,71 +20593,71 @@
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="66">
+      <c r="B11" s="63">
         <f>Employment_NEA!Z11</f>
         <v>13.817026483695495</v>
       </c>
-      <c r="C11" s="66">
+      <c r="C11" s="63">
         <f>Employment_NEA!AA11</f>
         <v>1079.2528480165688</v>
       </c>
-      <c r="D11" s="66">
+      <c r="D11" s="63">
         <f>Employment_NEA!AB11</f>
         <v>30.63652767229711</v>
       </c>
-      <c r="E11" s="66">
+      <c r="E11" s="63">
         <f>Employment_NEA!AC11</f>
         <v>108.46625672044593</v>
       </c>
-      <c r="F11" s="66">
+      <c r="F11" s="63">
         <f>Employment_NEA!AD11</f>
         <v>0.73963438458236608</v>
       </c>
-      <c r="G11" s="66">
+      <c r="G11" s="63">
         <f>Employment_NEA!AE11</f>
         <v>1.4609492922892096</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="63">
         <f>Employment_R11!AB12</f>
         <v>91.112294862768309</v>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="63">
         <f>Employment_R11!AC12</f>
         <v>304.67267883118382</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="63">
         <f>Employment_R11!AD12</f>
         <v>87.701775024416435</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="63">
         <f>Employment_R11!AE12</f>
         <v>48.574023365368383</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="63">
         <f>Employment_R11!AF12</f>
         <v>212.15510389502268</v>
       </c>
-      <c r="M11" s="66">
+      <c r="M11" s="63">
         <f>Employment_R11!AG12</f>
         <v>896.88326931059407</v>
       </c>
-      <c r="N11" s="66">
+      <c r="N11" s="63">
         <f>Employment_R11!AH12</f>
         <v>138.87269398021127</v>
       </c>
-      <c r="O11" s="66">
+      <c r="O11" s="63">
         <f>Employment_R11!AI12</f>
         <v>189.71287520858058</v>
       </c>
-      <c r="P11" s="66">
+      <c r="P11" s="63">
         <f>Employment_R11!AJ12</f>
         <v>485.30557864390045</v>
       </c>
-      <c r="Q11" s="66">
+      <c r="Q11" s="63">
         <f>Employment_R11!AK12</f>
         <v>350.62651926188545</v>
       </c>
-      <c r="R11" s="66">
+      <c r="R11" s="63">
         <f>Employment_R11!AL12</f>
         <v>5.841055443845006</v>
       </c>
@@ -20666,71 +20666,71 @@
       <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="66">
+      <c r="B12" s="63">
         <f>Employment_NEA!Z12</f>
         <v>548.27616367738767</v>
       </c>
-      <c r="C12" s="66">
+      <c r="C12" s="63">
         <f>Employment_NEA!AA12</f>
         <v>18526.933487867365</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="63">
         <f>Employment_NEA!AB12</f>
         <v>1214.9771519926269</v>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="63">
         <f>Employment_NEA!AC12</f>
         <v>792.99541054591975</v>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="63">
         <f>Employment_NEA!AD12</f>
         <v>2.2379747908278288E-3</v>
       </c>
-      <c r="G12" s="66">
+      <c r="G12" s="63">
         <f>Employment_NEA!AE12</f>
         <v>68.637011082195571</v>
       </c>
-      <c r="H12" s="66">
+      <c r="H12" s="63">
         <f>Employment_R11!AB13</f>
         <v>2368.6680665147892</v>
       </c>
-      <c r="I12" s="66">
+      <c r="I12" s="63">
         <f>Employment_R11!AC13</f>
         <v>5118.3789308440209</v>
       </c>
-      <c r="J12" s="66">
+      <c r="J12" s="63">
         <f>Employment_R11!AD13</f>
         <v>5393.5531047981585</v>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="63">
         <f>Employment_R11!AE13</f>
         <v>1595.8036494674338</v>
       </c>
-      <c r="L12" s="66">
+      <c r="L12" s="63">
         <f>Employment_R11!AF13</f>
         <v>413.2344400120445</v>
       </c>
-      <c r="M12" s="66">
+      <c r="M12" s="63">
         <f>Employment_R11!AG13</f>
         <v>2237.1660381314082</v>
       </c>
-      <c r="N12" s="66">
+      <c r="N12" s="63">
         <f>Employment_R11!AH13</f>
         <v>1834.9373855382178</v>
       </c>
-      <c r="O12" s="66">
+      <c r="O12" s="63">
         <f>Employment_R11!AI13</f>
         <v>1364.7534207190008</v>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="63">
         <f>Employment_R11!AJ13</f>
         <v>8861.2206336284871</v>
       </c>
-      <c r="Q12" s="66">
+      <c r="Q12" s="63">
         <f>Employment_R11!AK13</f>
         <v>5074.5052682145624</v>
       </c>
-      <c r="R12" s="66">
+      <c r="R12" s="63">
         <f>Employment_R11!AL13</f>
         <v>144.38832837104979</v>
       </c>
@@ -20739,71 +20739,71 @@
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="66">
+      <c r="B13" s="63">
         <f>Employment_NEA!Z13</f>
         <v>137.11501764620638</v>
       </c>
-      <c r="C13" s="66">
+      <c r="C13" s="63">
         <f>Employment_NEA!AA13</f>
         <v>12635.48795715404</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="63">
         <f>Employment_NEA!AB13</f>
         <v>364.60416082848849</v>
       </c>
-      <c r="E13" s="66">
+      <c r="E13" s="63">
         <f>Employment_NEA!AC13</f>
         <v>512.33481870442267</v>
       </c>
-      <c r="F13" s="66">
+      <c r="F13" s="63">
         <f>Employment_NEA!AD13</f>
         <v>6.5369598123762023</v>
       </c>
-      <c r="G13" s="66">
+      <c r="G13" s="63">
         <f>Employment_NEA!AE13</f>
         <v>26.31627775029223</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="63">
         <f>Employment_R11!AB14</f>
         <v>506.61467052760668</v>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="63">
         <f>Employment_R11!AC14</f>
         <v>1418.3603177178543</v>
       </c>
-      <c r="J13" s="66">
+      <c r="J13" s="63">
         <f>Employment_R11!AD14</f>
         <v>1298.0744581714775</v>
       </c>
-      <c r="K13" s="66">
+      <c r="K13" s="63">
         <f>Employment_R11!AE14</f>
         <v>504.40416976777334</v>
       </c>
-      <c r="L13" s="66">
+      <c r="L13" s="63">
         <f>Employment_R11!AF14</f>
         <v>232.2112716755085</v>
       </c>
-      <c r="M13" s="66">
+      <c r="M13" s="63">
         <f>Employment_R11!AG14</f>
         <v>1494.9694207256266</v>
       </c>
-      <c r="N13" s="66">
+      <c r="N13" s="63">
         <f>Employment_R11!AH14</f>
         <v>605.86280035733955</v>
       </c>
-      <c r="O13" s="66">
+      <c r="O13" s="63">
         <f>Employment_R11!AI14</f>
         <v>622.07872475270256</v>
       </c>
-      <c r="P13" s="66">
+      <c r="P13" s="63">
         <f>Employment_R11!AJ14</f>
         <v>2337.1421384332257</v>
       </c>
-      <c r="Q13" s="66">
+      <c r="Q13" s="63">
         <f>Employment_R11!AK14</f>
         <v>1245.7832588656061</v>
       </c>
-      <c r="R13" s="66">
+      <c r="R13" s="63">
         <f>Employment_R11!AL14</f>
         <v>58.235284273163984</v>
       </c>
@@ -20812,71 +20812,71 @@
       <c r="A14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="66">
+      <c r="B14" s="63">
         <f>Employment_NEA!Z14</f>
         <v>166.50316405260969</v>
       </c>
-      <c r="C14" s="66">
+      <c r="C14" s="63">
         <f>Employment_NEA!AA14</f>
         <v>6507.7801631730881</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="63">
         <f>Employment_NEA!AB14</f>
         <v>432.40064757708774</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="63">
         <f>Employment_NEA!AC14</f>
         <v>357.44091683067859</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="63">
         <f>Employment_NEA!AD14</f>
         <v>9.4426918257588935E-2</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="63">
         <f>Employment_NEA!AE14</f>
         <v>9.7042240570978002</v>
       </c>
-      <c r="H14" s="66">
+      <c r="H14" s="63">
         <f>Employment_R11!AB15</f>
         <v>326.92915570598717</v>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="63">
         <f>Employment_R11!AC15</f>
         <v>650.97317228759493</v>
       </c>
-      <c r="J14" s="66">
+      <c r="J14" s="63">
         <f>Employment_R11!AD15</f>
         <v>984.65364484648956</v>
       </c>
-      <c r="K14" s="66">
+      <c r="K14" s="63">
         <f>Employment_R11!AE15</f>
         <v>388.02965148714941</v>
       </c>
-      <c r="L14" s="66">
+      <c r="L14" s="63">
         <f>Employment_R11!AF15</f>
         <v>385.584772485212</v>
       </c>
-      <c r="M14" s="66">
+      <c r="M14" s="63">
         <f>Employment_R11!AG15</f>
         <v>455.81753103919254</v>
       </c>
-      <c r="N14" s="66">
+      <c r="N14" s="63">
         <f>Employment_R11!AH15</f>
         <v>287.26085851155682</v>
       </c>
-      <c r="O14" s="66">
+      <c r="O14" s="63">
         <f>Employment_R11!AI15</f>
         <v>461.05876767266619</v>
       </c>
-      <c r="P14" s="66">
+      <c r="P14" s="63">
         <f>Employment_R11!AJ15</f>
         <v>875.3587069252668</v>
       </c>
-      <c r="Q14" s="66">
+      <c r="Q14" s="63">
         <f>Employment_R11!AK15</f>
         <v>926.65681533626241</v>
       </c>
-      <c r="R14" s="66">
+      <c r="R14" s="63">
         <f>Employment_R11!AL15</f>
         <v>48.757861357470389</v>
       </c>
@@ -20885,71 +20885,71 @@
       <c r="A15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="63">
         <f>Employment_NEA!Z15</f>
         <v>59.937389959926129</v>
       </c>
-      <c r="C15" s="66">
+      <c r="C15" s="63">
         <f>Employment_NEA!AA15</f>
         <v>4481.6924106068745</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="63">
         <f>Employment_NEA!AB15</f>
         <v>295.68281776881884</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="63">
         <f>Employment_NEA!AC15</f>
         <v>501.80672615124007</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="63">
         <f>Employment_NEA!AD15</f>
         <v>46.862850437126255</v>
       </c>
-      <c r="G15" s="66">
+      <c r="G15" s="63">
         <f>Employment_NEA!AE15</f>
         <v>2.1038982112830285</v>
       </c>
-      <c r="H15" s="66">
+      <c r="H15" s="63">
         <f>Employment_R11!AB16</f>
         <v>368.14166876824731</v>
       </c>
-      <c r="I15" s="66">
+      <c r="I15" s="63">
         <f>Employment_R11!AC16</f>
         <v>1155.0896671235271</v>
       </c>
-      <c r="J15" s="66">
+      <c r="J15" s="63">
         <f>Employment_R11!AD16</f>
         <v>861.72852271034139</v>
       </c>
-      <c r="K15" s="66">
+      <c r="K15" s="63">
         <f>Employment_R11!AE16</f>
         <v>227.24738791253301</v>
       </c>
-      <c r="L15" s="66">
+      <c r="L15" s="63">
         <f>Employment_R11!AF16</f>
         <v>584.57934133822982</v>
       </c>
-      <c r="M15" s="66">
+      <c r="M15" s="63">
         <f>Employment_R11!AG16</f>
         <v>1132.0019096910162</v>
       </c>
-      <c r="N15" s="66">
+      <c r="N15" s="63">
         <f>Employment_R11!AH16</f>
         <v>1527.0807571877704</v>
       </c>
-      <c r="O15" s="66">
+      <c r="O15" s="63">
         <f>Employment_R11!AI16</f>
         <v>217.98645644917914</v>
       </c>
-      <c r="P15" s="66">
+      <c r="P15" s="63">
         <f>Employment_R11!AJ16</f>
         <v>876.4186170610725</v>
       </c>
-      <c r="Q15" s="66">
+      <c r="Q15" s="63">
         <f>Employment_R11!AK16</f>
         <v>875.76033363811223</v>
       </c>
-      <c r="R15" s="66">
+      <c r="R15" s="63">
         <f>Employment_R11!AL16</f>
         <v>56.644827243251008</v>
       </c>
@@ -20958,71 +20958,71 @@
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="66">
+      <c r="B16" s="63">
         <f>Employment_NEA!Z16</f>
         <v>1955.9209214659002</v>
       </c>
-      <c r="C16" s="66">
+      <c r="C16" s="63">
         <f>Employment_NEA!AA16</f>
         <v>48530.31769818606</v>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="63">
         <f>Employment_NEA!AB16</f>
         <v>4359.1122854791201</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="63">
         <f>Employment_NEA!AC16</f>
         <v>2982.7211719772681</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="63">
         <f>Employment_NEA!AD16</f>
         <v>1.9273600064356121E-5</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="63">
         <f>Employment_NEA!AE16</f>
         <v>121.01417917013664</v>
       </c>
-      <c r="H16" s="66">
+      <c r="H16" s="63">
         <f>Employment_R11!AB17</f>
         <v>6741.0168344716194</v>
       </c>
-      <c r="I16" s="66">
+      <c r="I16" s="63">
         <f>Employment_R11!AC17</f>
         <v>6563.2009170451438</v>
       </c>
-      <c r="J16" s="66">
+      <c r="J16" s="63">
         <f>Employment_R11!AD17</f>
         <v>12835.034268185091</v>
       </c>
-      <c r="K16" s="66">
+      <c r="K16" s="63">
         <f>Employment_R11!AE17</f>
         <v>4197.8034947569658</v>
       </c>
-      <c r="L16" s="66">
+      <c r="L16" s="63">
         <f>Employment_R11!AF17</f>
         <v>847.77944166681448</v>
       </c>
-      <c r="M16" s="66">
+      <c r="M16" s="63">
         <f>Employment_R11!AG17</f>
         <v>4191.414373103702</v>
       </c>
-      <c r="N16" s="66">
+      <c r="N16" s="63">
         <f>Employment_R11!AH17</f>
         <v>2155.6851105018832</v>
       </c>
-      <c r="O16" s="66">
+      <c r="O16" s="63">
         <f>Employment_R11!AI17</f>
         <v>2793.2884102192429</v>
       </c>
-      <c r="P16" s="66">
+      <c r="P16" s="63">
         <f>Employment_R11!AJ17</f>
         <v>12938.558563365288</v>
       </c>
-      <c r="Q16" s="66">
+      <c r="Q16" s="63">
         <f>Employment_R11!AK17</f>
         <v>11874.236167538169</v>
       </c>
-      <c r="R16" s="66">
+      <c r="R16" s="63">
         <f>Employment_R11!AL17</f>
         <v>240.93039179621002</v>
       </c>
@@ -21031,71 +21031,71 @@
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="66">
+      <c r="B17" s="63">
         <f>Employment_NEA!Z17</f>
         <v>494.0620631182237</v>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="63">
         <f>Employment_NEA!AA17</f>
         <v>9779.1460770912054</v>
       </c>
-      <c r="D17" s="66">
+      <c r="D17" s="63">
         <f>Employment_NEA!AB17</f>
         <v>1563.627468409202</v>
       </c>
-      <c r="E17" s="66">
+      <c r="E17" s="63">
         <f>Employment_NEA!AC17</f>
         <v>1588.6454056447121</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F17" s="63">
         <f>Employment_NEA!AD17</f>
         <v>3.8083232720542336E-6</v>
       </c>
-      <c r="G17" s="66">
+      <c r="G17" s="63">
         <f>Employment_NEA!AE17</f>
         <v>104.42306120220971</v>
       </c>
-      <c r="H17" s="66">
+      <c r="H17" s="63">
         <f>Employment_R11!AB18</f>
         <v>2152.8355340050393</v>
       </c>
-      <c r="I17" s="66">
+      <c r="I17" s="63">
         <f>Employment_R11!AC18</f>
         <v>3443.2920460409455</v>
       </c>
-      <c r="J17" s="66">
+      <c r="J17" s="63">
         <f>Employment_R11!AD18</f>
         <v>3655.0840889739366</v>
       </c>
-      <c r="K17" s="66">
+      <c r="K17" s="63">
         <f>Employment_R11!AE18</f>
         <v>1183.3414693185484</v>
       </c>
-      <c r="L17" s="66">
+      <c r="L17" s="63">
         <f>Employment_R11!AF18</f>
         <v>455.36087276027422</v>
       </c>
-      <c r="M17" s="66">
+      <c r="M17" s="63">
         <f>Employment_R11!AG18</f>
         <v>1827.0313866965118</v>
       </c>
-      <c r="N17" s="66">
+      <c r="N17" s="63">
         <f>Employment_R11!AH18</f>
         <v>1613.1252546800683</v>
       </c>
-      <c r="O17" s="66">
+      <c r="O17" s="63">
         <f>Employment_R11!AI18</f>
         <v>386.17975572574926</v>
       </c>
-      <c r="P17" s="66">
+      <c r="P17" s="63">
         <f>Employment_R11!AJ18</f>
         <v>7701.6727467522205</v>
       </c>
-      <c r="Q17" s="66">
+      <c r="Q17" s="63">
         <f>Employment_R11!AK18</f>
         <v>2158.5469501778111</v>
       </c>
-      <c r="R17" s="66">
+      <c r="R17" s="63">
         <f>Employment_R11!AL18</f>
         <v>96.548384644236151</v>
       </c>
@@ -21104,71 +21104,71 @@
       <c r="A18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="66">
+      <c r="B18" s="63">
         <f>Employment_NEA!Z18</f>
         <v>520.59846977826385</v>
       </c>
-      <c r="C18" s="66">
+      <c r="C18" s="63">
         <f>Employment_NEA!AA18</f>
         <v>5744.073534201304</v>
       </c>
-      <c r="D18" s="66">
+      <c r="D18" s="63">
         <f>Employment_NEA!AB18</f>
         <v>470.97660224497258</v>
       </c>
-      <c r="E18" s="66">
+      <c r="E18" s="63">
         <f>Employment_NEA!AC18</f>
         <v>317.84691130922391</v>
       </c>
-      <c r="F18" s="66">
+      <c r="F18" s="63">
         <f>Employment_NEA!AD18</f>
         <v>2.626589893115276</v>
       </c>
-      <c r="G18" s="66">
+      <c r="G18" s="63">
         <f>Employment_NEA!AE18</f>
         <v>20.597341388808832</v>
       </c>
-      <c r="H18" s="66">
+      <c r="H18" s="63">
         <f>Employment_R11!AB19</f>
         <v>5155.6209953525349</v>
       </c>
-      <c r="I18" s="66">
+      <c r="I18" s="63">
         <f>Employment_R11!AC19</f>
         <v>2935.6572534169904</v>
       </c>
-      <c r="J18" s="66">
+      <c r="J18" s="63">
         <f>Employment_R11!AD19</f>
         <v>2652.5423485531364</v>
       </c>
-      <c r="K18" s="66">
+      <c r="K18" s="63">
         <f>Employment_R11!AE19</f>
         <v>844.29276787196795</v>
       </c>
-      <c r="L18" s="66">
+      <c r="L18" s="63">
         <f>Employment_R11!AF19</f>
         <v>368.10806250595147</v>
       </c>
-      <c r="M18" s="66">
+      <c r="M18" s="63">
         <f>Employment_R11!AG19</f>
         <v>1137.2994625638921</v>
       </c>
-      <c r="N18" s="66">
+      <c r="N18" s="63">
         <f>Employment_R11!AH19</f>
         <v>957.70329750840165</v>
       </c>
-      <c r="O18" s="66">
+      <c r="O18" s="63">
         <f>Employment_R11!AI19</f>
         <v>1343.2457872131381</v>
       </c>
-      <c r="P18" s="66">
+      <c r="P18" s="63">
         <f>Employment_R11!AJ19</f>
         <v>1589.5583876165294</v>
       </c>
-      <c r="Q18" s="66">
+      <c r="Q18" s="63">
         <f>Employment_R11!AK19</f>
         <v>1439.3798413081724</v>
       </c>
-      <c r="R18" s="66">
+      <c r="R18" s="63">
         <f>Employment_R11!AL19</f>
         <v>50.459801705630895</v>
       </c>
@@ -21177,71 +21177,71 @@
       <c r="A19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="66">
+      <c r="B19" s="63">
         <f>Employment_NEA!Z19</f>
         <v>44.823693385882265</v>
       </c>
-      <c r="C19" s="66">
+      <c r="C19" s="63">
         <f>Employment_NEA!AA19</f>
         <v>4924.4952660964573</v>
       </c>
-      <c r="D19" s="66">
+      <c r="D19" s="63">
         <f>Employment_NEA!AB19</f>
         <v>115.74558566835162</v>
       </c>
-      <c r="E19" s="66">
+      <c r="E19" s="63">
         <f>Employment_NEA!AC19</f>
         <v>621.00906108046115</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F19" s="63">
         <f>Employment_NEA!AD19</f>
         <v>8.1764120522504502</v>
       </c>
-      <c r="G19" s="66">
+      <c r="G19" s="63">
         <f>Employment_NEA!AE19</f>
         <v>33.032771207925478</v>
       </c>
-      <c r="H19" s="66">
+      <c r="H19" s="63">
         <f>Employment_R11!AB20</f>
         <v>506.34297239218313</v>
       </c>
-      <c r="I19" s="66">
+      <c r="I19" s="63">
         <f>Employment_R11!AC20</f>
         <v>1213.5795069725987</v>
       </c>
-      <c r="J19" s="66">
+      <c r="J19" s="63">
         <f>Employment_R11!AD20</f>
         <v>736.93275005661826</v>
       </c>
-      <c r="K19" s="66">
+      <c r="K19" s="63">
         <f>Employment_R11!AE20</f>
         <v>459.60968136166991</v>
       </c>
-      <c r="L19" s="66">
+      <c r="L19" s="63">
         <f>Employment_R11!AF20</f>
         <v>957.18378747713905</v>
       </c>
-      <c r="M19" s="66">
+      <c r="M19" s="63">
         <f>Employment_R11!AG20</f>
         <v>842.37145024869926</v>
       </c>
-      <c r="N19" s="66">
+      <c r="N19" s="63">
         <f>Employment_R11!AH20</f>
         <v>657.57242540552716</v>
       </c>
-      <c r="O19" s="66">
+      <c r="O19" s="63">
         <f>Employment_R11!AI20</f>
         <v>829.17391388385272</v>
       </c>
-      <c r="P19" s="66">
+      <c r="P19" s="63">
         <f>Employment_R11!AJ20</f>
         <v>10702.706024255267</v>
       </c>
-      <c r="Q19" s="66">
+      <c r="Q19" s="63">
         <f>Employment_R11!AK20</f>
         <v>1054.5442113967106</v>
       </c>
-      <c r="R19" s="66">
+      <c r="R19" s="63">
         <f>Employment_R11!AL20</f>
         <v>69.232864600562891</v>
       </c>
@@ -21250,71 +21250,71 @@
       <c r="A20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="66">
+      <c r="B20" s="63">
         <f>Employment_NEA!Z20</f>
         <v>10.328303810289549</v>
       </c>
-      <c r="C20" s="66">
+      <c r="C20" s="63">
         <f>Employment_NEA!AA20</f>
         <v>407.04461394959236</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="63">
         <f>Employment_NEA!AB20</f>
         <v>18.381635035812838</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="63">
         <f>Employment_NEA!AC20</f>
         <v>172.17659457689231</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="63">
         <f>Employment_NEA!AD20</f>
         <v>3.1089846415063987E-3</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="63">
         <f>Employment_NEA!AE20</f>
         <v>1.0021227903953758E-2</v>
       </c>
-      <c r="H20" s="66">
+      <c r="H20" s="63">
         <f>Employment_R11!AB21</f>
         <v>262.6520762708538</v>
       </c>
-      <c r="I20" s="66">
+      <c r="I20" s="63">
         <f>Employment_R11!AC21</f>
         <v>58.015688433492443</v>
       </c>
-      <c r="J20" s="66">
+      <c r="J20" s="63">
         <f>Employment_R11!AD21</f>
         <v>164.0383460203588</v>
       </c>
-      <c r="K20" s="66">
+      <c r="K20" s="63">
         <f>Employment_R11!AE21</f>
         <v>49.308444628770772</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="63">
         <f>Employment_R11!AF21</f>
         <v>544.04651882062012</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="63">
         <f>Employment_R11!AG21</f>
         <v>18.907722996562246</v>
       </c>
-      <c r="N20" s="66">
+      <c r="N20" s="63">
         <f>Employment_R11!AH21</f>
         <v>339.96138558907234</v>
       </c>
-      <c r="O20" s="66">
+      <c r="O20" s="63">
         <f>Employment_R11!AI21</f>
         <v>2.4763183939521184E-2</v>
       </c>
-      <c r="P20" s="66">
+      <c r="P20" s="63">
         <f>Employment_R11!AJ21</f>
         <v>335.56383001313571</v>
       </c>
-      <c r="Q20" s="66">
+      <c r="Q20" s="63">
         <f>Employment_R11!AK21</f>
         <v>16.574411748592915</v>
       </c>
-      <c r="R20" s="66">
+      <c r="R20" s="63">
         <f>Employment_R11!AL21</f>
         <v>1.0174979018322888E-3</v>
       </c>
@@ -21323,71 +21323,71 @@
       <c r="A21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="66">
+      <c r="B21" s="63">
         <f>Employment_NEA!Z21</f>
         <v>6.5544071072595029</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="63">
         <f>Employment_NEA!AA21</f>
         <v>2928.4039309573209</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="63">
         <f>Employment_NEA!AB21</f>
         <v>52.091249851153435</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="63">
         <f>Employment_NEA!AC21</f>
         <v>203.6765486995549</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="63">
         <f>Employment_NEA!AD21</f>
         <v>10.720426774413095</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="63">
         <f>Employment_NEA!AE21</f>
         <v>2.5140642583530903</v>
       </c>
-      <c r="H21" s="66">
+      <c r="H21" s="63">
         <f>Employment_R11!AB22</f>
         <v>306.60204109481282</v>
       </c>
-      <c r="I21" s="66">
+      <c r="I21" s="63">
         <f>Employment_R11!AC22</f>
         <v>38.815409447000988</v>
       </c>
-      <c r="J21" s="66">
+      <c r="J21" s="63">
         <f>Employment_R11!AD22</f>
         <v>58.575078376302912</v>
       </c>
-      <c r="K21" s="66">
+      <c r="K21" s="63">
         <f>Employment_R11!AE22</f>
         <v>225.36185247032262</v>
       </c>
-      <c r="L21" s="66">
+      <c r="L21" s="63">
         <f>Employment_R11!AF22</f>
         <v>569.89763289426958</v>
       </c>
-      <c r="M21" s="66">
+      <c r="M21" s="63">
         <f>Employment_R11!AG22</f>
         <v>71.82403265213685</v>
       </c>
-      <c r="N21" s="66">
+      <c r="N21" s="63">
         <f>Employment_R11!AH22</f>
         <v>710.50252316596027</v>
       </c>
-      <c r="O21" s="66">
+      <c r="O21" s="63">
         <f>Employment_R11!AI22</f>
         <v>216.38977660609331</v>
       </c>
-      <c r="P21" s="66">
+      <c r="P21" s="63">
         <f>Employment_R11!AJ22</f>
         <v>11750.96334687194</v>
       </c>
-      <c r="Q21" s="66">
+      <c r="Q21" s="63">
         <f>Employment_R11!AK22</f>
         <v>408.7305250512282</v>
       </c>
-      <c r="R21" s="66">
+      <c r="R21" s="63">
         <f>Employment_R11!AL22</f>
         <v>7.6265891254818516</v>
       </c>
@@ -21396,71 +21396,71 @@
       <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="63">
         <f>Employment_NEA!Z22</f>
         <v>2.6353713900745919</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="63">
         <f>Employment_NEA!AA22</f>
         <v>145.29079267287213</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="63">
         <f>Employment_NEA!AB22</f>
         <v>23.112379734417967</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="63">
         <f>Employment_NEA!AC22</f>
         <v>441.59181486348336</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="63">
         <f>Employment_NEA!AD22</f>
         <v>3.1422930170608748E-3</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="63">
         <f>Employment_NEA!AE22</f>
         <v>0.14026793751121824</v>
       </c>
-      <c r="H22" s="66">
+      <c r="H22" s="63">
         <f>Employment_R11!AB23</f>
         <v>55.044181290678523</v>
       </c>
-      <c r="I22" s="66">
+      <c r="I22" s="63">
         <f>Employment_R11!AC23</f>
         <v>218.70389116662142</v>
       </c>
-      <c r="J22" s="66">
+      <c r="J22" s="63">
         <f>Employment_R11!AD23</f>
         <v>36.589590079031986</v>
       </c>
-      <c r="K22" s="66">
+      <c r="K22" s="63">
         <f>Employment_R11!AE23</f>
         <v>25.088299137355577</v>
       </c>
-      <c r="L22" s="66">
+      <c r="L22" s="63">
         <f>Employment_R11!AF23</f>
         <v>460.03039808125948</v>
       </c>
-      <c r="M22" s="66">
+      <c r="M22" s="63">
         <f>Employment_R11!AG23</f>
         <v>313.7182431569675</v>
       </c>
-      <c r="N22" s="66">
+      <c r="N22" s="63">
         <f>Employment_R11!AH23</f>
         <v>95.104809026178103</v>
       </c>
-      <c r="O22" s="66">
+      <c r="O22" s="63">
         <f>Employment_R11!AI23</f>
         <v>32.504354700065065</v>
       </c>
-      <c r="P22" s="66">
+      <c r="P22" s="63">
         <f>Employment_R11!AJ23</f>
         <v>271.30352391985218</v>
       </c>
-      <c r="Q22" s="66">
+      <c r="Q22" s="63">
         <f>Employment_R11!AK23</f>
         <v>203.09418192233974</v>
       </c>
-      <c r="R22" s="66">
+      <c r="R22" s="63">
         <f>Employment_R11!AL23</f>
         <v>1.9458244732340002</v>
       </c>
@@ -21469,71 +21469,71 @@
       <c r="A23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="66">
+      <c r="B23" s="63">
         <f>Employment_NEA!Z23</f>
         <v>1.1533027270409142</v>
       </c>
-      <c r="C23" s="66">
+      <c r="C23" s="63">
         <f>Employment_NEA!AA23</f>
         <v>44.662084895404945</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D23" s="63">
         <f>Employment_NEA!AB23</f>
         <v>10.059652830770821</v>
       </c>
-      <c r="E23" s="66">
+      <c r="E23" s="63">
         <f>Employment_NEA!AC23</f>
         <v>30.919041539420785</v>
       </c>
-      <c r="F23" s="66">
+      <c r="F23" s="63">
         <f>Employment_NEA!AD23</f>
         <v>0.19328973461279192</v>
       </c>
-      <c r="G23" s="66">
+      <c r="G23" s="63">
         <f>Employment_NEA!AE23</f>
         <v>3.0340273433710201</v>
       </c>
-      <c r="H23" s="66">
+      <c r="H23" s="63">
         <f>Employment_R11!AB24</f>
         <v>3.7108754649684648</v>
       </c>
-      <c r="I23" s="66">
+      <c r="I23" s="63">
         <f>Employment_R11!AC24</f>
         <v>136.08592237563195</v>
       </c>
-      <c r="J23" s="66">
+      <c r="J23" s="63">
         <f>Employment_R11!AD24</f>
         <v>7.9364686521266936</v>
       </c>
-      <c r="K23" s="66">
+      <c r="K23" s="63">
         <f>Employment_R11!AE24</f>
         <v>7.5227655482752356</v>
       </c>
-      <c r="L23" s="66">
+      <c r="L23" s="63">
         <f>Employment_R11!AF24</f>
         <v>27.400555506303252</v>
       </c>
-      <c r="M23" s="66">
+      <c r="M23" s="63">
         <f>Employment_R11!AG24</f>
         <v>165.72731968683672</v>
       </c>
-      <c r="N23" s="66">
+      <c r="N23" s="63">
         <f>Employment_R11!AH24</f>
         <v>57.806366470241329</v>
       </c>
-      <c r="O23" s="66">
+      <c r="O23" s="63">
         <f>Employment_R11!AI24</f>
         <v>2.1853175213366511</v>
       </c>
-      <c r="P23" s="66">
+      <c r="P23" s="63">
         <f>Employment_R11!AJ24</f>
         <v>131.32038650436476</v>
       </c>
-      <c r="Q23" s="66">
+      <c r="Q23" s="63">
         <f>Employment_R11!AK24</f>
         <v>30.191537307020266</v>
       </c>
-      <c r="R23" s="66">
+      <c r="R23" s="63">
         <f>Employment_R11!AL24</f>
         <v>0.62454410678181804</v>
       </c>
@@ -21542,71 +21542,71 @@
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="66">
+      <c r="B24" s="63">
         <f>Employment_NEA!Z24</f>
         <v>0.22940283707906492</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="63">
         <f>Employment_NEA!AA24</f>
         <v>175.84847770767743</v>
       </c>
-      <c r="D24" s="66">
+      <c r="D24" s="63">
         <f>Employment_NEA!AB24</f>
         <v>3.0257574019040199</v>
       </c>
-      <c r="E24" s="66">
+      <c r="E24" s="63">
         <f>Employment_NEA!AC24</f>
         <v>7.4334704045019448E-2</v>
       </c>
-      <c r="F24" s="66">
+      <c r="F24" s="63">
         <f>Employment_NEA!AD24</f>
         <v>0.2087927534396449</v>
       </c>
-      <c r="G24" s="66">
+      <c r="G24" s="63">
         <f>Employment_NEA!AE24</f>
         <v>9.9884025350496283E-3</v>
       </c>
-      <c r="H24" s="66">
+      <c r="H24" s="63">
         <f>Employment_R11!AB25</f>
         <v>41.708827395941334</v>
       </c>
-      <c r="I24" s="66">
+      <c r="I24" s="63">
         <f>Employment_R11!AC25</f>
         <v>47.12037866849176</v>
       </c>
-      <c r="J24" s="66">
+      <c r="J24" s="63">
         <f>Employment_R11!AD25</f>
         <v>87.384432525899243</v>
       </c>
-      <c r="K24" s="66">
+      <c r="K24" s="63">
         <f>Employment_R11!AE25</f>
         <v>11.998464152646926</v>
       </c>
-      <c r="L24" s="66">
+      <c r="L24" s="63">
         <f>Employment_R11!AF25</f>
         <v>6.1555756947979408</v>
       </c>
-      <c r="M24" s="66">
+      <c r="M24" s="63">
         <f>Employment_R11!AG25</f>
         <v>7.9315718405968063</v>
       </c>
-      <c r="N24" s="66">
+      <c r="N24" s="63">
         <f>Employment_R11!AH25</f>
         <v>40.439578563326229</v>
       </c>
-      <c r="O24" s="66">
+      <c r="O24" s="63">
         <f>Employment_R11!AI25</f>
         <v>1.2252208175532555</v>
       </c>
-      <c r="P24" s="66">
+      <c r="P24" s="63">
         <f>Employment_R11!AJ25</f>
         <v>56.672651164941506</v>
       </c>
-      <c r="Q24" s="66">
+      <c r="Q24" s="63">
         <f>Employment_R11!AK25</f>
         <v>6.0604271043046101</v>
       </c>
-      <c r="R24" s="66">
+      <c r="R24" s="63">
         <f>Employment_R11!AL25</f>
         <v>0.7664937854542262</v>
       </c>
@@ -21615,71 +21615,71 @@
       <c r="A25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="63">
         <f>Employment_NEA!Z25</f>
         <v>0.23738162427920073</v>
       </c>
-      <c r="C25" s="66">
+      <c r="C25" s="63">
         <f>Employment_NEA!AA25</f>
         <v>36.675698206470912</v>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="63">
         <f>Employment_NEA!AB25</f>
         <v>7.1273480167260379</v>
       </c>
-      <c r="E25" s="66">
+      <c r="E25" s="63">
         <f>Employment_NEA!AC25</f>
         <v>0.45514071046247634</v>
       </c>
-      <c r="F25" s="66">
+      <c r="F25" s="63">
         <f>Employment_NEA!AD25</f>
         <v>1.2867230993536387E-2</v>
       </c>
-      <c r="G25" s="66">
+      <c r="G25" s="63">
         <f>Employment_NEA!AE25</f>
         <v>9.2024064521292019E-3</v>
       </c>
-      <c r="H25" s="66">
+      <c r="H25" s="63">
         <f>Employment_R11!AB26</f>
         <v>5.0962568137086226</v>
       </c>
-      <c r="I25" s="66">
+      <c r="I25" s="63">
         <f>Employment_R11!AC26</f>
         <v>6.4217866840208648</v>
       </c>
-      <c r="J25" s="66">
+      <c r="J25" s="63">
         <f>Employment_R11!AD26</f>
         <v>25.511697927373344</v>
       </c>
-      <c r="K25" s="66">
+      <c r="K25" s="63">
         <f>Employment_R11!AE26</f>
         <v>2.7434540684161308</v>
       </c>
-      <c r="L25" s="66">
+      <c r="L25" s="63">
         <f>Employment_R11!AF26</f>
         <v>3.2800456070457309</v>
       </c>
-      <c r="M25" s="66">
+      <c r="M25" s="63">
         <f>Employment_R11!AG26</f>
         <v>4.6473728568889756</v>
       </c>
-      <c r="N25" s="66">
+      <c r="N25" s="63">
         <f>Employment_R11!AH26</f>
         <v>53.981437785875976</v>
       </c>
-      <c r="O25" s="66">
+      <c r="O25" s="63">
         <f>Employment_R11!AI26</f>
         <v>2.3685436311878007E-2</v>
       </c>
-      <c r="P25" s="66">
+      <c r="P25" s="63">
         <f>Employment_R11!AJ26</f>
         <v>23.500160176850873</v>
       </c>
-      <c r="Q25" s="66">
+      <c r="Q25" s="63">
         <f>Employment_R11!AK26</f>
         <v>15.126427259681293</v>
       </c>
-      <c r="R25" s="66">
+      <c r="R25" s="63">
         <f>Employment_R11!AL26</f>
         <v>0.30758094262822466</v>
       </c>
@@ -21688,71 +21688,71 @@
       <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="66">
+      <c r="B26" s="63">
         <f>Employment_NEA!Z26</f>
         <v>0.13811320170335639</v>
       </c>
-      <c r="C26" s="66">
+      <c r="C26" s="63">
         <f>Employment_NEA!AA26</f>
         <v>387.43949716212177</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="63">
         <f>Employment_NEA!AB26</f>
         <v>24.981431491602724</v>
       </c>
-      <c r="E26" s="66">
+      <c r="E26" s="63">
         <f>Employment_NEA!AC26</f>
         <v>125.07428642145159</v>
       </c>
-      <c r="F26" s="66">
+      <c r="F26" s="63">
         <f>Employment_NEA!AD26</f>
         <v>2.6795047901560551E-2</v>
       </c>
-      <c r="G26" s="66">
+      <c r="G26" s="63">
         <f>Employment_NEA!AE26</f>
         <v>14.787215548252842</v>
       </c>
-      <c r="H26" s="66">
+      <c r="H26" s="63">
         <f>Employment_R11!AB27</f>
         <v>82.390970810285594</v>
       </c>
-      <c r="I26" s="66">
+      <c r="I26" s="63">
         <f>Employment_R11!AC27</f>
         <v>389.17633614043712</v>
       </c>
-      <c r="J26" s="66">
+      <c r="J26" s="63">
         <f>Employment_R11!AD27</f>
         <v>52.556594380740577</v>
       </c>
-      <c r="K26" s="66">
+      <c r="K26" s="63">
         <f>Employment_R11!AE27</f>
         <v>39.68765629473549</v>
       </c>
-      <c r="L26" s="66">
+      <c r="L26" s="63">
         <f>Employment_R11!AF27</f>
         <v>134.66995829813416</v>
       </c>
-      <c r="M26" s="66">
+      <c r="M26" s="63">
         <f>Employment_R11!AG27</f>
         <v>30.645586576320504</v>
       </c>
-      <c r="N26" s="66">
+      <c r="N26" s="63">
         <f>Employment_R11!AH27</f>
         <v>260.60254859725154</v>
       </c>
-      <c r="O26" s="66">
+      <c r="O26" s="63">
         <f>Employment_R11!AI27</f>
         <v>276.69700069349608</v>
       </c>
-      <c r="P26" s="66">
+      <c r="P26" s="63">
         <f>Employment_R11!AJ27</f>
         <v>719.13353138191314</v>
       </c>
-      <c r="Q26" s="66">
+      <c r="Q26" s="63">
         <f>Employment_R11!AK27</f>
         <v>49.205376415078796</v>
       </c>
-      <c r="R26" s="66">
+      <c r="R26" s="63">
         <f>Employment_R11!AL27</f>
         <v>1.861472593468557</v>
       </c>
@@ -21761,71 +21761,71 @@
       <c r="A27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="66">
+      <c r="B27" s="63">
         <f>Employment_NEA!Z27</f>
         <v>1.8160239163915697</v>
       </c>
-      <c r="C27" s="66">
+      <c r="C27" s="63">
         <f>Employment_NEA!AA27</f>
         <v>178.66757182831819</v>
       </c>
-      <c r="D27" s="66">
+      <c r="D27" s="63">
         <f>Employment_NEA!AB27</f>
         <v>23.982959969260513</v>
       </c>
-      <c r="E27" s="66">
+      <c r="E27" s="63">
         <f>Employment_NEA!AC27</f>
         <v>227.24317740422842</v>
       </c>
-      <c r="F27" s="66">
+      <c r="F27" s="63">
         <f>Employment_NEA!AD27</f>
         <v>3.1651287303549906E-3</v>
       </c>
-      <c r="G27" s="66">
+      <c r="G27" s="63">
         <f>Employment_NEA!AE27</f>
         <v>0.35259102535819525</v>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="63">
         <f>Employment_R11!AB28</f>
         <v>18.52761691944924</v>
       </c>
-      <c r="I27" s="66">
+      <c r="I27" s="63">
         <f>Employment_R11!AC28</f>
         <v>105.20653230450881</v>
       </c>
-      <c r="J27" s="66">
+      <c r="J27" s="63">
         <f>Employment_R11!AD28</f>
         <v>126.9947891460796</v>
       </c>
-      <c r="K27" s="66">
+      <c r="K27" s="63">
         <f>Employment_R11!AE28</f>
         <v>26.048385657757322</v>
       </c>
-      <c r="L27" s="66">
+      <c r="L27" s="63">
         <f>Employment_R11!AF28</f>
         <v>156.09783226825783</v>
       </c>
-      <c r="M27" s="66">
+      <c r="M27" s="63">
         <f>Employment_R11!AG28</f>
         <v>3.3096083176659463</v>
       </c>
-      <c r="N27" s="66">
+      <c r="N27" s="63">
         <f>Employment_R11!AH28</f>
         <v>71.286382161882671</v>
       </c>
-      <c r="O27" s="66">
+      <c r="O27" s="63">
         <f>Employment_R11!AI28</f>
         <v>0.87949434043732833</v>
       </c>
-      <c r="P27" s="66">
+      <c r="P27" s="63">
         <f>Employment_R11!AJ28</f>
         <v>26.621998416616208</v>
       </c>
-      <c r="Q27" s="66">
+      <c r="Q27" s="63">
         <f>Employment_R11!AK28</f>
         <v>138.59802539527359</v>
       </c>
-      <c r="R27" s="66">
+      <c r="R27" s="63">
         <f>Employment_R11!AL28</f>
         <v>0.76472959067577273</v>
       </c>
@@ -21834,71 +21834,71 @@
       <c r="A28" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="63">
         <f>Employment_NEA!Z28</f>
         <v>2019.588</v>
       </c>
-      <c r="C28" s="66">
+      <c r="C28" s="63">
         <f>Employment_NEA!AA28</f>
         <v>60937.275540234892</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="63">
         <f>Employment_NEA!AB28</f>
         <v>4960.6779999999999</v>
       </c>
-      <c r="E28" s="66">
+      <c r="E28" s="63">
         <f>Employment_NEA!AC28</f>
         <v>4842.88</v>
       </c>
-      <c r="F28" s="66">
+      <c r="F28" s="63">
         <f>Employment_NEA!AD28</f>
         <v>68.847999999999999</v>
       </c>
-      <c r="G28" s="66">
+      <c r="G28" s="63">
         <f>Employment_NEA!AE28</f>
         <v>707.01614821011333</v>
       </c>
-      <c r="H28" s="66">
+      <c r="H28" s="63">
         <f>Employment_R11!AB29</f>
         <v>10316.340983109594</v>
       </c>
-      <c r="I28" s="66">
+      <c r="I28" s="63">
         <f>Employment_R11!AC29</f>
         <v>15116.026526077989</v>
       </c>
-      <c r="J28" s="66">
+      <c r="J28" s="63">
         <f>Employment_R11!AD29</f>
         <v>12122.850892565462</v>
       </c>
-      <c r="K28" s="66">
+      <c r="K28" s="63">
         <f>Employment_R11!AE29</f>
         <v>2743.5712632985892</v>
       </c>
-      <c r="L28" s="66">
+      <c r="L28" s="63">
         <f>Employment_R11!AF29</f>
         <v>2674.7563997171155</v>
       </c>
-      <c r="M28" s="66">
+      <c r="M28" s="63">
         <f>Employment_R11!AG29</f>
         <v>11760.851175260206</v>
       </c>
-      <c r="N28" s="66">
+      <c r="N28" s="63">
         <f>Employment_R11!AH29</f>
         <v>7277.6717554455699</v>
       </c>
-      <c r="O28" s="66">
+      <c r="O28" s="63">
         <f>Employment_R11!AI29</f>
         <v>1970.8292944336067</v>
       </c>
-      <c r="P28" s="66">
+      <c r="P28" s="63">
         <f>Employment_R11!AJ29</f>
         <v>59911.575384036485</v>
       </c>
-      <c r="Q28" s="66">
+      <c r="Q28" s="63">
         <f>Employment_R11!AK29</f>
         <v>15468.908921669681</v>
       </c>
-      <c r="R28" s="66">
+      <c r="R28" s="63">
         <f>Employment_R11!AL29</f>
         <v>1301.1884673955074</v>
       </c>
@@ -21907,71 +21907,71 @@
       <c r="A29" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="66">
+      <c r="B29" s="63">
         <f>Employment_NEA!Z29</f>
         <v>1157.2140168883764</v>
       </c>
-      <c r="C29" s="66">
+      <c r="C29" s="63">
         <f>Employment_NEA!AA29</f>
         <v>20755.461884555596</v>
       </c>
-      <c r="D29" s="66">
+      <c r="D29" s="63">
         <f>Employment_NEA!AB29</f>
         <v>3359.7805227726908</v>
       </c>
-      <c r="E29" s="66">
+      <c r="E29" s="63">
         <f>Employment_NEA!AC29</f>
         <v>5009.3815179380908</v>
       </c>
-      <c r="F29" s="66">
+      <c r="F29" s="63">
         <f>Employment_NEA!AD29</f>
         <v>50.502225411922808</v>
       </c>
-      <c r="G29" s="66">
+      <c r="G29" s="63">
         <f>Employment_NEA!AE29</f>
         <v>305.73094178109932</v>
       </c>
-      <c r="H29" s="66">
+      <c r="H29" s="63">
         <f>Employment_R11!AB30</f>
         <v>3503.8434487738887</v>
       </c>
-      <c r="I29" s="66">
+      <c r="I29" s="63">
         <f>Employment_R11!AC30</f>
         <v>9722.3484401190181</v>
       </c>
-      <c r="J29" s="66">
+      <c r="J29" s="63">
         <f>Employment_R11!AD30</f>
         <v>5945.5716199329108</v>
       </c>
-      <c r="K29" s="66">
+      <c r="K29" s="63">
         <f>Employment_R11!AE30</f>
         <v>1893.9582655899351</v>
       </c>
-      <c r="L29" s="66">
+      <c r="L29" s="63">
         <f>Employment_R11!AF30</f>
         <v>1629.9755548809092</v>
       </c>
-      <c r="M29" s="66">
+      <c r="M29" s="63">
         <f>Employment_R11!AG30</f>
         <v>3610.3300190430668</v>
       </c>
-      <c r="N29" s="66">
+      <c r="N29" s="63">
         <f>Employment_R11!AH30</f>
         <v>6960.6572258488786</v>
       </c>
-      <c r="O29" s="66">
+      <c r="O29" s="63">
         <f>Employment_R11!AI30</f>
         <v>906.60150365185336</v>
       </c>
-      <c r="P29" s="66">
+      <c r="P29" s="63">
         <f>Employment_R11!AJ30</f>
         <v>23661.278142146552</v>
       </c>
-      <c r="Q29" s="66">
+      <c r="Q29" s="63">
         <f>Employment_R11!AK30</f>
         <v>5402.6774827575637</v>
       </c>
-      <c r="R29" s="66">
+      <c r="R29" s="63">
         <f>Employment_R11!AL30</f>
         <v>431.87128955562127</v>
       </c>
@@ -21980,71 +21980,71 @@
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="66">
+      <c r="B30" s="63">
         <f>Employment_NEA!Z30</f>
         <v>119.26573580096631</v>
       </c>
-      <c r="C30" s="66">
+      <c r="C30" s="63">
         <f>Employment_NEA!AA30</f>
         <v>1304.3103830509237</v>
       </c>
-      <c r="D30" s="66">
+      <c r="D30" s="63">
         <f>Employment_NEA!AB30</f>
         <v>259.45287892872506</v>
       </c>
-      <c r="E30" s="66">
+      <c r="E30" s="63">
         <f>Employment_NEA!AC30</f>
         <v>420.22632071622843</v>
       </c>
-      <c r="F30" s="66">
+      <c r="F30" s="63">
         <f>Employment_NEA!AD30</f>
         <v>1.1339634508115755</v>
       </c>
-      <c r="G30" s="66">
+      <c r="G30" s="63">
         <f>Employment_NEA!AE30</f>
         <v>41.377161364089901</v>
       </c>
-      <c r="H30" s="66">
+      <c r="H30" s="63">
         <f>Employment_R11!AB31</f>
         <v>123.88421498957082</v>
       </c>
-      <c r="I30" s="66">
+      <c r="I30" s="63">
         <f>Employment_R11!AC31</f>
         <v>501.71757644013445</v>
       </c>
-      <c r="J30" s="66">
+      <c r="J30" s="63">
         <f>Employment_R11!AD31</f>
         <v>716.41621083672851</v>
       </c>
-      <c r="K30" s="66">
+      <c r="K30" s="63">
         <f>Employment_R11!AE31</f>
         <v>82.145062481759439</v>
       </c>
-      <c r="L30" s="66">
+      <c r="L30" s="63">
         <f>Employment_R11!AF31</f>
         <v>170.83879234983266</v>
       </c>
-      <c r="M30" s="66">
+      <c r="M30" s="63">
         <f>Employment_R11!AG31</f>
         <v>378.08310374710788</v>
       </c>
-      <c r="N30" s="66">
+      <c r="N30" s="63">
         <f>Employment_R11!AH31</f>
         <v>446.22972429865985</v>
       </c>
-      <c r="O30" s="66">
+      <c r="O30" s="63">
         <f>Employment_R11!AI31</f>
         <v>290.66014565456686</v>
       </c>
-      <c r="P30" s="66">
+      <c r="P30" s="63">
         <f>Employment_R11!AJ31</f>
         <v>873.81123044666253</v>
       </c>
-      <c r="Q30" s="66">
+      <c r="Q30" s="63">
         <f>Employment_R11!AK31</f>
         <v>1926.204491553254</v>
       </c>
-      <c r="R30" s="66">
+      <c r="R30" s="63">
         <f>Employment_R11!AL31</f>
         <v>30.40802438779366</v>
       </c>
@@ -22053,71 +22053,71 @@
       <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="66">
+      <c r="B31" s="63">
         <f>Employment_NEA!Z31</f>
         <v>154.88024731065721</v>
       </c>
-      <c r="C31" s="66">
+      <c r="C31" s="63">
         <f>Employment_NEA!AA31</f>
         <v>1526.2367149141446</v>
       </c>
-      <c r="D31" s="66">
+      <c r="D31" s="63">
         <f>Employment_NEA!AB31</f>
         <v>103.89759829858373</v>
       </c>
-      <c r="E31" s="66">
+      <c r="E31" s="63">
         <f>Employment_NEA!AC31</f>
         <v>711.40816134568058</v>
       </c>
-      <c r="F31" s="66">
+      <c r="F31" s="63">
         <f>Employment_NEA!AD31</f>
         <v>9.4868111372656152</v>
       </c>
-      <c r="G31" s="66">
+      <c r="G31" s="63">
         <f>Employment_NEA!AE31</f>
         <v>52.332429988930862</v>
       </c>
-      <c r="H31" s="66">
+      <c r="H31" s="63">
         <f>Employment_R11!AB32</f>
         <v>809.60813278934449</v>
       </c>
-      <c r="I31" s="66">
+      <c r="I31" s="63">
         <f>Employment_R11!AC32</f>
         <v>714.84849572849953</v>
       </c>
-      <c r="J31" s="66">
+      <c r="J31" s="63">
         <f>Employment_R11!AD32</f>
         <v>700.02366481422769</v>
       </c>
-      <c r="K31" s="66">
+      <c r="K31" s="63">
         <f>Employment_R11!AE32</f>
         <v>169.51882102296076</v>
       </c>
-      <c r="L31" s="66">
+      <c r="L31" s="63">
         <f>Employment_R11!AF32</f>
         <v>199.71626429877878</v>
       </c>
-      <c r="M31" s="66">
+      <c r="M31" s="63">
         <f>Employment_R11!AG32</f>
         <v>557.75666063810922</v>
       </c>
-      <c r="N31" s="66">
+      <c r="N31" s="63">
         <f>Employment_R11!AH32</f>
         <v>920.20994468892741</v>
       </c>
-      <c r="O31" s="66">
+      <c r="O31" s="63">
         <f>Employment_R11!AI32</f>
         <v>468.22545389708404</v>
       </c>
-      <c r="P31" s="66">
+      <c r="P31" s="63">
         <f>Employment_R11!AJ32</f>
         <v>819.34587788792055</v>
       </c>
-      <c r="Q31" s="66">
+      <c r="Q31" s="63">
         <f>Employment_R11!AK32</f>
         <v>1614.0680181034427</v>
       </c>
-      <c r="R31" s="66">
+      <c r="R31" s="63">
         <f>Employment_R11!AL32</f>
         <v>96.205805639316281</v>
       </c>
@@ -22126,71 +22126,71 @@
       <c r="A32" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="63">
         <f>Employment_NEA!Z32</f>
         <v>17873.965</v>
       </c>
-      <c r="C32" s="66">
+      <c r="C32" s="63">
         <f>Employment_NEA!AA32</f>
         <v>307209.36845325987</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="63">
         <f>Employment_NEA!AB32</f>
         <v>44997.080999999998</v>
       </c>
-      <c r="E32" s="66">
+      <c r="E32" s="63">
         <f>Employment_NEA!AC32</f>
         <v>41628.824000000001</v>
       </c>
-      <c r="F32" s="66">
+      <c r="F32" s="63">
         <f>Employment_NEA!AD32</f>
         <v>575.29200000000003</v>
       </c>
-      <c r="G32" s="66">
+      <c r="G32" s="63">
         <f>Employment_NEA!AE32</f>
         <v>5939.3496373633661</v>
       </c>
-      <c r="H32" s="66">
+      <c r="H32" s="63">
         <f>Employment_R11!AB33</f>
         <v>138746.43108323409</v>
       </c>
-      <c r="I32" s="66">
+      <c r="I32" s="63">
         <f>Employment_R11!AC33</f>
         <v>175362.05474038195</v>
       </c>
-      <c r="J32" s="66">
+      <c r="J32" s="63">
         <f>Employment_R11!AD33</f>
         <v>157606.96652957294</v>
       </c>
-      <c r="K32" s="66">
+      <c r="K32" s="63">
         <f>Employment_R11!AE33</f>
         <v>29295.041413059866</v>
       </c>
-      <c r="L32" s="66">
+      <c r="L32" s="63">
         <f>Employment_R11!AF33</f>
         <v>31973.248022847922</v>
       </c>
-      <c r="M32" s="66">
+      <c r="M32" s="63">
         <f>Employment_R11!AG33</f>
         <v>80425.214207812969</v>
       </c>
-      <c r="N32" s="66">
+      <c r="N32" s="63">
         <f>Employment_R11!AH33</f>
         <v>133795.82836494956</v>
       </c>
-      <c r="O32" s="66">
+      <c r="O32" s="63">
         <f>Employment_R11!AI33</f>
         <v>22167.936982145598</v>
       </c>
-      <c r="P32" s="66">
+      <c r="P32" s="63">
         <f>Employment_R11!AJ33</f>
         <v>201878.12447343086</v>
       </c>
-      <c r="Q32" s="66">
+      <c r="Q32" s="63">
         <f>Employment_R11!AK33</f>
         <v>123203.18139816164</v>
       </c>
-      <c r="R32" s="66">
+      <c r="R32" s="63">
         <f>Employment_R11!AL33</f>
         <v>11571.469648719938</v>
       </c>
